--- a/prospetto_mezzi.xlsx
+++ b/prospetto_mezzi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lavoro\1. SERVIZIO N.C.C. 1 STANZIALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1BD7692-DC96-4D8B-A260-8BEB771BE561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1F39A5C-8D37-4A55-97E5-E67C26B6D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="216">
   <si>
     <t>EL706PT</t>
   </si>
@@ -649,6 +649,45 @@
   </si>
   <si>
     <t>MERCEDES-BENZ FINANCIAL SERVICES ITALIA</t>
+  </si>
+  <si>
+    <t>CP590XY</t>
+  </si>
+  <si>
+    <t>FV527LR</t>
+  </si>
+  <si>
+    <t>NSLRRT67R05C773G</t>
+  </si>
+  <si>
+    <t>NISSAN PRIMASTAR</t>
+  </si>
+  <si>
+    <t>MERCEDES BENZ</t>
+  </si>
+  <si>
+    <t>GRIGIO?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 5 COMUNE ROCCA PRIORA      </t>
+  </si>
+  <si>
+    <t>AMORE ANDREA</t>
+  </si>
+  <si>
+    <t>MRANDR67P14Z133N</t>
+  </si>
+  <si>
+    <t>GROTTAFERRATA</t>
+  </si>
+  <si>
+    <t>RM8236127</t>
+  </si>
+  <si>
+    <t>ANSALDO ROBERTO (SENZA PATENTE)</t>
+  </si>
+  <si>
+    <t>CIVITAVECCHIA           (PROB. INCAUTO AFFIDO)</t>
   </si>
 </sst>
 </file>
@@ -872,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1066,6 +1105,12 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1100,7 +1145,7 @@
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="22">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1208,11 +1253,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC00000"/>
-      </font>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1335,10 +1375,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U38" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U38" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="B4:U38" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:U38">
-    <sortCondition sortBy="fontColor" ref="B4:B38" dxfId="20"/>
+    <sortCondition ref="B4:B38"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="2" xr3:uid="{779EAAEE-59A7-446B-AD7C-6F7003AD1695}" name="TARGA" dataDxfId="19"/>
@@ -1716,7 +1756,7 @@
     <row r="10" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D11" s="1"/>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="73" t="s">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -1737,7 +1777,7 @@
     </row>
     <row r="12" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D12" s="5"/>
-      <c r="E12" s="72"/>
+      <c r="E12" s="74"/>
       <c r="F12" s="14" t="s">
         <v>15</v>
       </c>
@@ -1752,7 +1792,7 @@
     </row>
     <row r="13" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="3"/>
-      <c r="E13" s="73"/>
+      <c r="E13" s="75"/>
       <c r="F13" s="17"/>
       <c r="G13" s="18" t="s">
         <v>14</v>
@@ -1765,7 +1805,7 @@
     </row>
     <row r="14" spans="4:10" ht="150" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
-      <c r="E14" s="74" t="s">
+      <c r="E14" s="76" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="29" t="s">
@@ -1786,7 +1826,7 @@
     </row>
     <row r="15" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
-      <c r="E15" s="75"/>
+      <c r="E15" s="77"/>
       <c r="F15" s="31" t="s">
         <v>19</v>
       </c>
@@ -1803,7 +1843,7 @@
     </row>
     <row r="16" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D16" s="3"/>
-      <c r="E16" s="76"/>
+      <c r="E16" s="78"/>
       <c r="F16" s="34"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
@@ -1814,7 +1854,7 @@
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
-      <c r="E17" s="77" t="s">
+      <c r="E17" s="79" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="11" t="s">
@@ -1831,7 +1871,7 @@
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
-      <c r="E18" s="78"/>
+      <c r="E18" s="80"/>
       <c r="F18" s="14" t="s">
         <v>19</v>
       </c>
@@ -1844,7 +1884,7 @@
     </row>
     <row r="19" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D19" s="3"/>
-      <c r="E19" s="79"/>
+      <c r="E19" s="81"/>
       <c r="F19" s="17"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
@@ -2171,320 +2211,346 @@
       <c r="T5" s="63"/>
       <c r="U5" s="63"/>
     </row>
-    <row r="6" spans="2:21" s="64" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B6" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="48" t="s">
+    <row r="6" spans="2:21" s="64" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B6" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="45" t="s">
         <v>97</v>
       </c>
       <c r="G6" s="62"/>
       <c r="H6" s="59"/>
-      <c r="I6" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="J6" s="48">
-        <v>7131491008</v>
-      </c>
-      <c r="K6" s="68" t="s">
-        <v>13</v>
+      <c r="I6" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="J6" s="45">
+        <v>15242251005</v>
+      </c>
+      <c r="K6" s="45" t="s">
+        <v>169</v>
       </c>
       <c r="L6" s="62"/>
-      <c r="M6" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="N6" s="47"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="49"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="U6" s="48"/>
-    </row>
-    <row r="7" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B7" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48" t="s">
+      <c r="M6" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="44"/>
+      <c r="O6" s="45"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="45"/>
+      <c r="T6" s="45"/>
+      <c r="U6" s="45"/>
+    </row>
+    <row r="7" spans="2:21" s="65" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="B7" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>175</v>
+      </c>
+      <c r="E7" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G7" s="62"/>
-      <c r="H7" s="59"/>
+      <c r="F7" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="52">
+        <v>45787</v>
+      </c>
       <c r="I7" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="J7" s="51" t="s">
-        <v>155</v>
+        <v>122</v>
+      </c>
+      <c r="J7" s="51">
+        <v>13068821001</v>
       </c>
       <c r="K7" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="L7" s="54">
-        <v>46766</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="L7" s="62"/>
       <c r="M7" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="40"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="63"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="63"/>
-      <c r="T7" s="63"/>
-      <c r="U7" s="63"/>
+      <c r="N7" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="O7" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q7" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="R7" s="52">
+        <v>47200</v>
+      </c>
+      <c r="S7" s="51"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
     </row>
     <row r="8" spans="2:21" s="66" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="48" t="s">
+      <c r="B8" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="48" t="s">
+      <c r="D8" s="45"/>
+      <c r="E8" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="45" t="s">
         <v>97</v>
       </c>
       <c r="G8" s="62"/>
       <c r="H8" s="59"/>
-      <c r="I8" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="J8" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="K8" s="62"/>
+      <c r="I8" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="45">
+        <v>15242251005</v>
+      </c>
+      <c r="K8" s="45" t="s">
+        <v>169</v>
+      </c>
       <c r="L8" s="62"/>
-      <c r="M8" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="47"/>
-      <c r="O8" s="48"/>
-      <c r="P8" s="48"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="48"/>
-      <c r="T8" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="U8" s="48"/>
+      <c r="M8" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N8" s="44"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="45"/>
+      <c r="Q8" s="45"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="45"/>
+      <c r="T8" s="45"/>
+      <c r="U8" s="45"/>
     </row>
     <row r="9" spans="2:21" s="66" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48" t="s">
+      <c r="B9" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F9" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G9" s="62"/>
-      <c r="H9" s="59"/>
+      <c r="F9" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="H9" s="52">
+        <v>40497</v>
+      </c>
       <c r="I9" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="J9" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="K9" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="L9" s="54">
-        <v>46766</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="J9" s="51">
+        <v>12611021002</v>
+      </c>
+      <c r="K9" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L9" s="62"/>
       <c r="M9" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="40"/>
-      <c r="O9" s="63"/>
-      <c r="P9" s="63"/>
-      <c r="Q9" s="63"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="63"/>
-      <c r="T9" s="63"/>
-      <c r="U9" s="63"/>
+      <c r="N9" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="O9" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P9" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q9" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="R9" s="53"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U9" s="51"/>
     </row>
     <row r="10" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="44" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45" t="s">
+      <c r="B10" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="51" t="s">
         <v>97</v>
       </c>
       <c r="G10" s="62"/>
       <c r="H10" s="59"/>
-      <c r="I10" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="J10" s="45">
-        <v>15242251005</v>
-      </c>
-      <c r="K10" s="45" t="s">
-        <v>169</v>
+      <c r="I10" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="J10" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="K10" s="67" t="s">
+        <v>168</v>
       </c>
       <c r="L10" s="62"/>
-      <c r="M10" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="44"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="46"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
+      <c r="M10" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="50"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="53"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="51"/>
     </row>
     <row r="11" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="45" t="s">
+      <c r="B11" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45" t="s">
+      <c r="D11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="62"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="45">
-        <v>15242251005</v>
-      </c>
-      <c r="K11" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="L11" s="62"/>
-      <c r="M11" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="44"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-    </row>
-    <row r="12" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B12" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="45" t="s">
+      <c r="F11" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="H11" s="52">
+        <v>41932</v>
+      </c>
+      <c r="I11" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="K11" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="L11" s="54">
+        <v>47246</v>
+      </c>
+      <c r="M11" s="53" t="s">
+        <v>143</v>
+      </c>
+      <c r="N11" s="50"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="53"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U11" s="51"/>
+    </row>
+    <row r="12" spans="2:21" s="65" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="48" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="45" t="s">
+      <c r="D12" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="48" t="s">
         <v>97</v>
       </c>
       <c r="G12" s="62"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J12" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K12" s="67" t="s">
-        <v>170</v>
+      <c r="I12" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="J12" s="48">
+        <v>7131491008</v>
+      </c>
+      <c r="K12" s="68" t="s">
+        <v>13</v>
       </c>
       <c r="L12" s="62"/>
-      <c r="M12" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N12" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="O12" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q12" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="R12" s="52">
-        <v>46790</v>
-      </c>
-      <c r="S12" s="51"/>
-      <c r="T12" s="51" t="s">
+      <c r="M12" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="N12" s="47"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="U12" s="51"/>
+      <c r="U12" s="48"/>
     </row>
     <row r="13" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B13" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45" t="s">
+      <c r="B13" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="62"/>
-      <c r="H13" s="59"/>
+      <c r="F13" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="H13" s="52">
+        <v>43179</v>
+      </c>
       <c r="I13" s="50" t="s">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="J13" s="51">
-        <v>14119701002</v>
+        <v>15242251005</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L13" s="62"/>
       <c r="M13" s="53" t="s">
@@ -2500,53 +2566,67 @@
       <c r="U13" s="51"/>
     </row>
     <row r="14" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B14" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45" t="s">
+      <c r="B14" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="E14" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F14" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="62"/>
-      <c r="H14" s="59"/>
+      <c r="F14" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" s="52">
+        <v>42065</v>
+      </c>
       <c r="I14" s="50" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="J14" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K14" s="51" t="s">
-        <v>169</v>
+        <v>12611021002</v>
+      </c>
+      <c r="K14" s="67" t="s">
+        <v>170</v>
       </c>
       <c r="L14" s="62"/>
       <c r="M14" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="50"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
-      <c r="R14" s="53"/>
+      <c r="N14" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="O14" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q14" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="R14" s="53" t="s">
+        <v>191</v>
+      </c>
       <c r="S14" s="51"/>
       <c r="T14" s="51"/>
       <c r="U14" s="51"/>
     </row>
-    <row r="15" spans="2:21" s="60" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:21" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="50" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>175</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D15" s="51"/>
       <c r="E15" s="51" t="s">
         <v>94</v>
       </c>
@@ -2554,70 +2634,60 @@
         <v>100</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="H15" s="52">
-        <v>45787</v>
+        <v>45387</v>
       </c>
       <c r="I15" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="J15" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="L15" s="54">
+        <v>46315</v>
+      </c>
+      <c r="M15" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="50"/>
+      <c r="O15" s="51"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U15" s="51"/>
+    </row>
+    <row r="16" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B16" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="62"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="J15" s="51">
+      <c r="J16" s="51">
         <v>13068821001</v>
-      </c>
-      <c r="K15" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="L15" s="62"/>
-      <c r="M15" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="O15" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q15" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="R15" s="52">
-        <v>47200</v>
-      </c>
-      <c r="S15" s="51"/>
-      <c r="T15" s="51"/>
-      <c r="U15" s="51"/>
-    </row>
-    <row r="16" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B16" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G16" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="H16" s="52">
-        <v>40497</v>
-      </c>
-      <c r="I16" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="J16" s="51">
-        <v>12611021002</v>
       </c>
       <c r="K16" s="67" t="s">
         <v>170</v>
@@ -2627,18 +2697,20 @@
         <v>22</v>
       </c>
       <c r="N16" s="50" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="O16" s="51" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="Q16" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="R16" s="53"/>
+        <v>126</v>
+      </c>
+      <c r="R16" s="52">
+        <v>46790</v>
+      </c>
       <c r="S16" s="51"/>
       <c r="T16" s="51" t="s">
         <v>89</v>
@@ -2647,31 +2719,35 @@
     </row>
     <row r="17" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="50" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D17" s="51"/>
       <c r="E17" s="51" t="s">
         <v>94</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="G17" s="62"/>
-      <c r="H17" s="59"/>
+        <v>100</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>109</v>
+      </c>
+      <c r="H17" s="52">
+        <v>43284</v>
+      </c>
       <c r="I17" s="50" t="s">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="J17" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="K17" s="67" t="s">
-        <v>168</v>
+        <v>15242251005</v>
+      </c>
+      <c r="K17" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="L17" s="62"/>
-      <c r="M17" s="59" t="s">
+      <c r="M17" s="53" t="s">
         <v>22</v>
       </c>
       <c r="N17" s="50"/>
@@ -2685,13 +2761,13 @@
     </row>
     <row r="18" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B18" s="50" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="E18" s="51" t="s">
         <v>94</v>
@@ -2700,45 +2776,53 @@
         <v>100</v>
       </c>
       <c r="G18" s="51" t="s">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="H18" s="52">
-        <v>41932</v>
+        <v>45084</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="J18" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="K18" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="L18" s="54">
-        <v>47246</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J18" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K18" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L18" s="69"/>
       <c r="M18" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="N18" s="50"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="53"/>
+        <v>22</v>
+      </c>
+      <c r="N18" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P18" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q18" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="R18" s="52">
+        <v>46568</v>
+      </c>
       <c r="S18" s="51"/>
-      <c r="T18" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T18" s="51"/>
       <c r="U18" s="51"/>
     </row>
     <row r="19" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B19" s="50" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="51"/>
+        <v>133</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>81</v>
+      </c>
       <c r="E19" s="51" t="s">
         <v>94</v>
       </c>
@@ -2746,42 +2830,54 @@
         <v>100</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="H19" s="52">
-        <v>43179</v>
+        <v>41404</v>
       </c>
       <c r="I19" s="50" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="J19" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K19" s="51" t="s">
+        <v>12578741006</v>
+      </c>
+      <c r="K19" s="67" t="s">
         <v>169</v>
       </c>
       <c r="L19" s="62"/>
       <c r="M19" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="50"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="51"/>
-      <c r="T19" s="51"/>
-      <c r="U19" s="51"/>
+      <c r="N19" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="O19" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="P19" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q19" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="R19" s="55">
+        <v>44044</v>
+      </c>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="U19" s="43"/>
     </row>
     <row r="20" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="50" t="s">
-        <v>174</v>
+        <v>91</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="D20" s="51" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="E20" s="51" t="s">
         <v>94</v>
@@ -2790,16 +2886,16 @@
         <v>100</v>
       </c>
       <c r="G20" s="51" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="H20" s="52">
-        <v>42065</v>
+        <v>42809</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J20" s="51">
-        <v>12611021002</v>
+        <v>13068821001</v>
       </c>
       <c r="K20" s="67" t="s">
         <v>170</v>
@@ -2809,58 +2905,60 @@
         <v>22</v>
       </c>
       <c r="N20" s="50" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="O20" s="51" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="Q20" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="R20" s="53" t="s">
-        <v>191</v>
+        <v>156</v>
+      </c>
+      <c r="R20" s="52">
+        <v>46766</v>
       </c>
       <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
+      <c r="T20" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U20" s="51"/>
     </row>
-    <row r="21" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" s="65" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B21" s="50" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="51"/>
+        <v>181</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>85</v>
+      </c>
       <c r="E21" s="51" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="F21" s="51" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="H21" s="52">
-        <v>45387</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="J21" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="K21" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="L21" s="54">
-        <v>46315</v>
-      </c>
-      <c r="M21" s="53" t="s">
-        <v>22</v>
+        <v>42423</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="J21" s="48">
+        <v>7988341009</v>
+      </c>
+      <c r="K21" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="L21" s="62"/>
+      <c r="M21" s="49" t="s">
+        <v>194</v>
       </c>
       <c r="N21" s="50"/>
       <c r="O21" s="51"/>
@@ -2868,110 +2966,92 @@
       <c r="Q21" s="51"/>
       <c r="R21" s="53"/>
       <c r="S21" s="51"/>
-      <c r="T21" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T21" s="51"/>
       <c r="U21" s="51"/>
     </row>
     <row r="22" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B22" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="51"/>
-      <c r="E22" s="51" t="s">
+      <c r="B22" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="H22" s="52">
-        <v>43284</v>
-      </c>
+      <c r="F22" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="62"/>
+      <c r="H22" s="59"/>
       <c r="I22" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J22" s="51">
-        <v>15242251005</v>
+        <v>154</v>
+      </c>
+      <c r="J22" s="51" t="s">
+        <v>155</v>
       </c>
       <c r="K22" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="L22" s="62"/>
+        <v>156</v>
+      </c>
+      <c r="L22" s="54">
+        <v>46766</v>
+      </c>
       <c r="M22" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N22" s="50"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="51"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="51"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="63"/>
+      <c r="P22" s="63"/>
+      <c r="Q22" s="63"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="63"/>
+      <c r="T22" s="63"/>
+      <c r="U22" s="63"/>
     </row>
     <row r="23" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B23" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="E23" s="51" t="s">
+      <c r="B23" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F23" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="H23" s="52">
-        <v>45084</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J23" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K23" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L23" s="69"/>
-      <c r="M23" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="O23" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P23" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q23" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="R23" s="52">
-        <v>46568</v>
-      </c>
-      <c r="S23" s="51"/>
-      <c r="T23" s="51"/>
-      <c r="U23" s="51"/>
+      <c r="F23" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="62"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="J23" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="47"/>
+      <c r="O23" s="48"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="48"/>
+      <c r="T23" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="U23" s="48"/>
     </row>
     <row r="24" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B24" s="50" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C24" s="51" t="s">
         <v>133</v>
@@ -2986,51 +3066,51 @@
         <v>100</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H24" s="52">
-        <v>41404</v>
+        <v>42426</v>
       </c>
       <c r="I24" s="50" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="J24" s="51">
-        <v>12578741006</v>
+        <v>13068821001</v>
       </c>
       <c r="K24" s="67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L24" s="62"/>
       <c r="M24" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="O24" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="P24" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q24" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="R24" s="55">
-        <v>44044</v>
-      </c>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43" t="s">
+      <c r="N24" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="O24" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q24" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="R24" s="52">
+        <v>46854</v>
+      </c>
+      <c r="S24" s="51"/>
+      <c r="T24" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="U24" s="43"/>
+      <c r="U24" s="51"/>
     </row>
     <row r="25" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B25" s="50" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C25" s="51" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="D25" s="51" t="s">
         <v>77</v>
@@ -3042,79 +3122,71 @@
         <v>100</v>
       </c>
       <c r="G25" s="51" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="H25" s="52">
-        <v>42809</v>
+        <v>43879</v>
       </c>
       <c r="I25" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J25" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K25" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L25" s="62"/>
+        <v>164</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="L25" s="54">
+        <v>46594</v>
+      </c>
       <c r="M25" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N25" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="O25" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P25" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q25" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="R25" s="52">
-        <v>46766</v>
-      </c>
+      <c r="N25" s="50"/>
+      <c r="O25" s="51"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="51"/>
+      <c r="R25" s="53"/>
       <c r="S25" s="51"/>
       <c r="T25" s="51" t="s">
         <v>89</v>
       </c>
       <c r="U25" s="51"/>
     </row>
-    <row r="26" spans="1:21" s="60" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B26" s="50" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="C26" s="51" t="s">
-        <v>181</v>
+        <v>98</v>
       </c>
       <c r="D26" s="51" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E26" s="51" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="F26" s="51" t="s">
         <v>100</v>
       </c>
       <c r="G26" s="51" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="H26" s="52">
-        <v>42423</v>
-      </c>
-      <c r="I26" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="J26" s="48">
-        <v>7988341009</v>
-      </c>
-      <c r="K26" s="68" t="s">
-        <v>193</v>
+        <v>45648</v>
+      </c>
+      <c r="I26" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J26" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K26" s="67" t="s">
+        <v>170</v>
       </c>
       <c r="L26" s="62"/>
-      <c r="M26" s="49" t="s">
-        <v>194</v>
+      <c r="M26" s="53" t="s">
+        <v>22</v>
       </c>
       <c r="N26" s="50"/>
       <c r="O26" s="51"/>
@@ -3122,19 +3194,21 @@
       <c r="Q26" s="51"/>
       <c r="R26" s="53"/>
       <c r="S26" s="51"/>
-      <c r="T26" s="51"/>
+      <c r="T26" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U26" s="51"/>
     </row>
     <row r="27" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="57"/>
       <c r="B27" s="51" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E27" s="51" t="s">
         <v>94</v>
@@ -3143,10 +3217,10 @@
         <v>100</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H27" s="52">
-        <v>42426</v>
+        <v>45412</v>
       </c>
       <c r="I27" s="51" t="s">
         <v>122</v>
@@ -3162,19 +3236,19 @@
         <v>22</v>
       </c>
       <c r="N27" s="51" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="O27" s="51" t="s">
         <v>22</v>
       </c>
       <c r="P27" s="51" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="Q27" s="51" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="R27" s="52">
-        <v>46854</v>
+        <v>46568</v>
       </c>
       <c r="S27" s="51"/>
       <c r="T27" s="51" t="s">
@@ -3183,63 +3257,55 @@
       <c r="U27" s="51"/>
     </row>
     <row r="28" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B28" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="51" t="s">
+      <c r="B28" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G28" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="H28" s="52">
-        <v>43879</v>
-      </c>
+      <c r="F28" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="62"/>
+      <c r="H28" s="59"/>
       <c r="I28" s="50" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="J28" s="51" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="K28" s="51" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="L28" s="54">
-        <v>46594</v>
+        <v>46766</v>
       </c>
       <c r="M28" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="50"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="53"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U28" s="51"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="63"/>
+      <c r="P28" s="63"/>
+      <c r="Q28" s="63"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="63"/>
+      <c r="T28" s="63"/>
+      <c r="U28" s="63"/>
     </row>
     <row r="29" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="57"/>
       <c r="B29" s="51" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C29" s="51" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="51" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E29" s="51" t="s">
         <v>94</v>
@@ -3248,16 +3314,16 @@
         <v>100</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="H29" s="52">
-        <v>45648</v>
+        <v>44985</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J29" s="51">
-        <v>13068821001</v>
+        <v>11767131003</v>
       </c>
       <c r="K29" s="67" t="s">
         <v>170</v>
@@ -3280,13 +3346,13 @@
     <row r="30" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
       <c r="B30" s="51" t="s">
-        <v>86</v>
+        <v>197</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="D30" s="51" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E30" s="51" t="s">
         <v>94</v>
@@ -3295,49 +3361,43 @@
         <v>100</v>
       </c>
       <c r="G30" s="51" t="s">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="H30" s="52">
-        <v>45412</v>
+        <v>45979</v>
       </c>
       <c r="I30" s="50" t="s">
-        <v>122</v>
+        <v>200</v>
       </c>
       <c r="J30" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K30" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L30" s="62"/>
+        <v>9075711219</v>
+      </c>
+      <c r="K30" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="L30" s="51"/>
       <c r="M30" s="53" t="s">
-        <v>22</v>
+        <v>201</v>
       </c>
       <c r="N30" s="50" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="O30" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P30" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q30" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="R30" s="52">
-        <v>46568</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="P30" s="51">
+        <v>2828850582</v>
+      </c>
+      <c r="Q30" s="51"/>
+      <c r="R30" s="53"/>
       <c r="S30" s="51"/>
-      <c r="T30" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T30" s="51"/>
       <c r="U30" s="51"/>
     </row>
     <row r="31" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
       <c r="B31" s="51" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C31" s="51" t="s">
         <v>98</v>
@@ -3352,27 +3412,33 @@
         <v>100</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="H31" s="52">
-        <v>44985</v>
+        <v>43584</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>130</v>
+        <v>78</v>
       </c>
       <c r="J31" s="51">
-        <v>11767131003</v>
+        <v>15242251005</v>
       </c>
       <c r="K31" s="67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L31" s="62"/>
       <c r="M31" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N31" s="50"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
+      <c r="N31" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="O31" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" s="51">
+        <v>14119701002</v>
+      </c>
       <c r="Q31" s="51"/>
       <c r="R31" s="53"/>
       <c r="S31" s="51"/>
@@ -3409,60 +3475,46 @@
       <c r="J32" s="51">
         <v>15242251005</v>
       </c>
-      <c r="K32" s="67" t="s">
+      <c r="K32" s="51" t="s">
         <v>169</v>
       </c>
       <c r="L32" s="62"/>
       <c r="M32" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N32" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="O32" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P32" s="51">
-        <v>14119701002</v>
-      </c>
+      <c r="N32" s="50"/>
+      <c r="O32" s="51"/>
+      <c r="P32" s="51"/>
       <c r="Q32" s="51"/>
       <c r="R32" s="53"/>
       <c r="S32" s="51"/>
-      <c r="T32" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T32" s="51"/>
       <c r="U32" s="51"/>
     </row>
     <row r="33" spans="2:21" s="70" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="51" t="s">
+      <c r="B33" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="51" t="s">
+      <c r="D33" s="45"/>
+      <c r="E33" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F33" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H33" s="52">
-        <v>43584</v>
-      </c>
+      <c r="F33" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="62"/>
+      <c r="H33" s="59"/>
       <c r="I33" s="50" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="J33" s="51">
-        <v>15242251005</v>
+        <v>14119701002</v>
       </c>
       <c r="K33" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L33" s="62"/>
       <c r="M33" s="53" t="s">
@@ -3478,138 +3530,171 @@
       <c r="U33" s="51"/>
     </row>
     <row r="34" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B34" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" s="51" t="s">
+      <c r="B34" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D34" s="45"/>
+      <c r="E34" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F34" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="H34" s="52">
-        <v>45909</v>
-      </c>
+      <c r="F34" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G34" s="62"/>
+      <c r="H34" s="59"/>
       <c r="I34" s="50" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="J34" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K34" s="67" t="s">
-        <v>170</v>
+        <v>15242251005</v>
+      </c>
+      <c r="K34" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="L34" s="62"/>
       <c r="M34" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N34" s="50" t="s">
+      <c r="N34" s="50"/>
+      <c r="O34" s="51"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="51"/>
+      <c r="R34" s="53"/>
+      <c r="S34" s="51"/>
+      <c r="T34" s="51"/>
+      <c r="U34" s="51"/>
+    </row>
+    <row r="35" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B35" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="52">
+        <v>45909</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J35" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K35" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L35" s="62"/>
+      <c r="M35" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="O34" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P34" s="51" t="s">
+      <c r="O35" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P35" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="Q34" s="51" t="s">
+      <c r="Q35" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="R34" s="52">
+      <c r="R35" s="52">
         <v>47469</v>
       </c>
-      <c r="S34" s="51"/>
-      <c r="T34" s="51" t="s">
+      <c r="S35" s="51"/>
+      <c r="T35" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="U34" s="51"/>
-    </row>
-    <row r="35" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B35" s="40" t="s">
-        <v>197</v>
-      </c>
-      <c r="C35" s="63" t="s">
-        <v>198</v>
-      </c>
-      <c r="D35" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" s="63" t="s">
+      <c r="U35" s="51"/>
+    </row>
+    <row r="36" spans="2:21" s="71" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B36" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="D36" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="E36" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="63" t="s">
+      <c r="F36" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" s="48"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="J36" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="N36" s="47"/>
+      <c r="O36" s="48"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="49"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="48"/>
+    </row>
+    <row r="37" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B37" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="D37" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="E37" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="G35" s="63" t="s">
-        <v>199</v>
-      </c>
-      <c r="H35" s="80">
-        <v>45979</v>
-      </c>
-      <c r="I35" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="J35" s="63">
-        <v>9075711219</v>
-      </c>
-      <c r="M35" s="41" t="s">
-        <v>201</v>
-      </c>
-      <c r="N35" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="O35" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="P35" s="63">
-        <v>2828850582</v>
-      </c>
-      <c r="Q35" s="63"/>
-      <c r="R35" s="41"/>
-      <c r="S35" s="63"/>
-      <c r="T35" s="63"/>
-      <c r="U35" s="63"/>
-    </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B36" s="40"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="40"/>
-      <c r="J36" s="63"/>
-      <c r="M36" s="41"/>
-      <c r="N36" s="40"/>
-      <c r="O36" s="63"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="41"/>
-      <c r="S36" s="63"/>
-      <c r="T36" s="63"/>
-      <c r="U36" s="63"/>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B37" s="40"/>
-      <c r="C37" s="63"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="40"/>
-      <c r="J37" s="63"/>
-      <c r="M37" s="41"/>
+      <c r="G37" s="63" t="s">
+        <v>209</v>
+      </c>
+      <c r="H37" s="82">
+        <v>41592</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="J37" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="K37" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="M37" s="41" t="s">
+        <v>212</v>
+      </c>
       <c r="N37" s="40"/>
       <c r="O37" s="63"/>
       <c r="P37" s="63"/>

--- a/prospetto_mezzi.xlsx
+++ b/prospetto_mezzi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Lavoro\1. SERVIZIO N.C.C. 1 STANZIALE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Fs-rm073\rm229 - gruppo civitavecchia\6\7\8\1. ATTIVITA' GLOBALE_SERVER\1. SERVIZIO N.C.C. 1 STANZIALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1F39A5C-8D37-4A55-97E5-E67C26B6D9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E03EBC-6284-4336-BACD-426A0ABCE129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="233">
   <si>
     <t>EL706PT</t>
   </si>
@@ -684,17 +684,68 @@
     <t>RM8236127</t>
   </si>
   <si>
-    <t>ANSALDO ROBERTO (SENZA PATENTE)</t>
-  </si>
-  <si>
-    <t>CIVITAVECCHIA           (PROB. INCAUTO AFFIDO)</t>
+    <t xml:space="preserve">CIVITAVECCHIA          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANSALDO ROBERTO       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (NO KB)</t>
+  </si>
+  <si>
+    <t>DN327LE</t>
+  </si>
+  <si>
+    <t>FW344LN</t>
+  </si>
+  <si>
+    <t>DD432WR</t>
+  </si>
+  <si>
+    <t>GL147SJ</t>
+  </si>
+  <si>
+    <t>FG170JP</t>
+  </si>
+  <si>
+    <t>BANINA RACHEL</t>
+  </si>
+  <si>
+    <t>BNNRHL64T71Z311V</t>
+  </si>
+  <si>
+    <t>TARQUINIA</t>
+  </si>
+  <si>
+    <t>VT8007860</t>
+  </si>
+  <si>
+    <t>MERCEDES BENZ VITO TOUR</t>
+  </si>
+  <si>
+    <t>PRIAMO SOCIETA COOPERATIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 3  COMUNE ORBETELLO </t>
+  </si>
+  <si>
+    <t>CIVI.CAR SOC. COOP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 6 COMUNE GROTTAFERRATA   </t>
+  </si>
+  <si>
+    <t>ROYAL BLU TRAVEL COOPERATIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC.28 COMUNE TREVI    </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -794,6 +845,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -911,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1111,6 +1170,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1138,8 +1200,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1375,10 +1452,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U38" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="B4:U38" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:U38">
-    <sortCondition ref="B4:B38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U48" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="B4:U48" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:U48">
+    <sortCondition ref="B4:B48"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="2" xr3:uid="{779EAAEE-59A7-446B-AD7C-6F7003AD1695}" name="TARGA" dataDxfId="19"/>
@@ -1756,7 +1833,7 @@
     <row r="10" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D11" s="1"/>
-      <c r="E11" s="73" t="s">
+      <c r="E11" s="74" t="s">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -1777,7 +1854,7 @@
     </row>
     <row r="12" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D12" s="5"/>
-      <c r="E12" s="74"/>
+      <c r="E12" s="75"/>
       <c r="F12" s="14" t="s">
         <v>15</v>
       </c>
@@ -1792,7 +1869,7 @@
     </row>
     <row r="13" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="3"/>
-      <c r="E13" s="75"/>
+      <c r="E13" s="76"/>
       <c r="F13" s="17"/>
       <c r="G13" s="18" t="s">
         <v>14</v>
@@ -1805,7 +1882,7 @@
     </row>
     <row r="14" spans="4:10" ht="150" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="77" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="29" t="s">
@@ -1826,7 +1903,7 @@
     </row>
     <row r="15" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
-      <c r="E15" s="77"/>
+      <c r="E15" s="78"/>
       <c r="F15" s="31" t="s">
         <v>19</v>
       </c>
@@ -1843,7 +1920,7 @@
     </row>
     <row r="16" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D16" s="3"/>
-      <c r="E16" s="78"/>
+      <c r="E16" s="79"/>
       <c r="F16" s="34"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
@@ -1854,7 +1931,7 @@
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
-      <c r="E17" s="79" t="s">
+      <c r="E17" s="80" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="11" t="s">
@@ -1871,7 +1948,7 @@
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
-      <c r="E18" s="80"/>
+      <c r="E18" s="81"/>
       <c r="F18" s="14" t="s">
         <v>19</v>
       </c>
@@ -1884,7 +1961,7 @@
     </row>
     <row r="19" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D19" s="3"/>
-      <c r="E19" s="81"/>
+      <c r="E19" s="82"/>
       <c r="F19" s="17"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
@@ -2086,7 +2163,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56392095-0261-4957-A1EF-F42F71E397DD}">
-  <dimension ref="A3:U38"/>
+  <dimension ref="A3:U48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="61"/>
@@ -2173,387 +2250,375 @@
     </row>
     <row r="5" spans="2:21" s="64" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B5" s="47" t="s">
-        <v>46</v>
+        <v>203</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>192</v>
-      </c>
-      <c r="D5" s="48"/>
+        <v>206</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>208</v>
+      </c>
       <c r="E5" s="48" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="62"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="50" t="s">
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="L5" s="48"/>
+      <c r="M5" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="N5" s="47"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="48"/>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+    </row>
+    <row r="6" spans="2:21" s="64" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B6" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="85" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="85"/>
+      <c r="E6" s="85" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="85" t="s">
+        <v>228</v>
+      </c>
+      <c r="H6" s="86"/>
+      <c r="I6" s="84" t="s">
+        <v>227</v>
+      </c>
+      <c r="J6" s="85">
+        <v>12838081003</v>
+      </c>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="N6" s="84"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="85"/>
+      <c r="Q6" s="85"/>
+      <c r="R6" s="86"/>
+      <c r="S6" s="85"/>
+      <c r="T6" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U6" s="85"/>
+    </row>
+    <row r="7" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B7" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="62"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J7" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="K7" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="L5" s="54">
+      <c r="L7" s="54">
         <v>46766</v>
       </c>
-      <c r="M5" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="40"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="41"/>
-      <c r="S5" s="63"/>
-      <c r="T5" s="63"/>
-      <c r="U5" s="63"/>
-    </row>
-    <row r="6" spans="2:21" s="64" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="44" t="s">
+      <c r="M7" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N7" s="40"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="63"/>
+      <c r="T7" s="63"/>
+      <c r="U7" s="63"/>
+    </row>
+    <row r="8" spans="2:21" s="66" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B8" s="47" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="48"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="84" t="s">
+        <v>222</v>
+      </c>
+      <c r="J8" s="85" t="s">
+        <v>223</v>
+      </c>
+      <c r="K8" s="85" t="s">
+        <v>225</v>
+      </c>
+      <c r="L8" s="85"/>
+      <c r="M8" s="86" t="s">
+        <v>224</v>
+      </c>
+      <c r="N8" s="47"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="U8" s="48"/>
+    </row>
+    <row r="9" spans="2:21" s="66" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B9" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="C9" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45" t="s">
+      <c r="D9" s="45"/>
+      <c r="E9" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F9" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="62"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="44" t="s">
+      <c r="G9" s="62"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="J6" s="45">
+      <c r="J9" s="45">
         <v>15242251005</v>
       </c>
-      <c r="K6" s="45" t="s">
+      <c r="K9" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="L6" s="62"/>
-      <c r="M6" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="44"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="45"/>
-      <c r="T6" s="45"/>
-      <c r="U6" s="45"/>
-    </row>
-    <row r="7" spans="2:21" s="65" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="B7" s="50" t="s">
+      <c r="L9" s="62"/>
+      <c r="M9" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="44"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="46"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+    </row>
+    <row r="10" spans="2:21" s="65" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="B10" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="51" t="s">
+      <c r="C10" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="51" t="s">
+      <c r="D10" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="E7" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="52">
-        <v>45787</v>
-      </c>
-      <c r="I7" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J7" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K7" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="L7" s="62"/>
-      <c r="M7" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N7" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="O7" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P7" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q7" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="R7" s="52">
-        <v>47200</v>
-      </c>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-    </row>
-    <row r="8" spans="2:21" s="66" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B8" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="62"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="45">
-        <v>15242251005</v>
-      </c>
-      <c r="K8" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="L8" s="62"/>
-      <c r="M8" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N8" s="44"/>
-      <c r="O8" s="45"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="45"/>
-      <c r="R8" s="46"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="45"/>
-      <c r="U8" s="45"/>
-    </row>
-    <row r="9" spans="2:21" s="66" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B9" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="H9" s="52">
-        <v>40497</v>
-      </c>
-      <c r="I9" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="J9" s="51">
-        <v>12611021002</v>
-      </c>
-      <c r="K9" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L9" s="62"/>
-      <c r="M9" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="O9" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q9" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="R9" s="53"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U9" s="51"/>
-    </row>
-    <row r="10" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B10" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D10" s="51"/>
       <c r="E10" s="51" t="s">
         <v>94</v>
       </c>
       <c r="F10" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="62"/>
-      <c r="H10" s="59"/>
+        <v>100</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="52">
+        <v>45787</v>
+      </c>
       <c r="I10" s="50" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J10" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="K10" s="67" t="s">
-        <v>168</v>
+        <v>13068821001</v>
+      </c>
+      <c r="K10" s="51" t="s">
+        <v>170</v>
       </c>
       <c r="L10" s="62"/>
-      <c r="M10" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="50"/>
-      <c r="O10" s="51"/>
-      <c r="P10" s="51"/>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="53"/>
+      <c r="M10" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="O10" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P10" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q10" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="R10" s="52">
+        <v>47200</v>
+      </c>
       <c r="S10" s="51"/>
       <c r="T10" s="51"/>
       <c r="U10" s="51"/>
     </row>
     <row r="11" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="51" t="s">
+      <c r="B11" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="D11" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="51" t="s">
+      <c r="D11" s="45"/>
+      <c r="E11" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F11" s="51" t="s">
+      <c r="F11" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="62"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="45">
+        <v>15242251005</v>
+      </c>
+      <c r="K11" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="L11" s="62"/>
+      <c r="M11" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="44"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="45"/>
+      <c r="T11" s="45"/>
+      <c r="U11" s="45"/>
+    </row>
+    <row r="12" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B12" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G11" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="H11" s="52">
-        <v>41932</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="J11" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="K11" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="L11" s="54">
-        <v>47246</v>
-      </c>
-      <c r="M11" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="N11" s="50"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="53"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51" t="s">
+      <c r="G12" s="51" t="s">
+        <v>115</v>
+      </c>
+      <c r="H12" s="52">
+        <v>40497</v>
+      </c>
+      <c r="I12" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="J12" s="51">
+        <v>12611021002</v>
+      </c>
+      <c r="K12" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L12" s="62"/>
+      <c r="M12" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N12" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="O12" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P12" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q12" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="R12" s="53"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="U11" s="51"/>
-    </row>
-    <row r="12" spans="2:21" s="65" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B12" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G12" s="62"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="J12" s="48">
-        <v>7131491008</v>
-      </c>
-      <c r="K12" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" s="62"/>
-      <c r="M12" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="N12" s="47"/>
-      <c r="O12" s="48"/>
-      <c r="P12" s="48"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="48"/>
-      <c r="T12" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="U12" s="48"/>
+      <c r="U12" s="51"/>
     </row>
     <row r="13" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B13" s="50" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D13" s="51"/>
       <c r="E13" s="51" t="s">
         <v>94</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" s="52">
-        <v>43179</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G13" s="62"/>
+      <c r="H13" s="59"/>
       <c r="I13" s="50" t="s">
-        <v>78</v>
+        <v>167</v>
       </c>
       <c r="J13" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K13" s="51" t="s">
-        <v>169</v>
+        <v>14119701002</v>
+      </c>
+      <c r="K13" s="67" t="s">
+        <v>168</v>
       </c>
       <c r="L13" s="62"/>
-      <c r="M13" s="53" t="s">
+      <c r="M13" s="59" t="s">
         <v>22</v>
       </c>
       <c r="N13" s="50"/>
@@ -2567,13 +2632,13 @@
     </row>
     <row r="14" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B14" s="50" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="E14" s="51" t="s">
         <v>94</v>
@@ -2582,149 +2647,131 @@
         <v>100</v>
       </c>
       <c r="G14" s="51" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="H14" s="52">
-        <v>42065</v>
+        <v>41932</v>
       </c>
       <c r="I14" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="J14" s="51">
-        <v>12611021002</v>
-      </c>
-      <c r="K14" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L14" s="62"/>
+        <v>140</v>
+      </c>
+      <c r="J14" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="54">
+        <v>47246</v>
+      </c>
       <c r="M14" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="O14" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q14" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="R14" s="53" t="s">
-        <v>191</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="N14" s="50"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="53"/>
       <c r="S14" s="51"/>
-      <c r="T14" s="51"/>
+      <c r="T14" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U14" s="51"/>
     </row>
-    <row r="15" spans="2:21" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B15" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="51" t="s">
+    <row r="15" spans="2:21" s="60" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B15" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="62"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="J15" s="48">
+        <v>7131491008</v>
+      </c>
+      <c r="K15" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="62"/>
+      <c r="M15" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="N15" s="47"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="U15" s="48"/>
+    </row>
+    <row r="16" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B16" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="51" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51" t="s">
+      <c r="D16" s="51"/>
+      <c r="E16" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="51" t="s">
+      <c r="F16" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G15" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="H15" s="52">
-        <v>45387</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="J15" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="K15" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="L15" s="54">
-        <v>46315</v>
-      </c>
-      <c r="M15" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="50"/>
-      <c r="O15" s="51"/>
-      <c r="P15" s="51"/>
-      <c r="Q15" s="51"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="51"/>
-      <c r="T15" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U15" s="51"/>
-    </row>
-    <row r="16" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B16" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G16" s="62"/>
-      <c r="H16" s="59"/>
+      <c r="G16" s="51" t="s">
+        <v>107</v>
+      </c>
+      <c r="H16" s="52">
+        <v>43179</v>
+      </c>
       <c r="I16" s="50" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="J16" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K16" s="67" t="s">
-        <v>170</v>
+        <v>15242251005</v>
+      </c>
+      <c r="K16" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="L16" s="62"/>
       <c r="M16" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="50" t="s">
-        <v>123</v>
-      </c>
-      <c r="O16" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P16" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q16" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="R16" s="52">
-        <v>46790</v>
-      </c>
+      <c r="N16" s="50"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="53"/>
       <c r="S16" s="51"/>
-      <c r="T16" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T16" s="51"/>
       <c r="U16" s="51"/>
     </row>
     <row r="17" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="50" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="C17" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="51"/>
+        <v>188</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>189</v>
+      </c>
       <c r="E17" s="51" t="s">
         <v>94</v>
       </c>
@@ -2732,43 +2779,51 @@
         <v>100</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>109</v>
+        <v>185</v>
       </c>
       <c r="H17" s="52">
-        <v>43284</v>
+        <v>42065</v>
       </c>
       <c r="I17" s="50" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="J17" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K17" s="51" t="s">
-        <v>169</v>
+        <v>12611021002</v>
+      </c>
+      <c r="K17" s="67" t="s">
+        <v>170</v>
       </c>
       <c r="L17" s="62"/>
       <c r="M17" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="50"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="53"/>
+      <c r="N17" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="O17" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" s="51" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q17" s="51" t="s">
+        <v>190</v>
+      </c>
+      <c r="R17" s="53" t="s">
+        <v>191</v>
+      </c>
       <c r="S17" s="51"/>
       <c r="T17" s="51"/>
       <c r="U17" s="51"/>
     </row>
     <row r="18" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B18" s="50" t="s">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>175</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D18" s="51"/>
       <c r="E18" s="51" t="s">
         <v>94</v>
       </c>
@@ -2776,109 +2831,97 @@
         <v>100</v>
       </c>
       <c r="G18" s="51" t="s">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="H18" s="52">
-        <v>45084</v>
+        <v>45387</v>
       </c>
       <c r="I18" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="J18" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="K18" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="L18" s="54">
+        <v>46315</v>
+      </c>
+      <c r="M18" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="50"/>
+      <c r="O18" s="51"/>
+      <c r="P18" s="51"/>
+      <c r="Q18" s="51"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="51"/>
+      <c r="T18" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U18" s="51"/>
+    </row>
+    <row r="19" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B19" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="62"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="51">
+      <c r="J19" s="51">
         <v>13068821001</v>
       </c>
-      <c r="K18" s="67" t="s">
+      <c r="K19" s="67" t="s">
         <v>170</v>
-      </c>
-      <c r="L18" s="69"/>
-      <c r="M18" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N18" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="O18" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P18" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q18" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="R18" s="52">
-        <v>46568</v>
-      </c>
-      <c r="S18" s="51"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="51"/>
-    </row>
-    <row r="19" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B19" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="H19" s="52">
-        <v>41404</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="J19" s="51">
-        <v>12578741006</v>
-      </c>
-      <c r="K19" s="67" t="s">
-        <v>169</v>
       </c>
       <c r="L19" s="62"/>
       <c r="M19" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="O19" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="P19" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q19" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="R19" s="55">
-        <v>44044</v>
-      </c>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43" t="s">
+      <c r="N19" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="O19" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P19" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q19" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="R19" s="52">
+        <v>46790</v>
+      </c>
+      <c r="S19" s="51"/>
+      <c r="T19" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="U19" s="43"/>
+      <c r="U19" s="51"/>
     </row>
     <row r="20" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="50" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>77</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="D20" s="51"/>
       <c r="E20" s="51" t="s">
         <v>94</v>
       </c>
@@ -2886,384 +2929,378 @@
         <v>100</v>
       </c>
       <c r="G20" s="51" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="H20" s="52">
-        <v>42809</v>
+        <v>43284</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="J20" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K20" s="67" t="s">
-        <v>170</v>
+        <v>15242251005</v>
+      </c>
+      <c r="K20" s="51" t="s">
+        <v>169</v>
       </c>
       <c r="L20" s="62"/>
       <c r="M20" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="O20" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P20" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q20" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="R20" s="52">
-        <v>46766</v>
-      </c>
+      <c r="N20" s="50"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="53"/>
       <c r="S20" s="51"/>
-      <c r="T20" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T20" s="51"/>
       <c r="U20" s="51"/>
     </row>
-    <row r="21" spans="1:21" s="65" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B21" s="50" t="s">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="D21" s="51" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="F21" s="51" t="s">
         <v>100</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="H21" s="52">
-        <v>42423</v>
-      </c>
-      <c r="I21" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="J21" s="48">
-        <v>7988341009</v>
-      </c>
-      <c r="K21" s="68" t="s">
-        <v>193</v>
-      </c>
-      <c r="L21" s="62"/>
-      <c r="M21" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="N21" s="50"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="53"/>
+        <v>45084</v>
+      </c>
+      <c r="I21" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K21" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L21" s="69"/>
+      <c r="M21" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="O21" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P21" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q21" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="R21" s="52">
+        <v>46568</v>
+      </c>
       <c r="S21" s="51"/>
       <c r="T21" s="51"/>
       <c r="U21" s="51"/>
     </row>
     <row r="22" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B22" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="48" t="s">
+      <c r="B22" s="50" t="s">
+        <v>92</v>
+      </c>
+      <c r="C22" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48" t="s">
+      <c r="D22" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G22" s="62"/>
-      <c r="H22" s="59"/>
+      <c r="F22" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="52">
+        <v>41404</v>
+      </c>
       <c r="I22" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="J22" s="51">
+        <v>12578741006</v>
+      </c>
+      <c r="K22" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="L22" s="62"/>
+      <c r="M22" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="O22" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="P22" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q22" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="R22" s="55">
+        <v>44044</v>
+      </c>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="U22" s="43"/>
+    </row>
+    <row r="23" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B23" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="52">
+        <v>42809</v>
+      </c>
+      <c r="I23" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J23" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K23" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L23" s="62"/>
+      <c r="M23" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="J22" s="51" t="s">
+      <c r="O23" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" s="51" t="s">
         <v>155</v>
       </c>
-      <c r="K22" s="51" t="s">
+      <c r="Q23" s="51" t="s">
         <v>156</v>
       </c>
-      <c r="L22" s="54">
+      <c r="R23" s="52">
         <v>46766</v>
       </c>
-      <c r="M22" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="40"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="63"/>
-      <c r="T22" s="63"/>
-      <c r="U22" s="63"/>
-    </row>
-    <row r="23" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B23" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G23" s="62"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="J23" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="47"/>
-      <c r="O23" s="48"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="48"/>
-      <c r="R23" s="49"/>
-      <c r="S23" s="48"/>
-      <c r="T23" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="U23" s="48"/>
-    </row>
-    <row r="24" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="S23" s="51"/>
+      <c r="T23" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U23" s="51"/>
+    </row>
+    <row r="24" spans="1:21" s="65" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
       <c r="B24" s="50" t="s">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="F24" s="51" t="s">
         <v>100</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="H24" s="52">
-        <v>42426</v>
-      </c>
-      <c r="I24" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J24" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K24" s="67" t="s">
-        <v>170</v>
+        <v>42423</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="J24" s="48">
+        <v>7988341009</v>
+      </c>
+      <c r="K24" s="68" t="s">
+        <v>193</v>
       </c>
       <c r="L24" s="62"/>
-      <c r="M24" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N24" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="O24" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P24" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q24" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="R24" s="52">
-        <v>46854</v>
-      </c>
+      <c r="M24" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="N24" s="50"/>
+      <c r="O24" s="51"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="51"/>
+      <c r="R24" s="53"/>
       <c r="S24" s="51"/>
-      <c r="T24" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T24" s="51"/>
       <c r="U24" s="51"/>
     </row>
     <row r="25" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B25" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="D25" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="51" t="s">
+      <c r="B25" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="51" t="s">
+      <c r="F25" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="62"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L25" s="54">
+        <v>46766</v>
+      </c>
+      <c r="M25" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="40"/>
+      <c r="O25" s="63"/>
+      <c r="P25" s="63"/>
+      <c r="Q25" s="63"/>
+      <c r="R25" s="41"/>
+      <c r="S25" s="63"/>
+      <c r="T25" s="63"/>
+      <c r="U25" s="63"/>
+    </row>
+    <row r="26" spans="1:21" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B26" s="84" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" s="85" t="s">
+        <v>133</v>
+      </c>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="85" t="s">
         <v>100</v>
       </c>
-      <c r="G25" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="H25" s="52">
-        <v>43879</v>
-      </c>
-      <c r="I25" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="J25" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="K25" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="L25" s="54">
-        <v>46594</v>
-      </c>
-      <c r="M25" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" s="50"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="51"/>
-      <c r="R25" s="53"/>
-      <c r="S25" s="51"/>
-      <c r="T25" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U25" s="51"/>
-    </row>
-    <row r="26" spans="1:21" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B26" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="H26" s="52">
-        <v>45648</v>
-      </c>
-      <c r="I26" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J26" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K26" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L26" s="62"/>
-      <c r="M26" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="50"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="53"/>
-      <c r="S26" s="51"/>
-      <c r="T26" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U26" s="51"/>
+      <c r="G26" s="85" t="s">
+        <v>232</v>
+      </c>
+      <c r="H26" s="86"/>
+      <c r="I26" s="84" t="s">
+        <v>231</v>
+      </c>
+      <c r="J26" s="85">
+        <v>11767131003</v>
+      </c>
+      <c r="K26" s="85"/>
+      <c r="L26" s="85"/>
+      <c r="M26" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="84"/>
+      <c r="O26" s="85"/>
+      <c r="P26" s="85"/>
+      <c r="Q26" s="85"/>
+      <c r="R26" s="86"/>
+      <c r="S26" s="85"/>
+      <c r="T26" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U26" s="85"/>
     </row>
     <row r="27" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="57"/>
-      <c r="B27" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="51" t="s">
+      <c r="B27" s="85" t="s">
+        <v>204</v>
+      </c>
+      <c r="C27" s="85" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" s="85" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="85" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="G27" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="H27" s="87">
+        <v>41592</v>
+      </c>
+      <c r="I27" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="J27" s="85" t="s">
+        <v>211</v>
+      </c>
+      <c r="K27" s="85" t="s">
+        <v>213</v>
+      </c>
+      <c r="L27" s="85"/>
+      <c r="M27" s="86" t="s">
+        <v>212</v>
+      </c>
+      <c r="N27" s="85"/>
+      <c r="O27" s="85"/>
+      <c r="P27" s="85"/>
+      <c r="Q27" s="85"/>
+      <c r="R27" s="86"/>
+      <c r="S27" s="85"/>
+      <c r="T27" s="85"/>
+      <c r="U27" s="85"/>
+    </row>
+    <row r="28" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B28" s="47" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="51" t="s">
+      <c r="D28" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="H27" s="52">
-        <v>45412</v>
-      </c>
-      <c r="I27" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="J27" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K27" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L27" s="62"/>
-      <c r="M27" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N27" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="O27" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P27" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q27" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="R27" s="52">
-        <v>46568</v>
-      </c>
-      <c r="S27" s="51"/>
-      <c r="T27" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U27" s="51"/>
-    </row>
-    <row r="28" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B28" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="48"/>
       <c r="E28" s="48" t="s">
         <v>94</v>
       </c>
@@ -3272,37 +3309,37 @@
       </c>
       <c r="G28" s="62"/>
       <c r="H28" s="59"/>
-      <c r="I28" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="J28" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="K28" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="L28" s="54">
-        <v>46766</v>
-      </c>
-      <c r="M28" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="41"/>
-      <c r="S28" s="63"/>
-      <c r="T28" s="63"/>
-      <c r="U28" s="63"/>
+      <c r="I28" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="J28" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="K28" s="83" t="s">
+        <v>216</v>
+      </c>
+      <c r="L28" s="62"/>
+      <c r="M28" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" s="47"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="U28" s="48"/>
     </row>
     <row r="29" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="57"/>
       <c r="B29" s="51" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="D29" s="51" t="s">
         <v>81</v>
@@ -3314,16 +3351,16 @@
         <v>100</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="H29" s="52">
-        <v>44985</v>
+        <v>42426</v>
       </c>
       <c r="I29" s="50" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J29" s="51">
-        <v>11767131003</v>
+        <v>13068821001</v>
       </c>
       <c r="K29" s="67" t="s">
         <v>170</v>
@@ -3332,11 +3369,21 @@
       <c r="M29" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="50"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="53"/>
+      <c r="N29" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="O29" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q29" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="R29" s="52">
+        <v>46854</v>
+      </c>
       <c r="S29" s="51"/>
       <c r="T29" s="51" t="s">
         <v>89</v>
@@ -3345,65 +3392,53 @@
     </row>
     <row r="30" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
-      <c r="B30" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E30" s="51" t="s">
+      <c r="B30" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F30" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="H30" s="52">
-        <v>45979</v>
-      </c>
-      <c r="I30" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="J30" s="51">
-        <v>9075711219</v>
-      </c>
-      <c r="K30" s="72" t="s">
-        <v>169</v>
-      </c>
-      <c r="L30" s="51"/>
-      <c r="M30" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="N30" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="O30" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="P30" s="51">
-        <v>2828850582</v>
-      </c>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="53"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="51"/>
+      <c r="F30" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="J30" s="48">
+        <v>12838081003</v>
+      </c>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48"/>
+      <c r="M30" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="47"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="49"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="U30" s="48"/>
     </row>
     <row r="31" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
       <c r="B31" s="51" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C31" s="51" t="s">
-        <v>98</v>
+        <v>162</v>
       </c>
       <c r="D31" s="51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E31" s="51" t="s">
         <v>94</v>
@@ -3412,33 +3447,29 @@
         <v>100</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="H31" s="52">
-        <v>43584</v>
+        <v>43879</v>
       </c>
       <c r="I31" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J31" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K31" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="L31" s="62"/>
+        <v>164</v>
+      </c>
+      <c r="J31" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="K31" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="L31" s="54">
+        <v>46594</v>
+      </c>
       <c r="M31" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N31" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="O31" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P31" s="51">
-        <v>14119701002</v>
-      </c>
+      <c r="N31" s="50"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="51"/>
       <c r="Q31" s="51"/>
       <c r="R31" s="53"/>
       <c r="S31" s="51"/>
@@ -3449,13 +3480,13 @@
     </row>
     <row r="32" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B32" s="50" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C32" s="51" t="s">
         <v>98</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>94</v>
@@ -3464,19 +3495,19 @@
         <v>100</v>
       </c>
       <c r="G32" s="51" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="H32" s="52">
-        <v>43584</v>
+        <v>45648</v>
       </c>
       <c r="I32" s="50" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="J32" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K32" s="51" t="s">
-        <v>169</v>
+        <v>13068821001</v>
+      </c>
+      <c r="K32" s="67" t="s">
+        <v>170</v>
       </c>
       <c r="L32" s="62"/>
       <c r="M32" s="53" t="s">
@@ -3488,241 +3519,590 @@
       <c r="Q32" s="51"/>
       <c r="R32" s="53"/>
       <c r="S32" s="51"/>
-      <c r="T32" s="51"/>
+      <c r="T32" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U32" s="51"/>
     </row>
     <row r="33" spans="2:21" s="70" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B33" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="45" t="s">
+      <c r="B33" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="51" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45" t="s">
+      <c r="D33" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F33" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" s="62"/>
-      <c r="H33" s="59"/>
+      <c r="F33" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="H33" s="52">
+        <v>45412</v>
+      </c>
       <c r="I33" s="50" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="J33" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="K33" s="51" t="s">
-        <v>168</v>
+        <v>13068821001</v>
+      </c>
+      <c r="K33" s="67" t="s">
+        <v>170</v>
       </c>
       <c r="L33" s="62"/>
       <c r="M33" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N33" s="50"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-      <c r="R33" s="53"/>
+      <c r="N33" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="O33" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q33" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="R33" s="52">
+        <v>46568</v>
+      </c>
       <c r="S33" s="51"/>
-      <c r="T33" s="51"/>
+      <c r="T33" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U33" s="51"/>
     </row>
     <row r="34" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B34" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C34" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="45"/>
-      <c r="E34" s="45" t="s">
+      <c r="B34" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F34" s="45" t="s">
+      <c r="F34" s="48" t="s">
         <v>97</v>
       </c>
       <c r="G34" s="62"/>
       <c r="H34" s="59"/>
       <c r="I34" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="J34" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K34" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L34" s="54">
+        <v>46766</v>
+      </c>
+      <c r="M34" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N34" s="40"/>
+      <c r="O34" s="63"/>
+      <c r="P34" s="63"/>
+      <c r="Q34" s="63"/>
+      <c r="R34" s="41"/>
+      <c r="S34" s="63"/>
+      <c r="T34" s="63"/>
+      <c r="U34" s="63"/>
+    </row>
+    <row r="35" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B35" s="84" t="s">
+        <v>220</v>
+      </c>
+      <c r="C35" s="85" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="85" t="s">
+        <v>230</v>
+      </c>
+      <c r="H35" s="86"/>
+      <c r="I35" s="84" t="s">
+        <v>229</v>
+      </c>
+      <c r="J35" s="85">
+        <v>11432111000</v>
+      </c>
+      <c r="K35" s="85"/>
+      <c r="L35" s="85"/>
+      <c r="M35" s="86" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="84"/>
+      <c r="O35" s="85"/>
+      <c r="P35" s="85"/>
+      <c r="Q35" s="85"/>
+      <c r="R35" s="86"/>
+      <c r="S35" s="85"/>
+      <c r="T35" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="U35" s="85"/>
+    </row>
+    <row r="36" spans="2:21" s="71" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B36" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G36" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H36" s="52">
+        <v>44985</v>
+      </c>
+      <c r="I36" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="J36" s="51">
+        <v>11767131003</v>
+      </c>
+      <c r="K36" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L36" s="62"/>
+      <c r="M36" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" s="50"/>
+      <c r="O36" s="51"/>
+      <c r="P36" s="51"/>
+      <c r="Q36" s="51"/>
+      <c r="R36" s="53"/>
+      <c r="S36" s="51"/>
+      <c r="T36" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U36" s="51"/>
+    </row>
+    <row r="37" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B37" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="H37" s="52">
+        <v>45979</v>
+      </c>
+      <c r="I37" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="J37" s="51">
+        <v>9075711219</v>
+      </c>
+      <c r="K37" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="L37" s="51"/>
+      <c r="M37" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="N37" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="O37" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="P37" s="51">
+        <v>2828850582</v>
+      </c>
+      <c r="Q37" s="51"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="51"/>
+      <c r="T37" s="51"/>
+      <c r="U37" s="51"/>
+    </row>
+    <row r="38" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B38" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" s="52">
+        <v>43584</v>
+      </c>
+      <c r="I38" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="J34" s="51">
+      <c r="J38" s="51">
         <v>15242251005</v>
       </c>
-      <c r="K34" s="51" t="s">
+      <c r="K38" s="67" t="s">
         <v>169</v>
       </c>
-      <c r="L34" s="62"/>
-      <c r="M34" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N34" s="50"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="51"/>
-      <c r="R34" s="53"/>
-      <c r="S34" s="51"/>
-      <c r="T34" s="51"/>
-      <c r="U34" s="51"/>
-    </row>
-    <row r="35" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B35" s="50" t="s">
+      <c r="L38" s="62"/>
+      <c r="M38" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="O38" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="Q38" s="51"/>
+      <c r="R38" s="53"/>
+      <c r="S38" s="51"/>
+      <c r="T38" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U38" s="51"/>
+    </row>
+    <row r="39" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B39" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" s="52">
+        <v>43584</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J39" s="51">
+        <v>15242251005</v>
+      </c>
+      <c r="K39" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L39" s="62"/>
+      <c r="M39" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" s="50"/>
+      <c r="O39" s="51"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="51"/>
+      <c r="R39" s="53"/>
+      <c r="S39" s="51"/>
+      <c r="T39" s="51"/>
+      <c r="U39" s="51"/>
+    </row>
+    <row r="40" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B40" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G40" s="62"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="J40" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="K40" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="L40" s="62"/>
+      <c r="M40" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" s="50"/>
+      <c r="O40" s="51"/>
+      <c r="P40" s="51"/>
+      <c r="Q40" s="51"/>
+      <c r="R40" s="53"/>
+      <c r="S40" s="51"/>
+      <c r="T40" s="51"/>
+      <c r="U40" s="51"/>
+    </row>
+    <row r="41" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B41" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="45"/>
+      <c r="E41" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G41" s="62"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J41" s="51">
+        <v>15242251005</v>
+      </c>
+      <c r="K41" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L41" s="62"/>
+      <c r="M41" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" s="50"/>
+      <c r="O41" s="51"/>
+      <c r="P41" s="51"/>
+      <c r="Q41" s="51"/>
+      <c r="R41" s="53"/>
+      <c r="S41" s="51"/>
+      <c r="T41" s="51"/>
+      <c r="U41" s="51"/>
+    </row>
+    <row r="42" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B42" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C42" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D42" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="E35" s="51" t="s">
+      <c r="E42" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="51" t="s">
+      <c r="F42" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G35" s="51" t="s">
+      <c r="G42" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="H35" s="52">
+      <c r="H42" s="52">
         <v>45909</v>
       </c>
-      <c r="I35" s="50" t="s">
+      <c r="I42" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="J35" s="51">
+      <c r="J42" s="51">
         <v>13068821001</v>
       </c>
-      <c r="K35" s="67" t="s">
+      <c r="K42" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="L35" s="62"/>
-      <c r="M35" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N35" s="50" t="s">
+      <c r="L42" s="62"/>
+      <c r="M42" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N42" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="O35" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P35" s="51" t="s">
+      <c r="O42" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="Q35" s="51" t="s">
+      <c r="Q42" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="R35" s="52">
+      <c r="R42" s="52">
         <v>47469</v>
       </c>
-      <c r="S35" s="51"/>
-      <c r="T35" s="51" t="s">
+      <c r="S42" s="51"/>
+      <c r="T42" s="51" t="s">
         <v>89</v>
       </c>
-      <c r="U35" s="51"/>
-    </row>
-    <row r="36" spans="2:21" s="71" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="C36" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="D36" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="E36" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G36" s="48"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="47" t="s">
-        <v>214</v>
-      </c>
-      <c r="J36" s="48" t="s">
-        <v>205</v>
-      </c>
-      <c r="K36" s="48"/>
-      <c r="L36" s="48"/>
-      <c r="M36" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="N36" s="47"/>
-      <c r="O36" s="48"/>
-      <c r="P36" s="48"/>
-      <c r="Q36" s="48"/>
-      <c r="R36" s="49"/>
-      <c r="S36" s="48"/>
-      <c r="T36" s="48"/>
-      <c r="U36" s="48"/>
-    </row>
-    <row r="37" spans="2:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="B37" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="C37" s="63" t="s">
-        <v>207</v>
-      </c>
-      <c r="D37" s="63" t="s">
-        <v>208</v>
-      </c>
-      <c r="E37" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="G37" s="63" t="s">
-        <v>209</v>
-      </c>
-      <c r="H37" s="82">
-        <v>41592</v>
-      </c>
-      <c r="I37" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="J37" s="63" t="s">
-        <v>211</v>
-      </c>
-      <c r="K37" s="63" t="s">
-        <v>213</v>
-      </c>
-      <c r="M37" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="N37" s="40"/>
-      <c r="O37" s="63"/>
-      <c r="P37" s="63"/>
-      <c r="Q37" s="63"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="63"/>
-      <c r="T37" s="63"/>
-      <c r="U37" s="63"/>
-    </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B38" s="40"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="63"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="40"/>
-      <c r="J38" s="63"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="40"/>
-      <c r="O38" s="63"/>
-      <c r="P38" s="63"/>
-      <c r="Q38" s="63"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="63"/>
-      <c r="T38" s="63"/>
-      <c r="U38" s="63"/>
+      <c r="U42" s="51"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B43" s="40"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
+      <c r="F43" s="63"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="63"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="40"/>
+      <c r="O43" s="63"/>
+      <c r="P43" s="63"/>
+      <c r="Q43" s="63"/>
+      <c r="R43" s="41"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="63"/>
+      <c r="U43" s="63"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B44" s="40"/>
+      <c r="C44" s="63"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
+      <c r="F44" s="63"/>
+      <c r="G44" s="63"/>
+      <c r="H44" s="41"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="63"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="40"/>
+      <c r="O44" s="63"/>
+      <c r="P44" s="63"/>
+      <c r="Q44" s="63"/>
+      <c r="R44" s="41"/>
+      <c r="S44" s="63"/>
+      <c r="T44" s="63"/>
+      <c r="U44" s="63"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B45" s="40"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
+      <c r="F45" s="63"/>
+      <c r="G45" s="63"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="63"/>
+      <c r="M45" s="41"/>
+      <c r="N45" s="40"/>
+      <c r="O45" s="63"/>
+      <c r="P45" s="63"/>
+      <c r="Q45" s="63"/>
+      <c r="R45" s="41"/>
+      <c r="S45" s="63"/>
+      <c r="T45" s="63"/>
+      <c r="U45" s="63"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B46" s="40"/>
+      <c r="C46" s="63"/>
+      <c r="D46" s="63"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="63"/>
+      <c r="G46" s="63"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="63"/>
+      <c r="M46" s="41"/>
+      <c r="N46" s="40"/>
+      <c r="O46" s="63"/>
+      <c r="P46" s="63"/>
+      <c r="Q46" s="63"/>
+      <c r="R46" s="41"/>
+      <c r="S46" s="63"/>
+      <c r="T46" s="63"/>
+      <c r="U46" s="63"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B47" s="40"/>
+      <c r="C47" s="63"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="63"/>
+      <c r="G47" s="63"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="63"/>
+      <c r="M47" s="41"/>
+      <c r="N47" s="40"/>
+      <c r="O47" s="63"/>
+      <c r="P47" s="63"/>
+      <c r="Q47" s="63"/>
+      <c r="R47" s="41"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="63"/>
+      <c r="U47" s="63"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B48" s="40"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="63"/>
+      <c r="M48" s="41"/>
+      <c r="N48" s="40"/>
+      <c r="O48" s="63"/>
+      <c r="P48" s="63"/>
+      <c r="Q48" s="63"/>
+      <c r="R48" s="41"/>
+      <c r="S48" s="63"/>
+      <c r="T48" s="63"/>
+      <c r="U48" s="63"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/prospetto_mezzi.xlsx
+++ b/prospetto_mezzi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Fs-rm073\rm229 - gruppo civitavecchia\6\7\8\1. ATTIVITA' GLOBALE_SERVER\1. SERVIZIO N.C.C. 1 STANZIALE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs-rm073\rm229 - gruppo civitavecchia\6\7\8\1. ATTIVITA' GLOBALE_SERVER\1. SERVIZIO N.C.C. 1 STANZIALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E03EBC-6284-4336-BACD-426A0ABCE129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC82405-5C1A-4AFE-A0EF-ACB6F0DEA268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
+    <workbookView xWindow="28680" yWindow="1740" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="254">
   <si>
     <t>EL706PT</t>
   </si>
@@ -739,6 +739,69 @@
   </si>
   <si>
     <t xml:space="preserve">LIC.28 COMUNE TREVI    </t>
+  </si>
+  <si>
+    <t>GM237RK</t>
+  </si>
+  <si>
+    <t>HB570PH</t>
+  </si>
+  <si>
+    <t>FM268AC</t>
+  </si>
+  <si>
+    <t>GZ015GP</t>
+  </si>
+  <si>
+    <t>DP769PH</t>
+  </si>
+  <si>
+    <t>GV964PL</t>
+  </si>
+  <si>
+    <t>DR147HX</t>
+  </si>
+  <si>
+    <t>S.O.S. SERVIZI ORGANIZZAZIONE SPETTACOLI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC9 COMUNE LICENZA   </t>
+  </si>
+  <si>
+    <t>MERCEDES V-KLASSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC1 COMUNE ROCCA SINIBALDA    </t>
+  </si>
+  <si>
+    <t>TRANSFER IN ROME SOC. COP</t>
+  </si>
+  <si>
+    <t>MORLUPO</t>
+  </si>
+  <si>
+    <t>TOMANOL SRL</t>
+  </si>
+  <si>
+    <t>FORD TOURNEO CUSTOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC3325 COMUNE NAPOLI      </t>
+  </si>
+  <si>
+    <t>DELLA PENNA AUTOTRASPORTI SPA</t>
+  </si>
+  <si>
+    <t>CIVITATOURS SRL</t>
+  </si>
+  <si>
+    <t>TOYOTA V</t>
+  </si>
+  <si>
+    <t>IANNI CECILIA</t>
+  </si>
+  <si>
+    <t>NNICCL69C62H501A</t>
   </si>
 </sst>
 </file>
@@ -970,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1173,6 +1236,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1198,24 +1285,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="14" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1452,10 +1521,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U48" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="B4:U48" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:U48">
-    <sortCondition ref="B4:B48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U66" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="B4:U66" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:U66">
+    <sortCondition ref="B4:B66"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="2" xr3:uid="{779EAAEE-59A7-446B-AD7C-6F7003AD1695}" name="TARGA" dataDxfId="19"/>
@@ -1833,7 +1902,7 @@
     <row r="10" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D11" s="1"/>
-      <c r="E11" s="74" t="s">
+      <c r="E11" s="82" t="s">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -1854,7 +1923,7 @@
     </row>
     <row r="12" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D12" s="5"/>
-      <c r="E12" s="75"/>
+      <c r="E12" s="83"/>
       <c r="F12" s="14" t="s">
         <v>15</v>
       </c>
@@ -1869,7 +1938,7 @@
     </row>
     <row r="13" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="3"/>
-      <c r="E13" s="76"/>
+      <c r="E13" s="84"/>
       <c r="F13" s="17"/>
       <c r="G13" s="18" t="s">
         <v>14</v>
@@ -1882,7 +1951,7 @@
     </row>
     <row r="14" spans="4:10" ht="150" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="85" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="29" t="s">
@@ -1903,7 +1972,7 @@
     </row>
     <row r="15" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
-      <c r="E15" s="78"/>
+      <c r="E15" s="86"/>
       <c r="F15" s="31" t="s">
         <v>19</v>
       </c>
@@ -1920,7 +1989,7 @@
     </row>
     <row r="16" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D16" s="3"/>
-      <c r="E16" s="79"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="34"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
@@ -1931,7 +2000,7 @@
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
-      <c r="E17" s="80" t="s">
+      <c r="E17" s="88" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="11" t="s">
@@ -1948,7 +2017,7 @@
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
-      <c r="E18" s="81"/>
+      <c r="E18" s="89"/>
       <c r="F18" s="14" t="s">
         <v>19</v>
       </c>
@@ -1961,7 +2030,7 @@
     </row>
     <row r="19" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D19" s="3"/>
-      <c r="E19" s="82"/>
+      <c r="E19" s="90"/>
       <c r="F19" s="17"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
@@ -2163,7 +2232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56392095-0261-4957-A1EF-F42F71E397DD}">
-  <dimension ref="A3:U48"/>
+  <dimension ref="A3:U66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="61"/>
@@ -2289,44 +2358,44 @@
       <c r="U5" s="48"/>
     </row>
     <row r="6" spans="2:21" s="64" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B6" s="84" t="s">
+      <c r="B6" s="75" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="85" t="s">
+      <c r="C6" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="85" t="s">
+      <c r="D6" s="76"/>
+      <c r="E6" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="85" t="s">
+      <c r="G6" s="76" t="s">
         <v>228</v>
       </c>
-      <c r="H6" s="86"/>
-      <c r="I6" s="84" t="s">
+      <c r="H6" s="77"/>
+      <c r="I6" s="75" t="s">
         <v>227</v>
       </c>
-      <c r="J6" s="85">
+      <c r="J6" s="76">
         <v>12838081003</v>
       </c>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="86" t="s">
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="84"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="85"/>
-      <c r="Q6" s="85"/>
-      <c r="R6" s="86"/>
-      <c r="S6" s="85"/>
-      <c r="T6" s="85" t="s">
+      <c r="N6" s="75"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="77"/>
+      <c r="S6" s="76"/>
+      <c r="T6" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="U6" s="85"/>
+      <c r="U6" s="76"/>
     </row>
     <row r="7" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B7" s="47" t="s">
@@ -2384,17 +2453,17 @@
       </c>
       <c r="G8" s="48"/>
       <c r="H8" s="49"/>
-      <c r="I8" s="84" t="s">
+      <c r="I8" s="75" t="s">
         <v>222</v>
       </c>
-      <c r="J8" s="85" t="s">
+      <c r="J8" s="76" t="s">
         <v>223</v>
       </c>
-      <c r="K8" s="85" t="s">
+      <c r="K8" s="76" t="s">
         <v>225</v>
       </c>
-      <c r="L8" s="85"/>
-      <c r="M8" s="86" t="s">
+      <c r="L8" s="76"/>
+      <c r="M8" s="77" t="s">
         <v>224</v>
       </c>
       <c r="N8" s="47"/>
@@ -2446,107 +2515,87 @@
       <c r="T9" s="45"/>
       <c r="U9" s="45"/>
     </row>
-    <row r="10" spans="2:21" s="65" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="B10" s="50" t="s">
+    <row r="10" spans="2:21" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B10" s="40" t="s">
+        <v>237</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="63"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="J10" s="63">
+        <v>14699681004</v>
+      </c>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="40"/>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="63"/>
+      <c r="R10" s="41"/>
+      <c r="S10" s="63"/>
+      <c r="T10" s="63"/>
+      <c r="U10" s="63"/>
+    </row>
+    <row r="11" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="48"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="J11" s="48" t="s">
+        <v>253</v>
+      </c>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="47"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+    </row>
+    <row r="12" spans="2:21" s="65" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="B12" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C12" s="51" t="s">
         <v>176</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="D12" s="51" t="s">
         <v>175</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="H10" s="52">
-        <v>45787</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J10" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K10" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="L10" s="62"/>
-      <c r="M10" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="50" t="s">
-        <v>178</v>
-      </c>
-      <c r="O10" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q10" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="R10" s="52">
-        <v>47200</v>
-      </c>
-      <c r="S10" s="51"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="51"/>
-    </row>
-    <row r="11" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="44" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="45"/>
-      <c r="E11" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="62"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="J11" s="45">
-        <v>15242251005</v>
-      </c>
-      <c r="K11" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="L11" s="62"/>
-      <c r="M11" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="44"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="45"/>
-      <c r="T11" s="45"/>
-      <c r="U11" s="45"/>
-    </row>
-    <row r="12" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B12" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>77</v>
       </c>
       <c r="E12" s="51" t="s">
         <v>94</v>
@@ -2555,18 +2604,18 @@
         <v>100</v>
       </c>
       <c r="G12" s="51" t="s">
-        <v>115</v>
+        <v>177</v>
       </c>
       <c r="H12" s="52">
-        <v>40497</v>
+        <v>45787</v>
       </c>
       <c r="I12" s="50" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J12" s="51">
-        <v>12611021002</v>
-      </c>
-      <c r="K12" s="67" t="s">
+        <v>13068821001</v>
+      </c>
+      <c r="K12" s="51" t="s">
         <v>170</v>
       </c>
       <c r="L12" s="62"/>
@@ -2574,71 +2623,71 @@
         <v>22</v>
       </c>
       <c r="N12" s="50" t="s">
-        <v>116</v>
+        <v>178</v>
       </c>
       <c r="O12" s="51" t="s">
         <v>22</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>117</v>
+        <v>179</v>
       </c>
       <c r="Q12" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="R12" s="53"/>
+        <v>180</v>
+      </c>
+      <c r="R12" s="52">
+        <v>47200</v>
+      </c>
       <c r="S12" s="51"/>
-      <c r="T12" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T12" s="51"/>
       <c r="U12" s="51"/>
     </row>
     <row r="13" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B13" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51" t="s">
+      <c r="B13" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F13" s="45" t="s">
         <v>97</v>
       </c>
       <c r="G13" s="62"/>
       <c r="H13" s="59"/>
-      <c r="I13" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="J13" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="K13" s="67" t="s">
-        <v>168</v>
+      <c r="I13" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="45">
+        <v>15242251005</v>
+      </c>
+      <c r="K13" s="45" t="s">
+        <v>169</v>
       </c>
       <c r="L13" s="62"/>
-      <c r="M13" s="59" t="s">
+      <c r="M13" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="50"/>
-      <c r="O13" s="51"/>
-      <c r="P13" s="51"/>
-      <c r="Q13" s="51"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="51"/>
-      <c r="T13" s="51"/>
-      <c r="U13" s="51"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="46"/>
+      <c r="S13" s="45"/>
+      <c r="T13" s="45"/>
+      <c r="U13" s="45"/>
     </row>
     <row r="14" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B14" s="50" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" s="51" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E14" s="51" t="s">
         <v>94</v>
@@ -2647,30 +2696,36 @@
         <v>100</v>
       </c>
       <c r="G14" s="51" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="H14" s="52">
-        <v>41932</v>
+        <v>40497</v>
       </c>
       <c r="I14" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="K14" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="L14" s="54">
-        <v>47246</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="J14" s="51">
+        <v>12611021002</v>
+      </c>
+      <c r="K14" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L14" s="62"/>
       <c r="M14" s="53" t="s">
-        <v>143</v>
-      </c>
-      <c r="N14" s="50"/>
-      <c r="O14" s="51"/>
-      <c r="P14" s="51"/>
-      <c r="Q14" s="51"/>
+        <v>22</v>
+      </c>
+      <c r="N14" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="O14" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q14" s="51" t="s">
+        <v>138</v>
+      </c>
       <c r="R14" s="53"/>
       <c r="S14" s="51"/>
       <c r="T14" s="51" t="s">
@@ -2678,56 +2733,54 @@
       </c>
       <c r="U14" s="51"/>
     </row>
-    <row r="15" spans="2:21" s="60" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="47" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="48" t="s">
+    <row r="15" spans="2:21" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="48" t="s">
+      <c r="D15" s="51"/>
+      <c r="E15" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="51" t="s">
         <v>97</v>
       </c>
       <c r="G15" s="62"/>
       <c r="H15" s="59"/>
-      <c r="I15" s="47" t="s">
-        <v>172</v>
-      </c>
-      <c r="J15" s="48">
-        <v>7131491008</v>
-      </c>
-      <c r="K15" s="68" t="s">
-        <v>13</v>
+      <c r="I15" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="J15" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="K15" s="67" t="s">
+        <v>168</v>
       </c>
       <c r="L15" s="62"/>
-      <c r="M15" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="N15" s="47"/>
-      <c r="O15" s="48"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="49"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="48" t="s">
-        <v>89</v>
-      </c>
-      <c r="U15" s="48"/>
+      <c r="M15" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="50"/>
+      <c r="O15" s="51"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="53"/>
+      <c r="S15" s="51"/>
+      <c r="T15" s="51"/>
+      <c r="U15" s="51"/>
     </row>
     <row r="16" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B16" s="50" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="51"/>
+        <v>98</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>85</v>
+      </c>
       <c r="E16" s="51" t="s">
         <v>94</v>
       </c>
@@ -2735,23 +2788,25 @@
         <v>100</v>
       </c>
       <c r="G16" s="51" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="H16" s="52">
-        <v>43179</v>
+        <v>41932</v>
       </c>
       <c r="I16" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J16" s="51">
-        <v>15242251005</v>
+        <v>140</v>
+      </c>
+      <c r="J16" s="51" t="s">
+        <v>141</v>
       </c>
       <c r="K16" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="L16" s="62"/>
+        <v>142</v>
+      </c>
+      <c r="L16" s="54">
+        <v>47246</v>
+      </c>
       <c r="M16" s="53" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="N16" s="50"/>
       <c r="O16" s="51"/>
@@ -2759,66 +2814,56 @@
       <c r="Q16" s="51"/>
       <c r="R16" s="53"/>
       <c r="S16" s="51"/>
-      <c r="T16" s="51"/>
+      <c r="T16" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U16" s="51"/>
     </row>
-    <row r="17" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B17" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="E17" s="51" t="s">
+    <row r="17" spans="1:21" s="65" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B17" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="H17" s="52">
-        <v>42065</v>
-      </c>
-      <c r="I17" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="J17" s="51">
-        <v>12611021002</v>
-      </c>
-      <c r="K17" s="67" t="s">
-        <v>170</v>
+      <c r="F17" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="62"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="J17" s="48">
+        <v>7131491008</v>
+      </c>
+      <c r="K17" s="68" t="s">
+        <v>13</v>
       </c>
       <c r="L17" s="62"/>
-      <c r="M17" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="O17" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P17" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q17" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="R17" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="S17" s="51"/>
-      <c r="T17" s="51"/>
-      <c r="U17" s="51"/>
+      <c r="M17" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="N17" s="47"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="U17" s="48"/>
     </row>
     <row r="18" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B18" s="50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C18" s="51" t="s">
         <v>106</v>
@@ -2831,23 +2876,21 @@
         <v>100</v>
       </c>
       <c r="G18" s="51" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="H18" s="52">
-        <v>45387</v>
+        <v>43179</v>
       </c>
       <c r="I18" s="50" t="s">
-        <v>111</v>
-      </c>
-      <c r="J18" s="51" t="s">
-        <v>112</v>
+        <v>78</v>
+      </c>
+      <c r="J18" s="51">
+        <v>15242251005</v>
       </c>
       <c r="K18" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="L18" s="54">
-        <v>46315</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="L18" s="62"/>
       <c r="M18" s="53" t="s">
         <v>22</v>
       </c>
@@ -2857,34 +2900,36 @@
       <c r="Q18" s="51"/>
       <c r="R18" s="53"/>
       <c r="S18" s="51"/>
-      <c r="T18" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T18" s="51"/>
       <c r="U18" s="51"/>
     </row>
     <row r="19" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B19" s="44" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="45" t="s">
+      <c r="B19" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="E19" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="62"/>
-      <c r="H19" s="59"/>
+      <c r="F19" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>185</v>
+      </c>
+      <c r="H19" s="52">
+        <v>42065</v>
+      </c>
       <c r="I19" s="50" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J19" s="51">
-        <v>13068821001</v>
+        <v>12611021002</v>
       </c>
       <c r="K19" s="67" t="s">
         <v>170</v>
@@ -2894,32 +2939,30 @@
         <v>22</v>
       </c>
       <c r="N19" s="50" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="O19" s="51" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="51" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="Q19" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="R19" s="52">
-        <v>46790</v>
+        <v>190</v>
+      </c>
+      <c r="R19" s="53" t="s">
+        <v>191</v>
       </c>
       <c r="S19" s="51"/>
-      <c r="T19" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T19" s="51"/>
       <c r="U19" s="51"/>
     </row>
     <row r="20" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D20" s="51"/>
       <c r="E20" s="51" t="s">
@@ -2929,21 +2972,23 @@
         <v>100</v>
       </c>
       <c r="G20" s="51" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H20" s="52">
-        <v>43284</v>
+        <v>45387</v>
       </c>
       <c r="I20" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J20" s="51">
-        <v>15242251005</v>
+        <v>111</v>
+      </c>
+      <c r="J20" s="51" t="s">
+        <v>112</v>
       </c>
       <c r="K20" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="L20" s="62"/>
+        <v>131</v>
+      </c>
+      <c r="L20" s="54">
+        <v>46315</v>
+      </c>
       <c r="M20" s="53" t="s">
         <v>22</v>
       </c>
@@ -2953,31 +2998,29 @@
       <c r="Q20" s="51"/>
       <c r="R20" s="53"/>
       <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
+      <c r="T20" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U20" s="51"/>
     </row>
     <row r="21" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B21" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="E21" s="51" t="s">
+      <c r="B21" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="45" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G21" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="H21" s="52">
-        <v>45084</v>
-      </c>
+      <c r="F21" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="62"/>
+      <c r="H21" s="59"/>
       <c r="I21" s="50" t="s">
         <v>122</v>
       </c>
@@ -2987,39 +3030,39 @@
       <c r="K21" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="L21" s="69"/>
+      <c r="L21" s="62"/>
       <c r="M21" s="53" t="s">
         <v>22</v>
       </c>
       <c r="N21" s="50" t="s">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="O21" s="51" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="51" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="Q21" s="51" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="R21" s="52">
-        <v>46568</v>
+        <v>46790</v>
       </c>
       <c r="S21" s="51"/>
-      <c r="T21" s="51"/>
+      <c r="T21" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U21" s="51"/>
     </row>
     <row r="22" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" s="50" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D22" s="51" t="s">
-        <v>81</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="D22" s="51"/>
       <c r="E22" s="51" t="s">
         <v>94</v>
       </c>
@@ -3027,54 +3070,42 @@
         <v>100</v>
       </c>
       <c r="G22" s="51" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="H22" s="52">
-        <v>41404</v>
+        <v>43284</v>
       </c>
       <c r="I22" s="50" t="s">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="J22" s="51">
-        <v>12578741006</v>
-      </c>
-      <c r="K22" s="67" t="s">
+        <v>15242251005</v>
+      </c>
+      <c r="K22" s="51" t="s">
         <v>169</v>
       </c>
       <c r="L22" s="62"/>
       <c r="M22" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N22" s="42" t="s">
-        <v>159</v>
-      </c>
-      <c r="O22" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="P22" s="43" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q22" s="43" t="s">
-        <v>161</v>
-      </c>
-      <c r="R22" s="55">
-        <v>44044</v>
-      </c>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="U22" s="43"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="51"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="51"/>
+      <c r="R22" s="53"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="51"/>
+      <c r="U22" s="51"/>
     </row>
     <row r="23" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B23" s="50" t="s">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="C23" s="51" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="D23" s="51" t="s">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="E23" s="51" t="s">
         <v>94</v>
@@ -3083,10 +3114,10 @@
         <v>100</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="H23" s="52">
-        <v>42809</v>
+        <v>45084</v>
       </c>
       <c r="I23" s="50" t="s">
         <v>122</v>
@@ -3097,396 +3128,400 @@
       <c r="K23" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="L23" s="62"/>
+      <c r="L23" s="69"/>
       <c r="M23" s="53" t="s">
         <v>22</v>
       </c>
       <c r="N23" s="50" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="O23" s="51" t="s">
         <v>22</v>
       </c>
       <c r="P23" s="51" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="Q23" s="51" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="R23" s="52">
-        <v>46766</v>
+        <v>46568</v>
       </c>
       <c r="S23" s="51"/>
-      <c r="T23" s="51" t="s">
-        <v>89</v>
-      </c>
+      <c r="T23" s="51"/>
       <c r="U23" s="51"/>
     </row>
-    <row r="24" spans="1:21" s="65" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B24" s="50" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="C24" s="51" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="D24" s="51" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E24" s="51" t="s">
-        <v>182</v>
+        <v>94</v>
       </c>
       <c r="F24" s="51" t="s">
         <v>100</v>
       </c>
       <c r="G24" s="51" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="H24" s="52">
-        <v>42423</v>
-      </c>
-      <c r="I24" s="47" t="s">
-        <v>184</v>
-      </c>
-      <c r="J24" s="48">
-        <v>7988341009</v>
-      </c>
-      <c r="K24" s="68" t="s">
-        <v>193</v>
+        <v>41404</v>
+      </c>
+      <c r="I24" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="J24" s="51">
+        <v>12578741006</v>
+      </c>
+      <c r="K24" s="67" t="s">
+        <v>169</v>
       </c>
       <c r="L24" s="62"/>
-      <c r="M24" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="N24" s="50"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="51"/>
-      <c r="R24" s="53"/>
-      <c r="S24" s="51"/>
-      <c r="T24" s="51"/>
-      <c r="U24" s="51"/>
+      <c r="M24" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="42" t="s">
+        <v>159</v>
+      </c>
+      <c r="O24" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" s="43" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q24" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="R24" s="55">
+        <v>44044</v>
+      </c>
+      <c r="S24" s="43"/>
+      <c r="T24" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="U24" s="43"/>
     </row>
     <row r="25" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B25" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48" t="s">
+      <c r="B25" s="50" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="62"/>
-      <c r="H25" s="59"/>
+      <c r="F25" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="52">
+        <v>42809</v>
+      </c>
       <c r="I25" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="J25" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="L25" s="54">
-        <v>46766</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J25" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K25" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L25" s="62"/>
       <c r="M25" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N25" s="40"/>
-      <c r="O25" s="63"/>
-      <c r="P25" s="63"/>
-      <c r="Q25" s="63"/>
-      <c r="R25" s="41"/>
-      <c r="S25" s="63"/>
-      <c r="T25" s="63"/>
-      <c r="U25" s="63"/>
-    </row>
-    <row r="26" spans="1:21" s="60" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B26" s="84" t="s">
-        <v>221</v>
-      </c>
-      <c r="C26" s="85" t="s">
-        <v>133</v>
-      </c>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="85" t="s">
+      <c r="N25" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="O25" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q25" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="R25" s="52">
+        <v>46766</v>
+      </c>
+      <c r="S25" s="51"/>
+      <c r="T25" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U25" s="51"/>
+    </row>
+    <row r="26" spans="1:21" s="60" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="B26" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="51" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G26" s="85" t="s">
-        <v>232</v>
-      </c>
-      <c r="H26" s="86"/>
-      <c r="I26" s="84" t="s">
-        <v>231</v>
-      </c>
-      <c r="J26" s="85">
-        <v>11767131003</v>
-      </c>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="84"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="85"/>
-      <c r="R26" s="86"/>
-      <c r="S26" s="85"/>
-      <c r="T26" s="85" t="s">
-        <v>76</v>
-      </c>
-      <c r="U26" s="85"/>
+      <c r="G26" s="51" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="52">
+        <v>42423</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>184</v>
+      </c>
+      <c r="J26" s="48">
+        <v>7988341009</v>
+      </c>
+      <c r="K26" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="L26" s="62"/>
+      <c r="M26" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="N26" s="50"/>
+      <c r="O26" s="51"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="51"/>
+      <c r="R26" s="53"/>
+      <c r="S26" s="51"/>
+      <c r="T26" s="51"/>
+      <c r="U26" s="51"/>
     </row>
     <row r="27" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="57"/>
-      <c r="B27" s="85" t="s">
-        <v>204</v>
-      </c>
-      <c r="C27" s="85" t="s">
-        <v>207</v>
-      </c>
-      <c r="D27" s="85" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="85" t="s">
+      <c r="B27" s="80" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="85" t="s">
+      <c r="F27" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G27" s="62"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="J27" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K27" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" s="54">
+        <v>46766</v>
+      </c>
+      <c r="M27" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="63"/>
+      <c r="O27" s="63"/>
+      <c r="P27" s="63"/>
+      <c r="Q27" s="63"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="63"/>
+      <c r="T27" s="63"/>
+      <c r="U27" s="63"/>
+    </row>
+    <row r="28" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B28" s="75" t="s">
+        <v>221</v>
+      </c>
+      <c r="C28" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G27" s="85" t="s">
-        <v>209</v>
-      </c>
-      <c r="H27" s="87">
-        <v>41592</v>
-      </c>
-      <c r="I27" s="85" t="s">
-        <v>210</v>
-      </c>
-      <c r="J27" s="85" t="s">
-        <v>211</v>
-      </c>
-      <c r="K27" s="85" t="s">
-        <v>213</v>
-      </c>
-      <c r="L27" s="85"/>
-      <c r="M27" s="86" t="s">
-        <v>212</v>
-      </c>
-      <c r="N27" s="85"/>
-      <c r="O27" s="85"/>
-      <c r="P27" s="85"/>
-      <c r="Q27" s="85"/>
-      <c r="R27" s="86"/>
-      <c r="S27" s="85"/>
-      <c r="T27" s="85"/>
-      <c r="U27" s="85"/>
-    </row>
-    <row r="28" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B28" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="D28" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="62"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="J28" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="K28" s="83" t="s">
-        <v>216</v>
-      </c>
-      <c r="L28" s="62"/>
-      <c r="M28" s="49" t="s">
+      <c r="G28" s="76" t="s">
+        <v>232</v>
+      </c>
+      <c r="H28" s="77"/>
+      <c r="I28" s="75" t="s">
+        <v>231</v>
+      </c>
+      <c r="J28" s="76">
+        <v>11767131003</v>
+      </c>
+      <c r="K28" s="76"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="N28" s="47"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48" t="s">
+      <c r="N28" s="75"/>
+      <c r="O28" s="76"/>
+      <c r="P28" s="76"/>
+      <c r="Q28" s="76"/>
+      <c r="R28" s="77"/>
+      <c r="S28" s="76"/>
+      <c r="T28" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="U28" s="48"/>
+      <c r="U28" s="76"/>
     </row>
     <row r="29" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="57"/>
-      <c r="B29" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D29" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="51" t="s">
+      <c r="B29" s="48" t="s">
+        <v>235</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F29" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="H29" s="52">
-        <v>42426</v>
-      </c>
-      <c r="I29" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J29" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K29" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L29" s="62"/>
-      <c r="M29" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N29" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="O29" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P29" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q29" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="R29" s="52">
-        <v>46854</v>
-      </c>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U29" s="51"/>
+      <c r="F29" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G29" s="48"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="J29" s="48">
+        <v>17833641008</v>
+      </c>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="N29" s="47"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="48"/>
     </row>
     <row r="30" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
-      <c r="B30" s="48" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="48" t="s">
-        <v>226</v>
-      </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48" t="s">
+      <c r="B30" s="76" t="s">
+        <v>204</v>
+      </c>
+      <c r="C30" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="D30" s="76" t="s">
+        <v>208</v>
+      </c>
+      <c r="E30" s="76" t="s">
         <v>94</v>
       </c>
-      <c r="F30" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="48"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="J30" s="48">
-        <v>12838081003</v>
-      </c>
-      <c r="K30" s="48"/>
-      <c r="L30" s="48"/>
-      <c r="M30" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="N30" s="47"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="48"/>
-      <c r="T30" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="U30" s="48"/>
+      <c r="F30" s="76" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" s="76" t="s">
+        <v>209</v>
+      </c>
+      <c r="H30" s="78">
+        <v>41592</v>
+      </c>
+      <c r="I30" s="75" t="s">
+        <v>210</v>
+      </c>
+      <c r="J30" s="76" t="s">
+        <v>211</v>
+      </c>
+      <c r="K30" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="L30" s="76"/>
+      <c r="M30" s="77" t="s">
+        <v>212</v>
+      </c>
+      <c r="N30" s="75"/>
+      <c r="O30" s="76"/>
+      <c r="P30" s="76"/>
+      <c r="Q30" s="76"/>
+      <c r="R30" s="77"/>
+      <c r="S30" s="76"/>
+      <c r="T30" s="76"/>
+      <c r="U30" s="76"/>
     </row>
     <row r="31" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="56"/>
-      <c r="B31" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="D31" s="51" t="s">
+      <c r="B31" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D31" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="51" t="s">
+      <c r="E31" s="48" t="s">
         <v>94</v>
       </c>
-      <c r="F31" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="H31" s="52">
-        <v>43879</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="J31" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="K31" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="L31" s="54">
-        <v>46594</v>
-      </c>
-      <c r="M31" s="53" t="s">
+      <c r="F31" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="62"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="47" t="s">
+        <v>113</v>
+      </c>
+      <c r="J31" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="K31" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="L31" s="62"/>
+      <c r="M31" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="N31" s="50"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="53"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U31" s="51"/>
+      <c r="N31" s="47"/>
+      <c r="O31" s="48"/>
+      <c r="P31" s="48"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="48"/>
+      <c r="T31" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="U31" s="48"/>
     </row>
     <row r="32" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B32" s="50" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C32" s="51" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="D32" s="51" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E32" s="51" t="s">
         <v>94</v>
@@ -3495,10 +3530,10 @@
         <v>100</v>
       </c>
       <c r="G32" s="51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H32" s="52">
-        <v>45648</v>
+        <v>42426</v>
       </c>
       <c r="I32" s="50" t="s">
         <v>122</v>
@@ -3513,11 +3548,21 @@
       <c r="M32" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N32" s="50"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51"/>
-      <c r="R32" s="53"/>
+      <c r="N32" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="O32" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q32" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="R32" s="52">
+        <v>46854</v>
+      </c>
       <c r="S32" s="51"/>
       <c r="T32" s="51" t="s">
         <v>89</v>
@@ -3525,150 +3570,146 @@
       <c r="U32" s="51"/>
     </row>
     <row r="33" spans="2:21" s="70" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B33" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="51" t="s">
+      <c r="B33" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="48"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="J33" s="48">
+        <v>12838081003</v>
+      </c>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="47"/>
+      <c r="O33" s="48"/>
+      <c r="P33" s="48"/>
+      <c r="Q33" s="48"/>
+      <c r="R33" s="49"/>
+      <c r="S33" s="48"/>
+      <c r="T33" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="U33" s="48"/>
+    </row>
+    <row r="34" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B34" s="50" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="51" t="s">
+      <c r="E34" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F33" s="51" t="s">
+      <c r="F34" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G33" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="H33" s="52">
-        <v>45412</v>
-      </c>
-      <c r="I33" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J33" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K33" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L33" s="62"/>
-      <c r="M33" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N33" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="O33" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P33" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q33" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="R33" s="52">
-        <v>46568</v>
-      </c>
-      <c r="S33" s="51"/>
-      <c r="T33" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U33" s="51"/>
-    </row>
-    <row r="34" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B34" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F34" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G34" s="62"/>
-      <c r="H34" s="59"/>
+      <c r="G34" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="H34" s="52">
+        <v>43879</v>
+      </c>
       <c r="I34" s="50" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="J34" s="51" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="K34" s="51" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L34" s="54">
-        <v>46766</v>
+        <v>46594</v>
       </c>
       <c r="M34" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N34" s="40"/>
-      <c r="O34" s="63"/>
-      <c r="P34" s="63"/>
-      <c r="Q34" s="63"/>
-      <c r="R34" s="41"/>
-      <c r="S34" s="63"/>
-      <c r="T34" s="63"/>
-      <c r="U34" s="63"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="51"/>
+      <c r="P34" s="51"/>
+      <c r="Q34" s="51"/>
+      <c r="R34" s="53"/>
+      <c r="S34" s="51"/>
+      <c r="T34" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U34" s="51"/>
     </row>
     <row r="35" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B35" s="84" t="s">
-        <v>220</v>
-      </c>
-      <c r="C35" s="85" t="s">
-        <v>133</v>
-      </c>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85" t="s">
+      <c r="B35" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="85" t="s">
+      <c r="F35" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G35" s="85" t="s">
-        <v>230</v>
-      </c>
-      <c r="H35" s="86"/>
-      <c r="I35" s="84" t="s">
-        <v>229</v>
-      </c>
-      <c r="J35" s="85">
-        <v>11432111000</v>
-      </c>
-      <c r="K35" s="85"/>
-      <c r="L35" s="85"/>
-      <c r="M35" s="86" t="s">
+      <c r="G35" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="H35" s="52">
+        <v>45648</v>
+      </c>
+      <c r="I35" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J35" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K35" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L35" s="62"/>
+      <c r="M35" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N35" s="84"/>
-      <c r="O35" s="85"/>
-      <c r="P35" s="85"/>
-      <c r="Q35" s="85"/>
-      <c r="R35" s="86"/>
-      <c r="S35" s="85"/>
-      <c r="T35" s="85" t="s">
-        <v>76</v>
-      </c>
-      <c r="U35" s="85"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="51"/>
+      <c r="P35" s="51"/>
+      <c r="Q35" s="51"/>
+      <c r="R35" s="53"/>
+      <c r="S35" s="51"/>
+      <c r="T35" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U35" s="51"/>
     </row>
     <row r="36" spans="2:21" s="71" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B36" s="50" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C36" s="51" t="s">
         <v>98</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E36" s="51" t="s">
         <v>94</v>
@@ -3677,16 +3718,16 @@
         <v>100</v>
       </c>
       <c r="G36" s="51" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="H36" s="52">
-        <v>44985</v>
+        <v>45412</v>
       </c>
       <c r="I36" s="50" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J36" s="51">
-        <v>11767131003</v>
+        <v>13068821001</v>
       </c>
       <c r="K36" s="67" t="s">
         <v>170</v>
@@ -3695,187 +3736,177 @@
       <c r="M36" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N36" s="50"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="53"/>
+      <c r="N36" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="O36" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P36" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q36" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="R36" s="52">
+        <v>46568</v>
+      </c>
       <c r="S36" s="51"/>
       <c r="T36" s="51" t="s">
         <v>89</v>
       </c>
       <c r="U36" s="51"/>
     </row>
-    <row r="37" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B37" s="50" t="s">
-        <v>197</v>
-      </c>
-      <c r="C37" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="D37" s="51" t="s">
+    <row r="37" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B37" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="62"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="J37" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K37" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L37" s="54">
+        <v>46766</v>
+      </c>
+      <c r="M37" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="40"/>
+      <c r="O37" s="63"/>
+      <c r="P37" s="63"/>
+      <c r="Q37" s="63"/>
+      <c r="R37" s="41"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="63"/>
+      <c r="U37" s="63"/>
+    </row>
+    <row r="38" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B38" s="75" t="s">
+        <v>220</v>
+      </c>
+      <c r="C38" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="76" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="H38" s="77"/>
+      <c r="I38" s="75" t="s">
+        <v>229</v>
+      </c>
+      <c r="J38" s="76">
+        <v>11432111000</v>
+      </c>
+      <c r="K38" s="76"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="75"/>
+      <c r="O38" s="76"/>
+      <c r="P38" s="76"/>
+      <c r="Q38" s="76"/>
+      <c r="R38" s="77"/>
+      <c r="S38" s="76"/>
+      <c r="T38" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="U38" s="76"/>
+    </row>
+    <row r="39" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B39" s="40" t="s">
+        <v>233</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D39" s="63"/>
+      <c r="E39" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="H39" s="81">
+        <v>42140</v>
+      </c>
+      <c r="I39" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="J39" s="63">
+        <v>7500861005</v>
+      </c>
+      <c r="K39" s="63"/>
+      <c r="L39" s="63"/>
+      <c r="M39" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="N39" s="40"/>
+      <c r="O39" s="63"/>
+      <c r="P39" s="63"/>
+      <c r="Q39" s="63"/>
+      <c r="R39" s="41"/>
+      <c r="S39" s="63"/>
+      <c r="T39" s="63"/>
+      <c r="U39" s="63"/>
+    </row>
+    <row r="40" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B40" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D40" s="51" t="s">
         <v>81</v>
       </c>
-      <c r="E37" s="51" t="s">
+      <c r="E40" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F37" s="51" t="s">
+      <c r="F40" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G37" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="H37" s="52">
-        <v>45979</v>
-      </c>
-      <c r="I37" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="J37" s="51">
-        <v>9075711219</v>
-      </c>
-      <c r="K37" s="72" t="s">
-        <v>169</v>
-      </c>
-      <c r="L37" s="51"/>
-      <c r="M37" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="N37" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="O37" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="P37" s="51">
-        <v>2828850582</v>
-      </c>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="53"/>
-      <c r="S37" s="51"/>
-      <c r="T37" s="51"/>
-      <c r="U37" s="51"/>
-    </row>
-    <row r="38" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B38" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C38" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D38" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E38" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H38" s="52">
-        <v>43584</v>
-      </c>
-      <c r="I38" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J38" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K38" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="L38" s="62"/>
-      <c r="M38" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N38" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="O38" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P38" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="53"/>
-      <c r="S38" s="51"/>
-      <c r="T38" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U38" s="51"/>
-    </row>
-    <row r="39" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B39" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E39" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G39" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H39" s="52">
-        <v>43584</v>
-      </c>
-      <c r="I39" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J39" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K39" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="L39" s="62"/>
-      <c r="M39" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N39" s="50"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="53"/>
-      <c r="S39" s="51"/>
-      <c r="T39" s="51"/>
-      <c r="U39" s="51"/>
-    </row>
-    <row r="40" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B40" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C40" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G40" s="62"/>
-      <c r="H40" s="59"/>
+      <c r="G40" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="H40" s="52">
+        <v>44985</v>
+      </c>
       <c r="I40" s="50" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="J40" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="K40" s="51" t="s">
-        <v>168</v>
+        <v>11767131003</v>
+      </c>
+      <c r="K40" s="67" t="s">
+        <v>170</v>
       </c>
       <c r="L40" s="62"/>
       <c r="M40" s="53" t="s">
@@ -3887,53 +3918,67 @@
       <c r="Q40" s="51"/>
       <c r="R40" s="53"/>
       <c r="S40" s="51"/>
-      <c r="T40" s="51"/>
+      <c r="T40" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="U40" s="51"/>
     </row>
-    <row r="41" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B41" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C41" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D41" s="45"/>
-      <c r="E41" s="45" t="s">
+    <row r="41" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B41" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="F41" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G41" s="62"/>
-      <c r="H41" s="59"/>
+      <c r="F41" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G41" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="H41" s="52">
+        <v>45979</v>
+      </c>
       <c r="I41" s="50" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="J41" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K41" s="51" t="s">
+        <v>9075711219</v>
+      </c>
+      <c r="K41" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="L41" s="62"/>
+      <c r="L41" s="51"/>
       <c r="M41" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N41" s="50"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="51"/>
+        <v>201</v>
+      </c>
+      <c r="N41" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="O41" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="P41" s="51">
+        <v>2828850582</v>
+      </c>
       <c r="Q41" s="51"/>
       <c r="R41" s="53"/>
       <c r="S41" s="51"/>
       <c r="T41" s="51"/>
       <c r="U41" s="51"/>
     </row>
-    <row r="42" spans="2:21" s="88" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B42" s="50" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="D42" s="51" t="s">
         <v>81</v>
@@ -3945,116 +3990,186 @@
         <v>100</v>
       </c>
       <c r="G42" s="51" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="H42" s="52">
-        <v>45909</v>
+        <v>43584</v>
       </c>
       <c r="I42" s="50" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="J42" s="51">
-        <v>13068821001</v>
+        <v>15242251005</v>
       </c>
       <c r="K42" s="67" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L42" s="62"/>
       <c r="M42" s="53" t="s">
         <v>22</v>
       </c>
       <c r="N42" s="50" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="O42" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="P42" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q42" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="R42" s="52">
-        <v>47469</v>
-      </c>
+      <c r="P42" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="Q42" s="51"/>
+      <c r="R42" s="53"/>
       <c r="S42" s="51"/>
       <c r="T42" s="51" t="s">
         <v>89</v>
       </c>
       <c r="U42" s="51"/>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B43" s="40"/>
-      <c r="C43" s="63"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="63"/>
-      <c r="F43" s="63"/>
-      <c r="G43" s="63"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="40"/>
-      <c r="J43" s="63"/>
-      <c r="M43" s="41"/>
-      <c r="N43" s="40"/>
-      <c r="O43" s="63"/>
-      <c r="P43" s="63"/>
-      <c r="Q43" s="63"/>
-      <c r="R43" s="41"/>
-      <c r="S43" s="63"/>
-      <c r="T43" s="63"/>
-      <c r="U43" s="63"/>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B44" s="40"/>
-      <c r="C44" s="63"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
-      <c r="F44" s="63"/>
-      <c r="G44" s="63"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="40"/>
-      <c r="J44" s="63"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="40"/>
-      <c r="O44" s="63"/>
-      <c r="P44" s="63"/>
-      <c r="Q44" s="63"/>
-      <c r="R44" s="41"/>
-      <c r="S44" s="63"/>
-      <c r="T44" s="63"/>
-      <c r="U44" s="63"/>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B45" s="40"/>
-      <c r="C45" s="63"/>
-      <c r="D45" s="63"/>
-      <c r="E45" s="63"/>
-      <c r="F45" s="63"/>
-      <c r="G45" s="63"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="40"/>
-      <c r="J45" s="63"/>
-      <c r="M45" s="41"/>
-      <c r="N45" s="40"/>
-      <c r="O45" s="63"/>
-      <c r="P45" s="63"/>
-      <c r="Q45" s="63"/>
-      <c r="R45" s="41"/>
-      <c r="S45" s="63"/>
-      <c r="T45" s="63"/>
-      <c r="U45" s="63"/>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B46" s="40"/>
-      <c r="C46" s="63"/>
+    <row r="43" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B43" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H43" s="52">
+        <v>43584</v>
+      </c>
+      <c r="I43" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J43" s="51">
+        <v>15242251005</v>
+      </c>
+      <c r="K43" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L43" s="62"/>
+      <c r="M43" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" s="50"/>
+      <c r="O43" s="51"/>
+      <c r="P43" s="51"/>
+      <c r="Q43" s="51"/>
+      <c r="R43" s="53"/>
+      <c r="S43" s="51"/>
+      <c r="T43" s="51"/>
+      <c r="U43" s="51"/>
+    </row>
+    <row r="44" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B44" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C44" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="45"/>
+      <c r="E44" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G44" s="62"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="J44" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="K44" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="L44" s="62"/>
+      <c r="M44" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N44" s="50"/>
+      <c r="O44" s="51"/>
+      <c r="P44" s="51"/>
+      <c r="Q44" s="51"/>
+      <c r="R44" s="53"/>
+      <c r="S44" s="51"/>
+      <c r="T44" s="51"/>
+      <c r="U44" s="51"/>
+    </row>
+    <row r="45" spans="2:21" s="80" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B45" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" s="45"/>
+      <c r="E45" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G45" s="62"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J45" s="51">
+        <v>15242251005</v>
+      </c>
+      <c r="K45" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L45" s="62"/>
+      <c r="M45" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="50"/>
+      <c r="O45" s="51"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="51"/>
+      <c r="R45" s="53"/>
+      <c r="S45" s="51"/>
+      <c r="T45" s="51"/>
+      <c r="U45" s="51"/>
+    </row>
+    <row r="46" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B46" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C46" s="63" t="s">
+        <v>251</v>
+      </c>
       <c r="D46" s="63"/>
-      <c r="E46" s="63"/>
-      <c r="F46" s="63"/>
+      <c r="E46" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F46" s="63" t="s">
+        <v>97</v>
+      </c>
       <c r="G46" s="63"/>
       <c r="H46" s="41"/>
-      <c r="I46" s="40"/>
-      <c r="J46" s="63"/>
-      <c r="M46" s="41"/>
+      <c r="I46" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="J46" s="63">
+        <v>14699681004</v>
+      </c>
+      <c r="M46" s="41" t="s">
+        <v>22</v>
+      </c>
       <c r="N46" s="40"/>
       <c r="O46" s="63"/>
       <c r="P46" s="63"/>
@@ -4064,37 +4179,91 @@
       <c r="T46" s="63"/>
       <c r="U46" s="63"/>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B47" s="40"/>
-      <c r="C47" s="63"/>
-      <c r="D47" s="63"/>
-      <c r="E47" s="63"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="63"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="40"/>
-      <c r="J47" s="63"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="40"/>
-      <c r="O47" s="63"/>
-      <c r="P47" s="63"/>
-      <c r="Q47" s="63"/>
-      <c r="R47" s="41"/>
-      <c r="S47" s="63"/>
-      <c r="T47" s="63"/>
-      <c r="U47" s="63"/>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B48" s="40"/>
-      <c r="C48" s="63"/>
+    <row r="47" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B47" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D47" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="H47" s="52">
+        <v>45909</v>
+      </c>
+      <c r="I47" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J47" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K47" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L47" s="62"/>
+      <c r="M47" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N47" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="O47" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P47" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q47" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="R47" s="52">
+        <v>47469</v>
+      </c>
+      <c r="S47" s="51"/>
+      <c r="T47" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U47" s="51"/>
+    </row>
+    <row r="48" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B48" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="C48" s="63" t="s">
+        <v>247</v>
+      </c>
       <c r="D48" s="63"/>
-      <c r="E48" s="63"/>
-      <c r="F48" s="63"/>
-      <c r="G48" s="63"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="40"/>
-      <c r="J48" s="63"/>
-      <c r="M48" s="41"/>
+      <c r="E48" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G48" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="H48" s="81">
+        <v>43883</v>
+      </c>
+      <c r="I48" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="J48" s="63">
+        <v>1158230639</v>
+      </c>
+      <c r="M48" s="41" t="s">
+        <v>201</v>
+      </c>
       <c r="N48" s="40"/>
       <c r="O48" s="63"/>
       <c r="P48" s="63"/>
@@ -4104,6 +4273,386 @@
       <c r="T48" s="63"/>
       <c r="U48" s="63"/>
     </row>
+    <row r="49" spans="2:21" s="80" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B49" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C49" s="63" t="s">
+        <v>242</v>
+      </c>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G49" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="H49" s="81">
+        <v>46384</v>
+      </c>
+      <c r="I49" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="J49" s="63">
+        <v>17702651005</v>
+      </c>
+      <c r="K49" s="63"/>
+      <c r="L49" s="63"/>
+      <c r="M49" s="41" t="s">
+        <v>245</v>
+      </c>
+      <c r="N49" s="40"/>
+      <c r="O49" s="63"/>
+      <c r="P49" s="63"/>
+      <c r="Q49" s="63"/>
+      <c r="R49" s="41"/>
+      <c r="S49" s="63"/>
+      <c r="T49" s="63"/>
+      <c r="U49" s="63"/>
+    </row>
+    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B50" s="40"/>
+      <c r="C50" s="63"/>
+      <c r="D50" s="63"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="63"/>
+      <c r="M50" s="41"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="63"/>
+      <c r="P50" s="63"/>
+      <c r="Q50" s="63"/>
+      <c r="R50" s="41"/>
+      <c r="S50" s="63"/>
+      <c r="T50" s="63"/>
+      <c r="U50" s="63"/>
+    </row>
+    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B51" s="40"/>
+      <c r="C51" s="63"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
+      <c r="F51" s="63"/>
+      <c r="G51" s="63"/>
+      <c r="H51" s="41"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="63"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="40"/>
+      <c r="O51" s="63"/>
+      <c r="P51" s="63"/>
+      <c r="Q51" s="63"/>
+      <c r="R51" s="41"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="63"/>
+      <c r="U51" s="63"/>
+    </row>
+    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B52" s="40"/>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="63"/>
+      <c r="G52" s="63"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="63"/>
+      <c r="M52" s="41"/>
+      <c r="N52" s="40"/>
+      <c r="O52" s="63"/>
+      <c r="P52" s="63"/>
+      <c r="Q52" s="63"/>
+      <c r="R52" s="41"/>
+      <c r="S52" s="63"/>
+      <c r="T52" s="63"/>
+      <c r="U52" s="63"/>
+    </row>
+    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B53" s="40"/>
+      <c r="C53" s="63"/>
+      <c r="D53" s="63"/>
+      <c r="E53" s="63"/>
+      <c r="F53" s="63"/>
+      <c r="G53" s="63"/>
+      <c r="H53" s="41"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="63"/>
+      <c r="M53" s="41"/>
+      <c r="N53" s="40"/>
+      <c r="O53" s="63"/>
+      <c r="P53" s="63"/>
+      <c r="Q53" s="63"/>
+      <c r="R53" s="41"/>
+      <c r="S53" s="63"/>
+      <c r="T53" s="63"/>
+      <c r="U53" s="63"/>
+    </row>
+    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B54" s="40"/>
+      <c r="C54" s="63"/>
+      <c r="D54" s="63"/>
+      <c r="E54" s="63"/>
+      <c r="F54" s="63"/>
+      <c r="G54" s="63"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="63"/>
+      <c r="M54" s="41"/>
+      <c r="N54" s="40"/>
+      <c r="O54" s="63"/>
+      <c r="P54" s="63"/>
+      <c r="Q54" s="63"/>
+      <c r="R54" s="41"/>
+      <c r="S54" s="63"/>
+      <c r="T54" s="63"/>
+      <c r="U54" s="63"/>
+    </row>
+    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B55" s="40"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="41"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="63"/>
+      <c r="M55" s="41"/>
+      <c r="N55" s="40"/>
+      <c r="O55" s="63"/>
+      <c r="P55" s="63"/>
+      <c r="Q55" s="63"/>
+      <c r="R55" s="41"/>
+      <c r="S55" s="63"/>
+      <c r="T55" s="63"/>
+      <c r="U55" s="63"/>
+    </row>
+    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B56" s="40"/>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="63"/>
+      <c r="F56" s="63"/>
+      <c r="G56" s="63"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="40"/>
+      <c r="J56" s="63"/>
+      <c r="M56" s="41"/>
+      <c r="N56" s="40"/>
+      <c r="O56" s="63"/>
+      <c r="P56" s="63"/>
+      <c r="Q56" s="63"/>
+      <c r="R56" s="41"/>
+      <c r="S56" s="63"/>
+      <c r="T56" s="63"/>
+      <c r="U56" s="63"/>
+    </row>
+    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B57" s="40"/>
+      <c r="C57" s="63"/>
+      <c r="D57" s="63"/>
+      <c r="E57" s="63"/>
+      <c r="F57" s="63"/>
+      <c r="G57" s="63"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="63"/>
+      <c r="M57" s="41"/>
+      <c r="N57" s="40"/>
+      <c r="O57" s="63"/>
+      <c r="P57" s="63"/>
+      <c r="Q57" s="63"/>
+      <c r="R57" s="41"/>
+      <c r="S57" s="63"/>
+      <c r="T57" s="63"/>
+      <c r="U57" s="63"/>
+    </row>
+    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B58" s="40"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="63"/>
+      <c r="M58" s="41"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="63"/>
+      <c r="P58" s="63"/>
+      <c r="Q58" s="63"/>
+      <c r="R58" s="41"/>
+      <c r="S58" s="63"/>
+      <c r="T58" s="63"/>
+      <c r="U58" s="63"/>
+    </row>
+    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B59" s="40"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="63"/>
+      <c r="M59" s="41"/>
+      <c r="N59" s="40"/>
+      <c r="O59" s="63"/>
+      <c r="P59" s="63"/>
+      <c r="Q59" s="63"/>
+      <c r="R59" s="41"/>
+      <c r="S59" s="63"/>
+      <c r="T59" s="63"/>
+      <c r="U59" s="63"/>
+    </row>
+    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B60" s="40"/>
+      <c r="C60" s="63"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="63"/>
+      <c r="F60" s="63"/>
+      <c r="G60" s="63"/>
+      <c r="H60" s="41"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="63"/>
+      <c r="M60" s="41"/>
+      <c r="N60" s="40"/>
+      <c r="O60" s="63"/>
+      <c r="P60" s="63"/>
+      <c r="Q60" s="63"/>
+      <c r="R60" s="41"/>
+      <c r="S60" s="63"/>
+      <c r="T60" s="63"/>
+      <c r="U60" s="63"/>
+    </row>
+    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B61" s="40"/>
+      <c r="C61" s="63"/>
+      <c r="D61" s="63"/>
+      <c r="E61" s="63"/>
+      <c r="F61" s="63"/>
+      <c r="G61" s="63"/>
+      <c r="H61" s="41"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="63"/>
+      <c r="M61" s="41"/>
+      <c r="N61" s="40"/>
+      <c r="O61" s="63"/>
+      <c r="P61" s="63"/>
+      <c r="Q61" s="63"/>
+      <c r="R61" s="41"/>
+      <c r="S61" s="63"/>
+      <c r="T61" s="63"/>
+      <c r="U61" s="63"/>
+    </row>
+    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B62" s="40"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="63"/>
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="63"/>
+      <c r="M62" s="41"/>
+      <c r="N62" s="40"/>
+      <c r="O62" s="63"/>
+      <c r="P62" s="63"/>
+      <c r="Q62" s="63"/>
+      <c r="R62" s="41"/>
+      <c r="S62" s="63"/>
+      <c r="T62" s="63"/>
+      <c r="U62" s="63"/>
+    </row>
+    <row r="63" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B63" s="40"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+      <c r="F63" s="63"/>
+      <c r="G63" s="63"/>
+      <c r="H63" s="41"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="63"/>
+      <c r="M63" s="41"/>
+      <c r="N63" s="40"/>
+      <c r="O63" s="63"/>
+      <c r="P63" s="63"/>
+      <c r="Q63" s="63"/>
+      <c r="R63" s="41"/>
+      <c r="S63" s="63"/>
+      <c r="T63" s="63"/>
+      <c r="U63" s="63"/>
+    </row>
+    <row r="64" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B64" s="40"/>
+      <c r="C64" s="63"/>
+      <c r="D64" s="63"/>
+      <c r="E64" s="63"/>
+      <c r="F64" s="63"/>
+      <c r="G64" s="63"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="40"/>
+      <c r="J64" s="63"/>
+      <c r="M64" s="41"/>
+      <c r="N64" s="40"/>
+      <c r="O64" s="63"/>
+      <c r="P64" s="63"/>
+      <c r="Q64" s="63"/>
+      <c r="R64" s="41"/>
+      <c r="S64" s="63"/>
+      <c r="T64" s="63"/>
+      <c r="U64" s="63"/>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B65" s="40"/>
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="63"/>
+      <c r="G65" s="63"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="40"/>
+      <c r="J65" s="63"/>
+      <c r="M65" s="41"/>
+      <c r="N65" s="40"/>
+      <c r="O65" s="63"/>
+      <c r="P65" s="63"/>
+      <c r="Q65" s="63"/>
+      <c r="R65" s="41"/>
+      <c r="S65" s="63"/>
+      <c r="T65" s="63"/>
+      <c r="U65" s="63"/>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B66" s="40"/>
+      <c r="C66" s="63"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="63"/>
+      <c r="G66" s="63"/>
+      <c r="H66" s="41"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="63"/>
+      <c r="M66" s="41"/>
+      <c r="N66" s="40"/>
+      <c r="O66" s="63"/>
+      <c r="P66" s="63"/>
+      <c r="Q66" s="63"/>
+      <c r="R66" s="41"/>
+      <c r="S66" s="63"/>
+      <c r="T66" s="63"/>
+      <c r="U66" s="63"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/prospetto_mezzi.xlsx
+++ b/prospetto_mezzi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs-rm073\rm229 - gruppo civitavecchia\6\7\8\1. ATTIVITA' GLOBALE_SERVER\1. SERVIZIO N.C.C. 1 STANZIALE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Fs-rm073\rm229 - gruppo civitavecchia\6\7\8\1. ATTIVITA' GLOBALE_SERVER\1. SERVIZIO N.C.C. 1 STANZIALE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC82405-5C1A-4AFE-A0EF-ACB6F0DEA268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892920F7-51BB-4607-9BE7-647F010C18B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1740" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="296">
   <si>
     <t>EL706PT</t>
   </si>
@@ -802,6 +802,132 @@
   </si>
   <si>
     <t>NNICCL69C62H501A</t>
+  </si>
+  <si>
+    <t>GS215WP</t>
+  </si>
+  <si>
+    <t>GN635AK</t>
+  </si>
+  <si>
+    <t>ROSSI AUTOSERVIZI SOC. COOP.</t>
+  </si>
+  <si>
+    <t>ALTRE ATTIVITA' DI TRASPORTI TERRESTRI DI PASSEGGERI NCA</t>
+  </si>
+  <si>
+    <t>ATTIVITA' DI AGENZIE DI VIAGGIO</t>
+  </si>
+  <si>
+    <t>NOLEGGIO E LEASING OPERAT.AUTOMOBILI E AUTOVEICOLI LEGGERI</t>
+  </si>
+  <si>
+    <t>HB498XT</t>
+  </si>
+  <si>
+    <t>GA499AK</t>
+  </si>
+  <si>
+    <t>GH035TX</t>
+  </si>
+  <si>
+    <t>FZ519WP</t>
+  </si>
+  <si>
+    <t>FX724FE</t>
+  </si>
+  <si>
+    <t>HA457LP</t>
+  </si>
+  <si>
+    <t>FM099SD</t>
+  </si>
+  <si>
+    <t>FP819VX</t>
+  </si>
+  <si>
+    <t>GZ846LS</t>
+  </si>
+  <si>
+    <t>GZ096HY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 1/2018 COMUNE BARLETTA     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 5/2010 COMUNE LAMEZIA TERME </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 17 COMUNE RONCIGLIONE         </t>
+  </si>
+  <si>
+    <t>GIUBILEO CRUISE SERVICE NCC</t>
+  </si>
+  <si>
+    <t>D'ALESSANDRO DANILO</t>
+  </si>
+  <si>
+    <t>DLSDNL95B18C773N</t>
+  </si>
+  <si>
+    <t>LIC. 1 COMUNE BASELICE</t>
+  </si>
+  <si>
+    <t>ETRUSCA TRAVEL TOUR NCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC15  COMUNE APRILIA    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 29872 COMUNE GUBBIO    </t>
+  </si>
+  <si>
+    <t>S.I.C. TURISMO SRL</t>
+  </si>
+  <si>
+    <t>GUBBIO</t>
+  </si>
+  <si>
+    <t>STELLANTIS FINANCIAL SERVICES ITALIA</t>
+  </si>
+  <si>
+    <t>TORINO</t>
+  </si>
+  <si>
+    <t>RENAULT VIVARO</t>
+  </si>
+  <si>
+    <t>GIUBILEO SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC329756 COMUNE BOLZANO-BOZEN   </t>
+  </si>
+  <si>
+    <t>IFM SPV</t>
+  </si>
+  <si>
+    <t>MERCEDES BENZ VITO TOURER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC. 17  COMUNE RONCIGLIONE  </t>
+  </si>
+  <si>
+    <t>RENAULT  CAPTUR</t>
+  </si>
+  <si>
+    <t>NATALE EMILIANO</t>
+  </si>
+  <si>
+    <t>NTLMLN74P13A489M</t>
+  </si>
+  <si>
+    <t>NUSCO</t>
+  </si>
+  <si>
+    <t>BOLZANO</t>
+  </si>
+  <si>
+    <t>RM8212197</t>
   </si>
 </sst>
 </file>
@@ -1033,7 +1159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1260,6 +1386,15 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1286,6 +1421,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1521,10 +1659,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U66" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="B4:U66" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:U66">
-    <sortCondition ref="B4:B66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B4:U65" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="B4:U65" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B5:U65">
+    <sortCondition ref="B4:B65"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="2" xr3:uid="{779EAAEE-59A7-446B-AD7C-6F7003AD1695}" name="TARGA" dataDxfId="19"/>
@@ -1902,7 +2040,7 @@
     <row r="10" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D11" s="1"/>
-      <c r="E11" s="82" t="s">
+      <c r="E11" s="85" t="s">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -1923,7 +2061,7 @@
     </row>
     <row r="12" spans="4:10" ht="30" x14ac:dyDescent="0.25">
       <c r="D12" s="5"/>
-      <c r="E12" s="83"/>
+      <c r="E12" s="86"/>
       <c r="F12" s="14" t="s">
         <v>15</v>
       </c>
@@ -1938,7 +2076,7 @@
     </row>
     <row r="13" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="3"/>
-      <c r="E13" s="84"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="17"/>
       <c r="G13" s="18" t="s">
         <v>14</v>
@@ -1951,7 +2089,7 @@
     </row>
     <row r="14" spans="4:10" ht="150" x14ac:dyDescent="0.25">
       <c r="D14" s="1"/>
-      <c r="E14" s="85" t="s">
+      <c r="E14" s="88" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="29" t="s">
@@ -1972,7 +2110,7 @@
     </row>
     <row r="15" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D15" s="5"/>
-      <c r="E15" s="86"/>
+      <c r="E15" s="89"/>
       <c r="F15" s="31" t="s">
         <v>19</v>
       </c>
@@ -1989,7 +2127,7 @@
     </row>
     <row r="16" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D16" s="3"/>
-      <c r="E16" s="87"/>
+      <c r="E16" s="90"/>
       <c r="F16" s="34"/>
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
@@ -2000,7 +2138,7 @@
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
-      <c r="E17" s="88" t="s">
+      <c r="E17" s="91" t="s">
         <v>26</v>
       </c>
       <c r="F17" s="11" t="s">
@@ -2017,7 +2155,7 @@
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D18" s="5"/>
-      <c r="E18" s="89"/>
+      <c r="E18" s="92"/>
       <c r="F18" s="14" t="s">
         <v>19</v>
       </c>
@@ -2030,7 +2168,7 @@
     </row>
     <row r="19" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D19" s="3"/>
-      <c r="E19" s="90"/>
+      <c r="E19" s="93"/>
       <c r="F19" s="17"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
@@ -2232,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56392095-0261-4957-A1EF-F42F71E397DD}">
-  <dimension ref="A3:U66"/>
+  <dimension ref="A3:U65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="61"/>
@@ -2357,7 +2495,7 @@
       <c r="T5" s="48"/>
       <c r="U5" s="48"/>
     </row>
-    <row r="6" spans="2:21" s="64" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:21" s="64" customFormat="1" ht="45" x14ac:dyDescent="0.15">
       <c r="B6" s="75" t="s">
         <v>219</v>
       </c>
@@ -2381,7 +2519,9 @@
       <c r="J6" s="76">
         <v>12838081003</v>
       </c>
-      <c r="K6" s="76"/>
+      <c r="K6" s="83" t="s">
+        <v>170</v>
+      </c>
       <c r="L6" s="76"/>
       <c r="M6" s="77" t="s">
         <v>22</v>
@@ -2537,7 +2677,9 @@
       <c r="J10" s="63">
         <v>14699681004</v>
       </c>
-      <c r="K10" s="63"/>
+      <c r="K10" s="84" t="s">
+        <v>258</v>
+      </c>
       <c r="L10" s="63"/>
       <c r="M10" s="41" t="s">
         <v>22</v>
@@ -3372,7 +3514,9 @@
       <c r="J28" s="76">
         <v>11767131003</v>
       </c>
-      <c r="K28" s="76"/>
+      <c r="K28" s="84" t="s">
+        <v>170</v>
+      </c>
       <c r="L28" s="76"/>
       <c r="M28" s="77" t="s">
         <v>22</v>
@@ -3388,211 +3532,189 @@
       </c>
       <c r="U28" s="76"/>
     </row>
-    <row r="29" spans="1:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="57"/>
-      <c r="B29" s="48" t="s">
-        <v>235</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="48" t="s">
+      <c r="B29" s="63" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="48"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="47" t="s">
-        <v>246</v>
-      </c>
-      <c r="J29" s="48">
-        <v>17833641008</v>
-      </c>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="49" t="s">
+      <c r="G29" s="63"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="J29" s="63">
+        <v>18064001003</v>
+      </c>
+      <c r="K29" s="63"/>
+      <c r="L29" s="63"/>
+      <c r="M29" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="N29" s="47"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="63"/>
+      <c r="P29" s="63"/>
+      <c r="Q29" s="63"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="63"/>
+      <c r="T29" s="63"/>
+      <c r="U29" s="63"/>
     </row>
     <row r="30" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="56"/>
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="48" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="47" t="s">
+        <v>246</v>
+      </c>
+      <c r="J30" s="48">
+        <v>17833641008</v>
+      </c>
+      <c r="K30" s="84" t="s">
+        <v>259</v>
+      </c>
+      <c r="L30" s="48"/>
+      <c r="M30" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="N30" s="47"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="49"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="48"/>
+    </row>
+    <row r="31" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="56"/>
+      <c r="B31" s="63" t="s">
+        <v>267</v>
+      </c>
+      <c r="C31" s="63" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="63"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="J31" s="63">
+        <v>18064001003</v>
+      </c>
+      <c r="M31" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="N31" s="40"/>
+      <c r="O31" s="63"/>
+      <c r="P31" s="63"/>
+      <c r="Q31" s="63"/>
+      <c r="R31" s="41"/>
+      <c r="S31" s="63"/>
+      <c r="T31" s="63"/>
+      <c r="U31" s="63"/>
+    </row>
+    <row r="32" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B32" s="75" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C32" s="76" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="76" t="s">
+      <c r="D32" s="76" t="s">
         <v>208</v>
       </c>
-      <c r="E30" s="76" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="76" t="s">
+      <c r="E32" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G30" s="76" t="s">
+      <c r="G32" s="76" t="s">
         <v>209</v>
       </c>
-      <c r="H30" s="78">
+      <c r="H32" s="78">
         <v>41592</v>
       </c>
-      <c r="I30" s="75" t="s">
+      <c r="I32" s="75" t="s">
         <v>210</v>
       </c>
-      <c r="J30" s="76" t="s">
+      <c r="J32" s="76" t="s">
         <v>211</v>
       </c>
-      <c r="K30" s="76" t="s">
+      <c r="K32" s="76" t="s">
         <v>213</v>
       </c>
-      <c r="L30" s="76"/>
-      <c r="M30" s="77" t="s">
+      <c r="L32" s="76"/>
+      <c r="M32" s="77" t="s">
         <v>212</v>
       </c>
-      <c r="N30" s="75"/>
-      <c r="O30" s="76"/>
-      <c r="P30" s="76"/>
-      <c r="Q30" s="76"/>
-      <c r="R30" s="77"/>
-      <c r="S30" s="76"/>
-      <c r="T30" s="76"/>
-      <c r="U30" s="76"/>
-    </row>
-    <row r="31" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="56"/>
-      <c r="B31" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="D31" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="E31" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G31" s="62"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="47" t="s">
-        <v>113</v>
-      </c>
-      <c r="J31" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="K31" s="74" t="s">
-        <v>216</v>
-      </c>
-      <c r="L31" s="62"/>
-      <c r="M31" s="49" t="s">
-        <v>22</v>
-      </c>
-      <c r="N31" s="47"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="49"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="U31" s="48"/>
-    </row>
-    <row r="32" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B32" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D32" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E32" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="H32" s="52">
-        <v>42426</v>
-      </c>
-      <c r="I32" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J32" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K32" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L32" s="62"/>
-      <c r="M32" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N32" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="O32" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P32" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q32" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="R32" s="52">
-        <v>46854</v>
-      </c>
-      <c r="S32" s="51"/>
-      <c r="T32" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U32" s="51"/>
+      <c r="N32" s="75"/>
+      <c r="O32" s="76"/>
+      <c r="P32" s="76"/>
+      <c r="Q32" s="76"/>
+      <c r="R32" s="77"/>
+      <c r="S32" s="76"/>
+      <c r="T32" s="76"/>
+      <c r="U32" s="76"/>
     </row>
     <row r="33" spans="2:21" s="70" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B33" s="47" t="s">
-        <v>218</v>
+        <v>75</v>
       </c>
       <c r="C33" s="48" t="s">
-        <v>226</v>
-      </c>
-      <c r="D33" s="48"/>
+        <v>98</v>
+      </c>
+      <c r="D33" s="48" t="s">
+        <v>77</v>
+      </c>
       <c r="E33" s="48" t="s">
         <v>94</v>
       </c>
       <c r="F33" s="48" t="s">
         <v>97</v>
       </c>
-      <c r="G33" s="48"/>
-      <c r="H33" s="49"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="59"/>
       <c r="I33" s="47" t="s">
-        <v>227</v>
-      </c>
-      <c r="J33" s="48">
-        <v>12838081003</v>
-      </c>
-      <c r="K33" s="48"/>
-      <c r="L33" s="48"/>
+        <v>113</v>
+      </c>
+      <c r="J33" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="K33" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="L33" s="62"/>
       <c r="M33" s="49" t="s">
         <v>22</v>
       </c>
@@ -3609,13 +3731,13 @@
     </row>
     <row r="34" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B34" s="50" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C34" s="51" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="D34" s="51" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E34" s="51" t="s">
         <v>94</v>
@@ -3624,31 +3746,39 @@
         <v>100</v>
       </c>
       <c r="G34" s="51" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="H34" s="52">
-        <v>43879</v>
+        <v>42426</v>
       </c>
       <c r="I34" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="J34" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="K34" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="L34" s="54">
-        <v>46594</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="J34" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K34" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L34" s="62"/>
       <c r="M34" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N34" s="50"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="51"/>
-      <c r="R34" s="53"/>
+      <c r="N34" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="O34" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" s="51" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q34" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="R34" s="52">
+        <v>46854</v>
+      </c>
       <c r="S34" s="51"/>
       <c r="T34" s="51" t="s">
         <v>89</v>
@@ -3656,236 +3786,242 @@
       <c r="U34" s="51"/>
     </row>
     <row r="35" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B35" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D35" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="E35" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="51" t="s">
+      <c r="B35" s="47" t="s">
+        <v>218</v>
+      </c>
+      <c r="C35" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G35" s="48"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="J35" s="48">
+        <v>12838081003</v>
+      </c>
+      <c r="K35" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="L35" s="48"/>
+      <c r="M35" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="47"/>
+      <c r="O35" s="48"/>
+      <c r="P35" s="48"/>
+      <c r="Q35" s="48"/>
+      <c r="R35" s="49"/>
+      <c r="S35" s="48"/>
+      <c r="T35" s="48" t="s">
+        <v>76</v>
+      </c>
+      <c r="U35" s="48"/>
+    </row>
+    <row r="36" spans="2:21" s="71" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="C36" s="63" t="s">
+        <v>207</v>
+      </c>
+      <c r="D36" s="63"/>
+      <c r="E36" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="G35" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="H35" s="52">
-        <v>45648</v>
-      </c>
-      <c r="I35" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J35" s="51">
+      <c r="G36" s="63" t="s">
+        <v>278</v>
+      </c>
+      <c r="H36" s="81">
+        <v>45394</v>
+      </c>
+      <c r="I36" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J36" s="63">
         <v>13068821001</v>
       </c>
-      <c r="K35" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L35" s="62"/>
-      <c r="M35" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N35" s="50"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-      <c r="R35" s="53"/>
-      <c r="S35" s="51"/>
-      <c r="T35" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U35" s="51"/>
-    </row>
-    <row r="36" spans="2:21" s="71" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="C36" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D36" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="E36" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="G36" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="H36" s="52">
-        <v>45412</v>
-      </c>
-      <c r="I36" s="50" t="s">
-        <v>122</v>
-      </c>
-      <c r="J36" s="51">
-        <v>13068821001</v>
-      </c>
-      <c r="K36" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="L36" s="62"/>
-      <c r="M36" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N36" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="O36" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P36" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q36" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="R36" s="52">
-        <v>46568</v>
-      </c>
-      <c r="S36" s="51"/>
-      <c r="T36" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U36" s="51"/>
+      <c r="K36" s="63"/>
+      <c r="L36" s="63"/>
+      <c r="M36" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" s="40"/>
+      <c r="O36" s="63"/>
+      <c r="P36" s="63"/>
+      <c r="Q36" s="63"/>
+      <c r="R36" s="41"/>
+      <c r="S36" s="63"/>
+      <c r="T36" s="63"/>
+      <c r="U36" s="63"/>
     </row>
     <row r="37" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B37" s="58" t="s">
-        <v>45</v>
+      <c r="B37" s="47" t="s">
+        <v>263</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>108</v>
+        <v>207</v>
       </c>
       <c r="D37" s="48"/>
       <c r="E37" s="48" t="s">
         <v>94</v>
       </c>
       <c r="F37" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G37" s="62"/>
-      <c r="H37" s="59"/>
-      <c r="I37" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="J37" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="K37" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="L37" s="54">
-        <v>46766</v>
-      </c>
-      <c r="M37" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N37" s="40"/>
-      <c r="O37" s="63"/>
-      <c r="P37" s="63"/>
-      <c r="Q37" s="63"/>
-      <c r="R37" s="41"/>
-      <c r="S37" s="63"/>
-      <c r="T37" s="63"/>
-      <c r="U37" s="63"/>
-    </row>
-    <row r="38" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B38" s="75" t="s">
-        <v>220</v>
-      </c>
-      <c r="C38" s="76" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="76" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G38" s="76" t="s">
-        <v>230</v>
-      </c>
-      <c r="H38" s="77"/>
-      <c r="I38" s="75" t="s">
-        <v>229</v>
-      </c>
-      <c r="J38" s="76">
-        <v>11432111000</v>
-      </c>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="N38" s="75"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="76"/>
-      <c r="Q38" s="76"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="76"/>
-      <c r="T38" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="U38" s="76"/>
+      <c r="G37" s="48" t="s">
+        <v>276</v>
+      </c>
+      <c r="H37" s="94">
+        <v>45701</v>
+      </c>
+      <c r="I37" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="J37" s="48">
+        <v>12578741006</v>
+      </c>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="47" t="s">
+        <v>159</v>
+      </c>
+      <c r="O37" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P37" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q37" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="R37" s="94">
+        <v>44044</v>
+      </c>
+      <c r="S37" s="48"/>
+      <c r="T37" s="48"/>
+      <c r="U37" s="48"/>
+    </row>
+    <row r="38" spans="2:21" s="73" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="C38" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="63" t="s">
+        <v>271</v>
+      </c>
+      <c r="H38" s="81">
+        <v>45084</v>
+      </c>
+      <c r="I38" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="J38" s="63">
+        <v>13068821001</v>
+      </c>
+      <c r="K38" s="63"/>
+      <c r="L38" s="63"/>
+      <c r="M38" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="O38" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q38" s="63" t="s">
+        <v>147</v>
+      </c>
+      <c r="R38" s="81">
+        <v>46568</v>
+      </c>
+      <c r="S38" s="63"/>
+      <c r="T38" s="63"/>
+      <c r="U38" s="63"/>
     </row>
     <row r="39" spans="2:21" s="73" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B39" s="40" t="s">
-        <v>233</v>
+      <c r="B39" s="50" t="s">
+        <v>93</v>
       </c>
       <c r="C39" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="51" t="s">
         <v>100</v>
       </c>
-      <c r="G39" s="63" t="s">
-        <v>241</v>
-      </c>
-      <c r="H39" s="81">
-        <v>42140</v>
-      </c>
-      <c r="I39" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="J39" s="63">
-        <v>7500861005</v>
-      </c>
-      <c r="K39" s="63"/>
-      <c r="L39" s="63"/>
-      <c r="M39" s="41" t="s">
-        <v>194</v>
-      </c>
-      <c r="N39" s="40"/>
-      <c r="O39" s="63"/>
-      <c r="P39" s="63"/>
-      <c r="Q39" s="63"/>
-      <c r="R39" s="41"/>
-      <c r="S39" s="63"/>
-      <c r="T39" s="63"/>
-      <c r="U39" s="63"/>
+      <c r="G39" s="51" t="s">
+        <v>163</v>
+      </c>
+      <c r="H39" s="52">
+        <v>43879</v>
+      </c>
+      <c r="I39" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="J39" s="51" t="s">
+        <v>165</v>
+      </c>
+      <c r="K39" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="L39" s="54">
+        <v>46594</v>
+      </c>
+      <c r="M39" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" s="50"/>
+      <c r="O39" s="51"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="51"/>
+      <c r="R39" s="53"/>
+      <c r="S39" s="51"/>
+      <c r="T39" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U39" s="51"/>
     </row>
     <row r="40" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B40" s="50" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C40" s="51" t="s">
         <v>98</v>
       </c>
       <c r="D40" s="51" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E40" s="51" t="s">
         <v>94</v>
@@ -3894,16 +4030,16 @@
         <v>100</v>
       </c>
       <c r="G40" s="51" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="H40" s="52">
-        <v>44985</v>
+        <v>45648</v>
       </c>
       <c r="I40" s="50" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="J40" s="51">
-        <v>11767131003</v>
+        <v>13068821001</v>
       </c>
       <c r="K40" s="67" t="s">
         <v>170</v>
@@ -3925,13 +4061,13 @@
     </row>
     <row r="41" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B41" s="50" t="s">
-        <v>197</v>
+        <v>86</v>
       </c>
       <c r="C41" s="51" t="s">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E41" s="51" t="s">
         <v>94</v>
@@ -3940,235 +4076,254 @@
         <v>100</v>
       </c>
       <c r="G41" s="51" t="s">
-        <v>199</v>
+        <v>144</v>
       </c>
       <c r="H41" s="52">
-        <v>45979</v>
+        <v>45412</v>
       </c>
       <c r="I41" s="50" t="s">
-        <v>200</v>
+        <v>122</v>
       </c>
       <c r="J41" s="51">
-        <v>9075711219</v>
-      </c>
-      <c r="K41" s="72" t="s">
-        <v>169</v>
-      </c>
-      <c r="L41" s="51"/>
+        <v>13068821001</v>
+      </c>
+      <c r="K41" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L41" s="62"/>
       <c r="M41" s="53" t="s">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="N41" s="50" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="O41" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" s="51" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q41" s="51" t="s">
+        <v>147</v>
+      </c>
+      <c r="R41" s="52">
+        <v>46568</v>
+      </c>
+      <c r="S41" s="51"/>
+      <c r="T41" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U41" s="51"/>
+    </row>
+    <row r="42" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B42" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G42" s="62"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="50" t="s">
+        <v>154</v>
+      </c>
+      <c r="J42" s="51" t="s">
+        <v>155</v>
+      </c>
+      <c r="K42" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="L42" s="54">
+        <v>46766</v>
+      </c>
+      <c r="M42" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N42" s="40"/>
+      <c r="O42" s="63"/>
+      <c r="P42" s="63"/>
+      <c r="Q42" s="63"/>
+      <c r="R42" s="41"/>
+      <c r="S42" s="63"/>
+      <c r="T42" s="63"/>
+      <c r="U42" s="63"/>
+    </row>
+    <row r="43" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B43" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" s="63" t="s">
+        <v>133</v>
+      </c>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F43" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G43" s="63" t="s">
+        <v>272</v>
+      </c>
+      <c r="H43" s="81">
+        <v>42865</v>
+      </c>
+      <c r="I43" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="J43" s="63">
+        <v>17830511006</v>
+      </c>
+      <c r="M43" s="41" t="s">
         <v>194</v>
       </c>
-      <c r="P41" s="51">
-        <v>2828850582</v>
-      </c>
-      <c r="Q41" s="51"/>
-      <c r="R41" s="53"/>
-      <c r="S41" s="51"/>
-      <c r="T41" s="51"/>
-      <c r="U41" s="51"/>
-    </row>
-    <row r="42" spans="2:21" s="79" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B42" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E42" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="51" t="s">
+      <c r="N43" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="O43" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" s="63" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q43" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="R43" s="81">
+        <v>46294</v>
+      </c>
+      <c r="S43" s="63"/>
+      <c r="T43" s="63"/>
+      <c r="U43" s="63"/>
+    </row>
+    <row r="44" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B44" s="40" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="63" t="s">
         <v>100</v>
       </c>
-      <c r="G42" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H42" s="52">
-        <v>43584</v>
-      </c>
-      <c r="I42" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J42" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K42" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="L42" s="62"/>
-      <c r="M42" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N42" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="O42" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P42" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="Q42" s="51"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="51"/>
-      <c r="T42" s="51" t="s">
-        <v>89</v>
-      </c>
-      <c r="U42" s="51"/>
-    </row>
-    <row r="43" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B43" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="51" t="s">
-        <v>94</v>
-      </c>
-      <c r="F43" s="51" t="s">
+      <c r="G44" s="63" t="s">
+        <v>289</v>
+      </c>
+      <c r="H44" s="81">
+        <v>42865</v>
+      </c>
+      <c r="I44" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="J44" s="63">
+        <v>17830511006</v>
+      </c>
+      <c r="M44" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="N44" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="O44" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" s="63" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q44" s="63" t="s">
+        <v>295</v>
+      </c>
+      <c r="R44" s="81">
+        <v>46294</v>
+      </c>
+      <c r="S44" s="63"/>
+      <c r="T44" s="63"/>
+      <c r="U44" s="63"/>
+    </row>
+    <row r="45" spans="2:21" s="80" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B45" s="75" t="s">
+        <v>220</v>
+      </c>
+      <c r="C45" s="76" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="76" t="s">
         <v>100</v>
       </c>
-      <c r="G43" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="H43" s="52">
-        <v>43584</v>
-      </c>
-      <c r="I43" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J43" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K43" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="L43" s="62"/>
-      <c r="M43" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N43" s="50"/>
-      <c r="O43" s="51"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="51"/>
-      <c r="R43" s="53"/>
-      <c r="S43" s="51"/>
-      <c r="T43" s="51"/>
-      <c r="U43" s="51"/>
-    </row>
-    <row r="44" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B44" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="45"/>
-      <c r="E44" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F44" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G44" s="62"/>
-      <c r="H44" s="59"/>
-      <c r="I44" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="J44" s="51">
-        <v>14119701002</v>
-      </c>
-      <c r="K44" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="L44" s="62"/>
-      <c r="M44" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N44" s="50"/>
-      <c r="O44" s="51"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="51"/>
-      <c r="R44" s="53"/>
-      <c r="S44" s="51"/>
-      <c r="T44" s="51"/>
-      <c r="U44" s="51"/>
-    </row>
-    <row r="45" spans="2:21" s="80" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B45" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="45" t="s">
-        <v>97</v>
-      </c>
-      <c r="G45" s="62"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="J45" s="51">
-        <v>15242251005</v>
-      </c>
-      <c r="K45" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="L45" s="62"/>
-      <c r="M45" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="N45" s="50"/>
-      <c r="O45" s="51"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="51"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="51"/>
-      <c r="T45" s="51"/>
-      <c r="U45" s="51"/>
-    </row>
-    <row r="46" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="G45" s="76" t="s">
+        <v>230</v>
+      </c>
+      <c r="H45" s="77"/>
+      <c r="I45" s="75" t="s">
+        <v>229</v>
+      </c>
+      <c r="J45" s="76">
+        <v>11432111000</v>
+      </c>
+      <c r="K45" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="L45" s="76"/>
+      <c r="M45" s="77" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="75"/>
+      <c r="O45" s="76"/>
+      <c r="P45" s="76"/>
+      <c r="Q45" s="76"/>
+      <c r="R45" s="77"/>
+      <c r="S45" s="76"/>
+      <c r="T45" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="U45" s="76"/>
+    </row>
+    <row r="46" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B46" s="40" t="s">
-        <v>238</v>
-      </c>
-      <c r="C46" s="63" t="s">
-        <v>251</v>
+        <v>233</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>133</v>
       </c>
       <c r="D46" s="63"/>
       <c r="E46" s="63" t="s">
         <v>94</v>
       </c>
       <c r="F46" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="G46" s="63"/>
-      <c r="H46" s="41"/>
+        <v>100</v>
+      </c>
+      <c r="G46" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="H46" s="81">
+        <v>42140</v>
+      </c>
       <c r="I46" s="40" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="J46" s="63">
-        <v>14699681004</v>
+        <v>7500861005</v>
+      </c>
+      <c r="K46" s="84" t="s">
+        <v>169</v>
       </c>
       <c r="M46" s="41" t="s">
-        <v>22</v>
+        <v>194</v>
       </c>
       <c r="N46" s="40"/>
       <c r="O46" s="63"/>
@@ -4181,10 +4336,10 @@
     </row>
     <row r="47" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B47" s="50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C47" s="51" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="D47" s="51" t="s">
         <v>81</v>
@@ -4196,16 +4351,16 @@
         <v>100</v>
       </c>
       <c r="G47" s="51" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H47" s="52">
-        <v>45909</v>
+        <v>44985</v>
       </c>
       <c r="I47" s="50" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J47" s="51">
-        <v>13068821001</v>
+        <v>11767131003</v>
       </c>
       <c r="K47" s="67" t="s">
         <v>170</v>
@@ -4214,55 +4369,44 @@
       <c r="M47" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="N47" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="O47" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="P47" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q47" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="R47" s="52">
-        <v>47469</v>
-      </c>
+      <c r="N47" s="50"/>
+      <c r="O47" s="51"/>
+      <c r="P47" s="51"/>
+      <c r="Q47" s="51"/>
+      <c r="R47" s="53"/>
       <c r="S47" s="51"/>
       <c r="T47" s="51" t="s">
         <v>89</v>
       </c>
       <c r="U47" s="51"/>
     </row>
-    <row r="48" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:21" ht="45" x14ac:dyDescent="0.15">
       <c r="B48" s="40" t="s">
-        <v>236</v>
+        <v>255</v>
       </c>
       <c r="C48" s="63" t="s">
-        <v>247</v>
+        <v>98</v>
       </c>
       <c r="D48" s="63"/>
       <c r="E48" s="63" t="s">
         <v>94</v>
       </c>
       <c r="F48" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="G48" s="63" t="s">
-        <v>248</v>
-      </c>
-      <c r="H48" s="81">
-        <v>43883</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G48" s="63"/>
+      <c r="H48" s="41"/>
       <c r="I48" s="40" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="J48" s="63">
-        <v>1158230639</v>
+        <v>17044251001</v>
+      </c>
+      <c r="K48" s="83" t="s">
+        <v>170</v>
       </c>
       <c r="M48" s="41" t="s">
-        <v>201</v>
+        <v>143</v>
       </c>
       <c r="N48" s="40"/>
       <c r="O48" s="63"/>
@@ -4273,36 +4417,34 @@
       <c r="T48" s="63"/>
       <c r="U48" s="63"/>
     </row>
-    <row r="49" spans="2:21" s="80" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" s="80" customFormat="1" ht="45" x14ac:dyDescent="0.15">
       <c r="B49" s="40" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="C49" s="63" t="s">
-        <v>242</v>
+        <v>98</v>
       </c>
       <c r="D49" s="63"/>
       <c r="E49" s="63" t="s">
         <v>94</v>
       </c>
       <c r="F49" s="63" t="s">
-        <v>100</v>
-      </c>
-      <c r="G49" s="63" t="s">
-        <v>243</v>
-      </c>
-      <c r="H49" s="81">
-        <v>46384</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="G49" s="63"/>
+      <c r="H49" s="41"/>
       <c r="I49" s="40" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="J49" s="63">
-        <v>17702651005</v>
-      </c>
-      <c r="K49" s="63"/>
+        <v>17044251001</v>
+      </c>
+      <c r="K49" s="83" t="s">
+        <v>170</v>
+      </c>
       <c r="L49" s="63"/>
       <c r="M49" s="41" t="s">
-        <v>245</v>
+        <v>143</v>
       </c>
       <c r="N49" s="40"/>
       <c r="O49" s="63"/>
@@ -4313,117 +4455,257 @@
       <c r="T49" s="63"/>
       <c r="U49" s="63"/>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B50" s="40"/>
-      <c r="C50" s="63"/>
-      <c r="D50" s="63"/>
-      <c r="E50" s="63"/>
-      <c r="F50" s="63"/>
-      <c r="G50" s="63"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="63"/>
-      <c r="M50" s="41"/>
-      <c r="N50" s="40"/>
-      <c r="O50" s="63"/>
-      <c r="P50" s="63"/>
-      <c r="Q50" s="63"/>
-      <c r="R50" s="41"/>
-      <c r="S50" s="63"/>
-      <c r="T50" s="63"/>
-      <c r="U50" s="63"/>
-    </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B51" s="40"/>
-      <c r="C51" s="63"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="63"/>
-      <c r="M51" s="41"/>
-      <c r="N51" s="40"/>
-      <c r="O51" s="63"/>
-      <c r="P51" s="63"/>
-      <c r="Q51" s="63"/>
-      <c r="R51" s="41"/>
-      <c r="S51" s="63"/>
-      <c r="T51" s="63"/>
-      <c r="U51" s="63"/>
-    </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B52" s="40"/>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="63"/>
-      <c r="G52" s="63"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="63"/>
-      <c r="M52" s="41"/>
-      <c r="N52" s="40"/>
-      <c r="O52" s="63"/>
-      <c r="P52" s="63"/>
-      <c r="Q52" s="63"/>
-      <c r="R52" s="41"/>
-      <c r="S52" s="63"/>
-      <c r="T52" s="63"/>
-      <c r="U52" s="63"/>
-    </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B53" s="40"/>
-      <c r="C53" s="63"/>
-      <c r="D53" s="63"/>
-      <c r="E53" s="63"/>
-      <c r="F53" s="63"/>
-      <c r="G53" s="63"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="63"/>
-      <c r="M53" s="41"/>
-      <c r="N53" s="40"/>
-      <c r="O53" s="63"/>
-      <c r="P53" s="63"/>
-      <c r="Q53" s="63"/>
-      <c r="R53" s="41"/>
-      <c r="S53" s="63"/>
-      <c r="T53" s="63"/>
-      <c r="U53" s="63"/>
-    </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B54" s="40"/>
-      <c r="C54" s="63"/>
-      <c r="D54" s="63"/>
-      <c r="E54" s="63"/>
-      <c r="F54" s="63"/>
-      <c r="G54" s="63"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="63"/>
-      <c r="M54" s="41"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="63"/>
-      <c r="P54" s="63"/>
-      <c r="Q54" s="63"/>
-      <c r="R54" s="41"/>
-      <c r="S54" s="63"/>
-      <c r="T54" s="63"/>
-      <c r="U54" s="63"/>
-    </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B55" s="40"/>
-      <c r="C55" s="63"/>
+    <row r="50" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B50" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F50" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G50" s="51" t="s">
+        <v>199</v>
+      </c>
+      <c r="H50" s="52">
+        <v>45979</v>
+      </c>
+      <c r="I50" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="J50" s="51">
+        <v>9075711219</v>
+      </c>
+      <c r="K50" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="L50" s="51"/>
+      <c r="M50" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="N50" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="O50" s="51" t="s">
+        <v>194</v>
+      </c>
+      <c r="P50" s="51">
+        <v>2828850582</v>
+      </c>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="53"/>
+      <c r="S50" s="51"/>
+      <c r="T50" s="51"/>
+      <c r="U50" s="51"/>
+    </row>
+    <row r="51" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B51" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D51" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F51" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G51" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H51" s="52">
+        <v>43584</v>
+      </c>
+      <c r="I51" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J51" s="51">
+        <v>15242251005</v>
+      </c>
+      <c r="K51" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="L51" s="62"/>
+      <c r="M51" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="O51" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P51" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="Q51" s="51"/>
+      <c r="R51" s="53"/>
+      <c r="S51" s="51"/>
+      <c r="T51" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U51" s="51"/>
+    </row>
+    <row r="52" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B52" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E52" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F52" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G52" s="51" t="s">
+        <v>103</v>
+      </c>
+      <c r="H52" s="52">
+        <v>43584</v>
+      </c>
+      <c r="I52" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J52" s="51">
+        <v>15242251005</v>
+      </c>
+      <c r="K52" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L52" s="62"/>
+      <c r="M52" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N52" s="50"/>
+      <c r="O52" s="51"/>
+      <c r="P52" s="51"/>
+      <c r="Q52" s="51"/>
+      <c r="R52" s="53"/>
+      <c r="S52" s="51"/>
+      <c r="T52" s="51"/>
+      <c r="U52" s="51"/>
+    </row>
+    <row r="53" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B53" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="45"/>
+      <c r="E53" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G53" s="62"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="J53" s="51">
+        <v>14119701002</v>
+      </c>
+      <c r="K53" s="51" t="s">
+        <v>168</v>
+      </c>
+      <c r="L53" s="62"/>
+      <c r="M53" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N53" s="50"/>
+      <c r="O53" s="51"/>
+      <c r="P53" s="51"/>
+      <c r="Q53" s="51"/>
+      <c r="R53" s="53"/>
+      <c r="S53" s="51"/>
+      <c r="T53" s="51"/>
+      <c r="U53" s="51"/>
+    </row>
+    <row r="54" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B54" s="44" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="D54" s="45"/>
+      <c r="E54" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="G54" s="62"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="J54" s="51">
+        <v>15242251005</v>
+      </c>
+      <c r="K54" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="L54" s="62"/>
+      <c r="M54" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N54" s="50"/>
+      <c r="O54" s="51"/>
+      <c r="P54" s="51"/>
+      <c r="Q54" s="51"/>
+      <c r="R54" s="53"/>
+      <c r="S54" s="51"/>
+      <c r="T54" s="51"/>
+      <c r="U54" s="51"/>
+    </row>
+    <row r="55" spans="2:21" s="82" customFormat="1" ht="30" x14ac:dyDescent="0.15">
+      <c r="B55" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" s="63" t="s">
+        <v>251</v>
+      </c>
       <c r="D55" s="63"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
+      <c r="E55" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" s="63" t="s">
+        <v>97</v>
+      </c>
       <c r="G55" s="63"/>
       <c r="H55" s="41"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="63"/>
-      <c r="M55" s="41"/>
+      <c r="I55" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="J55" s="63">
+        <v>14699681004</v>
+      </c>
+      <c r="K55" s="83" t="s">
+        <v>258</v>
+      </c>
+      <c r="L55" s="63"/>
+      <c r="M55" s="41" t="s">
+        <v>22</v>
+      </c>
       <c r="N55" s="40"/>
       <c r="O55" s="63"/>
       <c r="P55" s="63"/>
@@ -4433,37 +4715,94 @@
       <c r="T55" s="63"/>
       <c r="U55" s="63"/>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B56" s="40"/>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
-      <c r="E56" s="63"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="63"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="63"/>
-      <c r="M56" s="41"/>
-      <c r="N56" s="40"/>
-      <c r="O56" s="63"/>
-      <c r="P56" s="63"/>
-      <c r="Q56" s="63"/>
-      <c r="R56" s="41"/>
-      <c r="S56" s="63"/>
-      <c r="T56" s="63"/>
-      <c r="U56" s="63"/>
-    </row>
-    <row r="57" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B57" s="40"/>
-      <c r="C57" s="63"/>
+    <row r="56" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B56" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="D56" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="E56" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F56" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="G56" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="H56" s="52">
+        <v>45909</v>
+      </c>
+      <c r="I56" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="J56" s="51">
+        <v>13068821001</v>
+      </c>
+      <c r="K56" s="67" t="s">
+        <v>170</v>
+      </c>
+      <c r="L56" s="62"/>
+      <c r="M56" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="N56" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="O56" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56" s="51" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q56" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="R56" s="52">
+        <v>47469</v>
+      </c>
+      <c r="S56" s="51"/>
+      <c r="T56" s="51" t="s">
+        <v>89</v>
+      </c>
+      <c r="U56" s="51"/>
+    </row>
+    <row r="57" spans="2:21" ht="33.75" x14ac:dyDescent="0.15">
+      <c r="B57" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="C57" s="63" t="s">
+        <v>247</v>
+      </c>
       <c r="D57" s="63"/>
-      <c r="E57" s="63"/>
-      <c r="F57" s="63"/>
-      <c r="G57" s="63"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="63"/>
-      <c r="M57" s="41"/>
+      <c r="E57" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G57" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="H57" s="81">
+        <v>43883</v>
+      </c>
+      <c r="I57" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="J57" s="63">
+        <v>1158230639</v>
+      </c>
+      <c r="K57" s="83" t="s">
+        <v>257</v>
+      </c>
+      <c r="M57" s="41" t="s">
+        <v>201</v>
+      </c>
       <c r="N57" s="40"/>
       <c r="O57" s="63"/>
       <c r="P57" s="63"/>
@@ -4473,37 +4812,71 @@
       <c r="T57" s="63"/>
       <c r="U57" s="63"/>
     </row>
-    <row r="58" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B58" s="40"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="63"/>
-      <c r="E58" s="63"/>
-      <c r="F58" s="63"/>
-      <c r="G58" s="63"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="63"/>
-      <c r="M58" s="41"/>
-      <c r="N58" s="40"/>
-      <c r="O58" s="63"/>
-      <c r="P58" s="63"/>
-      <c r="Q58" s="63"/>
-      <c r="R58" s="41"/>
-      <c r="S58" s="63"/>
-      <c r="T58" s="63"/>
-      <c r="U58" s="63"/>
-    </row>
-    <row r="59" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B59" s="40"/>
-      <c r="C59" s="63"/>
+    <row r="58" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B58" s="47" t="s">
+        <v>269</v>
+      </c>
+      <c r="C58" s="48" t="s">
+        <v>290</v>
+      </c>
+      <c r="D58" s="48"/>
+      <c r="E58" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="G58" s="48"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="J58" s="48" t="s">
+        <v>292</v>
+      </c>
+      <c r="K58" s="48"/>
+      <c r="L58" s="48"/>
+      <c r="M58" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="N58" s="47"/>
+      <c r="O58" s="48"/>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="48"/>
+      <c r="R58" s="49"/>
+      <c r="S58" s="48"/>
+      <c r="T58" s="48"/>
+      <c r="U58" s="48"/>
+    </row>
+    <row r="59" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B59" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" s="63" t="s">
+        <v>181</v>
+      </c>
       <c r="D59" s="63"/>
-      <c r="E59" s="63"/>
-      <c r="F59" s="63"/>
-      <c r="G59" s="63"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="63"/>
-      <c r="M59" s="41"/>
+      <c r="E59" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G59" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="H59" s="81">
+        <v>44901</v>
+      </c>
+      <c r="I59" s="40" t="s">
+        <v>287</v>
+      </c>
+      <c r="J59" s="63">
+        <v>3185110214</v>
+      </c>
+      <c r="M59" s="41" t="s">
+        <v>294</v>
+      </c>
       <c r="N59" s="40"/>
       <c r="O59" s="63"/>
       <c r="P59" s="63"/>
@@ -4513,57 +4886,131 @@
       <c r="T59" s="63"/>
       <c r="U59" s="63"/>
     </row>
-    <row r="60" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B60" s="40"/>
-      <c r="C60" s="63"/>
+    <row r="60" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B60" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="C60" s="63" t="s">
+        <v>162</v>
+      </c>
       <c r="D60" s="63"/>
-      <c r="E60" s="63"/>
-      <c r="F60" s="63"/>
-      <c r="G60" s="63"/>
-      <c r="H60" s="41"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="63"/>
-      <c r="M60" s="41"/>
-      <c r="N60" s="40"/>
-      <c r="O60" s="63"/>
-      <c r="P60" s="63"/>
+      <c r="E60" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G60" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="H60" s="81">
+        <v>45825</v>
+      </c>
+      <c r="I60" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="J60" s="63">
+        <v>6575701005</v>
+      </c>
+      <c r="M60" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="N60" s="40" t="s">
+        <v>282</v>
+      </c>
+      <c r="O60" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="P60" s="63">
+        <v>8822460963</v>
+      </c>
       <c r="Q60" s="63"/>
       <c r="R60" s="41"/>
       <c r="S60" s="63"/>
       <c r="T60" s="63"/>
       <c r="U60" s="63"/>
     </row>
-    <row r="61" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B61" s="40"/>
-      <c r="C61" s="63"/>
+    <row r="61" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B61" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="63" t="s">
+        <v>162</v>
+      </c>
       <c r="D61" s="63"/>
-      <c r="E61" s="63"/>
-      <c r="F61" s="63"/>
-      <c r="G61" s="63"/>
-      <c r="H61" s="41"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="63"/>
-      <c r="M61" s="41"/>
-      <c r="N61" s="40"/>
-      <c r="O61" s="63"/>
-      <c r="P61" s="63"/>
-      <c r="Q61" s="63"/>
-      <c r="R61" s="41"/>
+      <c r="E61" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G61" s="63" t="s">
+        <v>270</v>
+      </c>
+      <c r="H61" s="81">
+        <v>46084</v>
+      </c>
+      <c r="I61" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="J61" s="63">
+        <v>13068821001</v>
+      </c>
+      <c r="M61" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N61" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="O61" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="P61" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q61" s="63" t="s">
+        <v>126</v>
+      </c>
+      <c r="R61" s="81">
+        <v>46790</v>
+      </c>
       <c r="S61" s="63"/>
       <c r="T61" s="63"/>
       <c r="U61" s="63"/>
     </row>
-    <row r="62" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B62" s="40"/>
-      <c r="C62" s="63"/>
+    <row r="62" spans="2:21" s="82" customFormat="1" ht="33.75" x14ac:dyDescent="0.15">
+      <c r="B62" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="C62" s="63" t="s">
+        <v>242</v>
+      </c>
       <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="41"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="63"/>
-      <c r="M62" s="41"/>
+      <c r="E62" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="F62" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="G62" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="H62" s="81">
+        <v>46384</v>
+      </c>
+      <c r="I62" s="40" t="s">
+        <v>244</v>
+      </c>
+      <c r="J62" s="63">
+        <v>17702651005</v>
+      </c>
+      <c r="K62" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="L62" s="63"/>
+      <c r="M62" s="41" t="s">
+        <v>245</v>
+      </c>
       <c r="N62" s="40"/>
       <c r="O62" s="63"/>
       <c r="P62" s="63"/>
@@ -4633,26 +5080,6 @@
       <c r="T65" s="63"/>
       <c r="U65" s="63"/>
     </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B66" s="40"/>
-      <c r="C66" s="63"/>
-      <c r="D66" s="63"/>
-      <c r="E66" s="63"/>
-      <c r="F66" s="63"/>
-      <c r="G66" s="63"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="40"/>
-      <c r="J66" s="63"/>
-      <c r="M66" s="41"/>
-      <c r="N66" s="40"/>
-      <c r="O66" s="63"/>
-      <c r="P66" s="63"/>
-      <c r="Q66" s="63"/>
-      <c r="R66" s="41"/>
-      <c r="S66" s="63"/>
-      <c r="T66" s="63"/>
-      <c r="U66" s="63"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/prospetto_mezzi.xlsx
+++ b/prospetto_mezzi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mario\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392D0AE0-99A7-42FF-AAE4-2B38825248EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDC350B-CE45-4856-9D5E-7CEE99FEE717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{63F5E9A3-0BF8-43C0-B158-766C2F1F4E49}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="335">
   <si>
     <t>EL706PT</t>
   </si>
@@ -274,9 +274,6 @@
     <t>PORTI DI ROMA SOC. COOP.</t>
   </si>
   <si>
-    <t>DZ969VD</t>
-  </si>
-  <si>
     <t>ER572RD</t>
   </si>
   <si>
@@ -382,15 +379,6 @@
     <t>GBBLRT49R07C773A</t>
   </si>
   <si>
-    <t>LIC.2 COMUNE FILIANO</t>
-  </si>
-  <si>
-    <t>BASTIANELLI GIAN MARCO</t>
-  </si>
-  <si>
-    <t>BSTGMR92P30C773G</t>
-  </si>
-  <si>
     <t>VESPUCCI TOURS</t>
   </si>
   <si>
@@ -451,9 +439,6 @@
     <t>RM8230801</t>
   </si>
   <si>
-    <t>NO LICENZA</t>
-  </si>
-  <si>
     <t>LIC.040/05 COMUNE COMISO</t>
   </si>
   <si>
@@ -566,9 +551,6 @@
   </si>
   <si>
     <t>OPEL ADAM</t>
-  </si>
-  <si>
-    <t>LIC.1 COMUNE CARAGLIO</t>
   </si>
   <si>
     <t>CHATO ROMERO WILIAN FABIAN</t>
@@ -1774,10 +1756,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B1:U71" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
-  <autoFilter ref="B1:U71" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:U71">
-    <sortCondition ref="B1:B71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}" name="Tabella1" displayName="Tabella1" ref="B1:U70" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
+  <autoFilter ref="B1:U70" xr:uid="{098D25CA-7D73-487D-9947-96C01FB54397}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:U70">
+    <sortCondition ref="B1:B70"/>
   </sortState>
   <tableColumns count="20">
     <tableColumn id="2" xr3:uid="{779EAAEE-59A7-446B-AD7C-6F7003AD1695}" name="TARGA" dataDxfId="19"/>
@@ -2466,7 +2448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56392095-0261-4957-A1EF-F42F71E397DD}">
-  <dimension ref="A1:U71"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="53"/>
@@ -2499,46 +2481,46 @@
         <v>63</v>
       </c>
       <c r="E1" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>96</v>
-      </c>
       <c r="G1" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H1" s="32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I1" s="30" t="s">
         <v>64</v>
       </c>
       <c r="J1" s="31" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="K1" s="31" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="L1" s="31" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M1" s="32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="N1" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O1" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="P1" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q1" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="R1" s="32" t="s">
         <v>128</v>
-      </c>
-      <c r="P1" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q1" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>132</v>
       </c>
       <c r="S1" s="54" t="s">
         <v>65</v>
@@ -2552,34 +2534,34 @@
     </row>
     <row r="2" spans="2:21" s="55" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G2" s="41"/>
       <c r="H2" s="42"/>
       <c r="I2" s="40" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="J2" s="41" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="K2" s="41" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="L2" s="41"/>
       <c r="M2" s="42" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="N2" s="40"/>
       <c r="O2" s="41"/>
@@ -2592,30 +2574,30 @@
     </row>
     <row r="3" spans="2:21" s="55" customFormat="1" ht="45" x14ac:dyDescent="0.15">
       <c r="B3" s="61" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C3" s="62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D3" s="62"/>
       <c r="E3" s="62" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="62" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H3" s="63"/>
       <c r="I3" s="61" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="J3" s="62">
         <v>12838081003</v>
       </c>
       <c r="K3" s="67" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L3" s="62"/>
       <c r="M3" s="63" t="s">
@@ -2637,25 +2619,25 @@
         <v>46</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D4" s="41"/>
       <c r="E4" s="41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G4" s="54"/>
       <c r="H4" s="34"/>
       <c r="I4" s="43" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="J4" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="K4" s="44" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="L4" s="47">
         <v>46766</v>
@@ -2674,32 +2656,32 @@
     </row>
     <row r="5" spans="2:21" s="57" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B5" s="40" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D5" s="41"/>
       <c r="E5" s="41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G5" s="41"/>
       <c r="H5" s="42"/>
       <c r="I5" s="61" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="J5" s="62" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="K5" s="62" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="L5" s="62"/>
       <c r="M5" s="63" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="N5" s="40"/>
       <c r="O5" s="41"/>
@@ -2714,25 +2696,25 @@
     </row>
     <row r="6" spans="2:21" s="57" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" s="40" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" s="41"/>
       <c r="E6" s="41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" s="41"/>
       <c r="H6" s="42"/>
       <c r="I6" s="40" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="J6" s="41" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K6" s="41"/>
       <c r="L6" s="41"/>
@@ -2753,14 +2735,14 @@
         <v>70</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" s="38"/>
       <c r="E7" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G7" s="54"/>
       <c r="H7" s="34"/>
@@ -2771,7 +2753,7 @@
         <v>15242251005</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L7" s="54"/>
       <c r="M7" s="39" t="s">
@@ -2788,28 +2770,28 @@
     </row>
     <row r="8" spans="2:21" s="56" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B8" s="33" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C8" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D8" s="54"/>
       <c r="E8" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F8" s="54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G8" s="54"/>
       <c r="H8" s="34"/>
       <c r="I8" s="33" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="J8" s="54">
         <v>14699681004</v>
       </c>
       <c r="K8" s="68" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L8" s="54"/>
       <c r="M8" s="34" t="s">
@@ -2826,25 +2808,25 @@
     </row>
     <row r="9" spans="2:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B9" s="40" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D9" s="41"/>
       <c r="E9" s="41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G9" s="41"/>
       <c r="H9" s="42"/>
       <c r="I9" s="40" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="K9" s="41"/>
       <c r="L9" s="41"/>
@@ -2865,47 +2847,43 @@
         <v>17</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D10" s="44" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E10" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F10" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="H10" s="45">
-        <v>45787</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G10" s="44"/>
+      <c r="H10" s="45"/>
       <c r="I10" s="43" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J10" s="44">
         <v>13068821001</v>
       </c>
       <c r="K10" s="44" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L10" s="54"/>
       <c r="M10" s="46" t="s">
         <v>22</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="O10" s="44" t="s">
         <v>22</v>
       </c>
       <c r="P10" s="44" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="Q10" s="44" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="R10" s="45">
         <v>47200</v>
@@ -2919,14 +2897,14 @@
         <v>71</v>
       </c>
       <c r="C11" s="38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D11" s="38"/>
       <c r="E11" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G11" s="54"/>
       <c r="H11" s="34"/>
@@ -2937,7 +2915,7 @@
         <v>15242251005</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L11" s="54"/>
       <c r="M11" s="39" t="s">
@@ -2952,88 +2930,80 @@
       <c r="T11" s="38"/>
       <c r="U11" s="38"/>
     </row>
-    <row r="12" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B12" s="43" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="44" t="s">
-        <v>77</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="D12" s="44"/>
       <c r="E12" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F12" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="45">
-        <v>40497</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G12" s="54"/>
+      <c r="H12" s="34"/>
       <c r="I12" s="43" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="J12" s="44">
-        <v>12611021002</v>
+        <v>14119701002</v>
       </c>
       <c r="K12" s="58" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="L12" s="54"/>
-      <c r="M12" s="46" t="s">
+      <c r="M12" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="O12" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="44" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q12" s="44" t="s">
-        <v>138</v>
-      </c>
+      <c r="N12" s="43"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="44"/>
       <c r="R12" s="46"/>
       <c r="S12" s="44"/>
-      <c r="T12" s="44" t="s">
-        <v>89</v>
-      </c>
+      <c r="T12" s="44"/>
       <c r="U12" s="44"/>
     </row>
     <row r="13" spans="2:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B13" s="43" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C13" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="54"/>
-      <c r="H13" s="34"/>
+      <c r="G13" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="45">
+        <v>41932</v>
+      </c>
       <c r="I13" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="J13" s="44">
-        <v>14119701002</v>
-      </c>
-      <c r="K13" s="58" t="s">
-        <v>168</v>
-      </c>
-      <c r="L13" s="54"/>
-      <c r="M13" s="34" t="s">
-        <v>22</v>
+        <v>135</v>
+      </c>
+      <c r="J13" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="K13" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="L13" s="47">
+        <v>47246</v>
+      </c>
+      <c r="M13" s="46" t="s">
+        <v>138</v>
       </c>
       <c r="N13" s="43"/>
       <c r="O13" s="44"/>
@@ -3041,769 +3011,767 @@
       <c r="Q13" s="44"/>
       <c r="R13" s="46"/>
       <c r="S13" s="44"/>
-      <c r="T13" s="44"/>
+      <c r="T13" s="44" t="s">
+        <v>88</v>
+      </c>
       <c r="U13" s="44"/>
     </row>
-    <row r="14" spans="2:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B14" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="44" t="s">
+    <row r="14" spans="2:21" s="56" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B14" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>139</v>
-      </c>
-      <c r="H14" s="45">
-        <v>41932</v>
-      </c>
-      <c r="I14" s="43" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="K14" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="L14" s="47">
-        <v>47246</v>
-      </c>
-      <c r="M14" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="N14" s="43"/>
-      <c r="O14" s="44"/>
-      <c r="P14" s="44"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="46"/>
-      <c r="S14" s="44"/>
-      <c r="T14" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="U14" s="44"/>
-    </row>
-    <row r="15" spans="2:21" s="56" customFormat="1" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B15" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="41" t="s">
+      <c r="D14" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="54"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" s="41">
+        <v>7131491008</v>
+      </c>
+      <c r="K14" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="L14" s="54"/>
+      <c r="M14" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="N14" s="40"/>
+      <c r="O14" s="41"/>
+      <c r="P14" s="41"/>
+      <c r="Q14" s="41"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="41"/>
+      <c r="T14" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="U14" s="41"/>
+    </row>
+    <row r="15" spans="2:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="44"/>
+      <c r="E15" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="54"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="J15" s="41">
-        <v>7131491008</v>
-      </c>
-      <c r="K15" s="59" t="s">
-        <v>13</v>
+      <c r="G15" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="45">
+        <v>43179</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="44">
+        <v>15242251005</v>
+      </c>
+      <c r="K15" s="44" t="s">
+        <v>164</v>
       </c>
       <c r="L15" s="54"/>
-      <c r="M15" s="42" t="s">
-        <v>173</v>
-      </c>
-      <c r="N15" s="40"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="U15" s="41"/>
+      <c r="M15" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" s="43"/>
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="44"/>
+      <c r="T15" s="44"/>
+      <c r="U15" s="44"/>
     </row>
     <row r="16" spans="2:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B16" s="43" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="44"/>
+        <v>182</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>183</v>
+      </c>
       <c r="E16" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G16" s="44" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="H16" s="45">
-        <v>43179</v>
+        <v>42065</v>
       </c>
       <c r="I16" s="43" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="J16" s="44">
-        <v>15242251005</v>
-      </c>
-      <c r="K16" s="44" t="s">
-        <v>169</v>
+        <v>12611021002</v>
+      </c>
+      <c r="K16" s="58" t="s">
+        <v>165</v>
       </c>
       <c r="L16" s="54"/>
       <c r="M16" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="43"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="44"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="46"/>
+      <c r="N16" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="O16" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q16" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="R16" s="46" t="s">
+        <v>185</v>
+      </c>
       <c r="S16" s="44"/>
       <c r="T16" s="44"/>
       <c r="U16" s="44"/>
     </row>
     <row r="17" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B17" s="43" t="s">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="44" t="s">
-        <v>189</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="D17" s="44"/>
       <c r="E17" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F17" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G17" s="44" t="s">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="H17" s="45">
-        <v>42065</v>
+        <v>45387</v>
       </c>
       <c r="I17" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="J17" s="44">
-        <v>12611021002</v>
-      </c>
-      <c r="K17" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="L17" s="54"/>
+        <v>110</v>
+      </c>
+      <c r="J17" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="K17" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="L17" s="47">
+        <v>46315</v>
+      </c>
       <c r="M17" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="43" t="s">
-        <v>186</v>
-      </c>
-      <c r="O17" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="P17" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q17" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="R17" s="46" t="s">
-        <v>191</v>
-      </c>
+      <c r="N17" s="43"/>
+      <c r="O17" s="44"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="46"/>
       <c r="S17" s="44"/>
-      <c r="T17" s="44"/>
+      <c r="T17" s="44" t="s">
+        <v>88</v>
+      </c>
       <c r="U17" s="44"/>
     </row>
     <row r="18" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B18" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="H18" s="45">
-        <v>45387</v>
-      </c>
+      <c r="B18" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G18" s="54"/>
+      <c r="H18" s="34"/>
       <c r="I18" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="J18" s="44" t="s">
-        <v>112</v>
-      </c>
-      <c r="K18" s="44" t="s">
-        <v>131</v>
-      </c>
-      <c r="L18" s="47">
-        <v>46315</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="J18" s="44">
+        <v>13068821001</v>
+      </c>
+      <c r="K18" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="L18" s="54"/>
       <c r="M18" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N18" s="43"/>
-      <c r="O18" s="44"/>
-      <c r="P18" s="44"/>
-      <c r="Q18" s="44"/>
-      <c r="R18" s="46"/>
+      <c r="N18" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="O18" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P18" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q18" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="R18" s="45">
+        <v>46790</v>
+      </c>
       <c r="S18" s="44"/>
       <c r="T18" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U18" s="44"/>
     </row>
     <row r="19" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B19" s="37" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" s="38" t="s">
+      <c r="B19" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="D19" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="54"/>
-      <c r="H19" s="34"/>
+      <c r="G19" s="44" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" s="45">
+        <v>43284</v>
+      </c>
       <c r="I19" s="43" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="J19" s="44">
-        <v>13068821001</v>
-      </c>
-      <c r="K19" s="58" t="s">
-        <v>170</v>
+        <v>15242251005</v>
+      </c>
+      <c r="K19" s="44" t="s">
+        <v>164</v>
       </c>
       <c r="L19" s="54"/>
       <c r="M19" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="O19" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="P19" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q19" s="44" t="s">
-        <v>126</v>
-      </c>
-      <c r="R19" s="45">
-        <v>46790</v>
-      </c>
+      <c r="N19" s="43"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+      <c r="R19" s="46"/>
       <c r="S19" s="44"/>
-      <c r="T19" s="44" t="s">
-        <v>89</v>
-      </c>
+      <c r="T19" s="44"/>
       <c r="U19" s="44"/>
     </row>
     <row r="20" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B20" s="43" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="44"/>
+        <v>129</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>170</v>
+      </c>
       <c r="E20" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G20" s="44" t="s">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="H20" s="45">
-        <v>43284</v>
+        <v>45084</v>
       </c>
       <c r="I20" s="43" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="J20" s="44">
-        <v>15242251005</v>
-      </c>
-      <c r="K20" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="L20" s="54"/>
+        <v>13068821001</v>
+      </c>
+      <c r="K20" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="L20" s="44"/>
       <c r="M20" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N20" s="43"/>
-      <c r="O20" s="44"/>
-      <c r="P20" s="44"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="46"/>
+      <c r="N20" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="O20" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P20" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q20" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="R20" s="45">
+        <v>46568</v>
+      </c>
       <c r="S20" s="44"/>
       <c r="T20" s="44"/>
       <c r="U20" s="44"/>
     </row>
     <row r="21" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B21" s="43" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="E21" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G21" s="44" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="H21" s="45">
-        <v>45084</v>
+        <v>41404</v>
       </c>
       <c r="I21" s="43" t="s">
-        <v>122</v>
+        <v>152</v>
       </c>
       <c r="J21" s="44">
-        <v>13068821001</v>
+        <v>12578741006</v>
       </c>
       <c r="K21" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="L21" s="44"/>
+        <v>164</v>
+      </c>
+      <c r="L21" s="54"/>
       <c r="M21" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N21" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="O21" s="44" t="s">
+      <c r="N21" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="O21" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="P21" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q21" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="R21" s="45">
-        <v>46568</v>
-      </c>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
-      <c r="U21" s="44"/>
-    </row>
-    <row r="22" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="P21" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q21" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="R21" s="48">
+        <v>44044</v>
+      </c>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="U21" s="36"/>
+    </row>
+    <row r="22" spans="1:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B22" s="43" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C22" s="44" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E22" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G22" s="44" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="H22" s="45">
-        <v>41404</v>
+        <v>42809</v>
       </c>
       <c r="I22" s="43" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="J22" s="44">
-        <v>12578741006</v>
+        <v>13068821001</v>
       </c>
       <c r="K22" s="58" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="L22" s="54"/>
       <c r="M22" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N22" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="O22" s="36" t="s">
+      <c r="N22" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="O22" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="P22" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q22" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="R22" s="48">
-        <v>44044</v>
-      </c>
-      <c r="S22" s="36"/>
-      <c r="T22" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="U22" s="36"/>
-    </row>
-    <row r="23" spans="1:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B23" s="43" t="s">
-        <v>91</v>
+      <c r="P22" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q22" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="R22" s="45">
+        <v>46766</v>
+      </c>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="U22" s="44"/>
+    </row>
+    <row r="23" spans="1:21" s="56" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="50"/>
+      <c r="B23" s="44" t="s">
+        <v>26</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E23" s="44" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="F23" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="45">
+        <v>42423</v>
+      </c>
+      <c r="I23" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="J23" s="41">
+        <v>7988341009</v>
+      </c>
+      <c r="K23" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="L23" s="54"/>
+      <c r="M23" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="N23" s="44"/>
+      <c r="O23" s="44"/>
+      <c r="P23" s="44"/>
+      <c r="Q23" s="44"/>
+      <c r="R23" s="46"/>
+      <c r="S23" s="44"/>
+      <c r="T23" s="44"/>
+      <c r="U23" s="44"/>
+    </row>
+    <row r="24" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B24" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="54"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="K24" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="L24" s="47">
+        <v>46766</v>
+      </c>
+      <c r="M24" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="33"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="54"/>
+      <c r="R24" s="34"/>
+      <c r="S24" s="54"/>
+      <c r="T24" s="54"/>
+      <c r="U24" s="54"/>
+    </row>
+    <row r="25" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="50"/>
+      <c r="B25" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="H25" s="63"/>
+      <c r="I25" s="61" t="s">
+        <v>225</v>
+      </c>
+      <c r="J25" s="62">
+        <v>11767131003</v>
+      </c>
+      <c r="K25" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="L25" s="62"/>
+      <c r="M25" s="63" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="61"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="62"/>
+      <c r="Q25" s="62"/>
+      <c r="R25" s="63"/>
+      <c r="S25" s="62"/>
+      <c r="T25" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="U25" s="62"/>
+    </row>
+    <row r="26" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="49"/>
+      <c r="B26" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="C26" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="54"/>
+      <c r="E26" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="54"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="J26" s="54">
+        <v>18064001003</v>
+      </c>
+      <c r="M26" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="N26" s="33"/>
+      <c r="O26" s="54"/>
+      <c r="P26" s="54"/>
+      <c r="Q26" s="54"/>
+      <c r="R26" s="34"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="54"/>
+      <c r="U26" s="54"/>
+    </row>
+    <row r="27" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="49"/>
+      <c r="B27" s="41" t="s">
+        <v>229</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G27" s="41"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="40" t="s">
+        <v>240</v>
+      </c>
+      <c r="J27" s="41">
+        <v>17833641008</v>
+      </c>
+      <c r="K27" s="68" t="s">
+        <v>253</v>
+      </c>
+      <c r="L27" s="41"/>
+      <c r="M27" s="42" t="s">
+        <v>188</v>
+      </c>
+      <c r="N27" s="40"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+    </row>
+    <row r="28" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B28" s="71" t="s">
+        <v>308</v>
+      </c>
+      <c r="C28" s="72" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="72" t="s">
+        <v>96</v>
+      </c>
+      <c r="G28" s="72"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="J28" s="72" t="s">
+        <v>322</v>
+      </c>
+      <c r="K28" s="72" t="s">
+        <v>329</v>
+      </c>
+      <c r="L28" s="74">
+        <v>47122</v>
+      </c>
+      <c r="M28" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" s="71"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="73"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="72"/>
+    </row>
+    <row r="29" spans="1:21" s="60" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B29" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="C29" s="54" t="s">
         <v>100</v>
       </c>
-      <c r="G23" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="H23" s="45">
-        <v>42809</v>
-      </c>
-      <c r="I23" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="J23" s="44">
-        <v>13068821001</v>
-      </c>
-      <c r="K23" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="L23" s="54"/>
-      <c r="M23" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N23" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="O23" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="P23" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q23" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="R23" s="45">
-        <v>46766</v>
-      </c>
-      <c r="S23" s="44"/>
-      <c r="T23" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="U23" s="44"/>
-    </row>
-    <row r="24" spans="1:21" s="56" customFormat="1" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>181</v>
-      </c>
-      <c r="D24" s="44" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="F24" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="H24" s="45">
-        <v>42423</v>
-      </c>
-      <c r="I24" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="J24" s="41">
-        <v>7988341009</v>
-      </c>
-      <c r="K24" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="L24" s="54"/>
-      <c r="M24" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="N24" s="44"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="44"/>
-      <c r="R24" s="46"/>
-      <c r="S24" s="44"/>
-      <c r="T24" s="44"/>
-      <c r="U24" s="44"/>
-    </row>
-    <row r="25" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B25" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="54"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="J25" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="L25" s="47">
-        <v>46766</v>
-      </c>
-      <c r="M25" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" s="33"/>
-      <c r="O25" s="54"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="54"/>
-      <c r="R25" s="34"/>
-      <c r="S25" s="54"/>
-      <c r="T25" s="54"/>
-      <c r="U25" s="54"/>
-    </row>
-    <row r="26" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
-      <c r="B26" s="62" t="s">
-        <v>221</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="D26" s="62"/>
-      <c r="E26" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26" s="62" t="s">
-        <v>232</v>
-      </c>
-      <c r="H26" s="63"/>
-      <c r="I26" s="61" t="s">
-        <v>231</v>
-      </c>
-      <c r="J26" s="62">
-        <v>11767131003</v>
-      </c>
-      <c r="K26" s="68" t="s">
-        <v>170</v>
-      </c>
-      <c r="L26" s="62"/>
-      <c r="M26" s="63" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="61"/>
-      <c r="O26" s="62"/>
-      <c r="P26" s="62"/>
-      <c r="Q26" s="62"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="62"/>
-      <c r="T26" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="U26" s="62"/>
-    </row>
-    <row r="27" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="49"/>
-      <c r="B27" s="54" t="s">
-        <v>266</v>
-      </c>
-      <c r="C27" s="54" t="s">
-        <v>284</v>
-      </c>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="G27" s="54"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="J27" s="54">
+      <c r="D29" s="54"/>
+      <c r="E29" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="G29" s="54"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="J29" s="54">
         <v>18064001003</v>
       </c>
-      <c r="M27" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="N27" s="33"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="54"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-    </row>
-    <row r="28" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="49"/>
-      <c r="B28" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="41"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="J28" s="41">
-        <v>17833641008</v>
-      </c>
-      <c r="K28" s="68" t="s">
-        <v>259</v>
-      </c>
-      <c r="L28" s="41"/>
-      <c r="M28" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="N28" s="40"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="41"/>
-    </row>
-    <row r="29" spans="1:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="B29" s="71" t="s">
-        <v>314</v>
-      </c>
-      <c r="C29" s="72" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" s="72"/>
-      <c r="E29" s="72" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="72" t="s">
-        <v>97</v>
-      </c>
-      <c r="G29" s="72"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="71" t="s">
-        <v>327</v>
-      </c>
-      <c r="J29" s="72" t="s">
-        <v>328</v>
-      </c>
-      <c r="K29" s="72" t="s">
-        <v>335</v>
-      </c>
-      <c r="L29" s="74">
-        <v>47122</v>
-      </c>
-      <c r="M29" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="N29" s="71"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="72"/>
-      <c r="Q29" s="72"/>
-      <c r="R29" s="73"/>
-      <c r="S29" s="72"/>
-      <c r="T29" s="72"/>
-      <c r="U29" s="72"/>
-    </row>
-    <row r="30" spans="1:21" s="60" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="N29" s="33"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="34"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="54"/>
+    </row>
+    <row r="30" spans="1:21" s="56" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="33" t="s">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="C30" s="54" t="s">
-        <v>101</v>
+        <v>236</v>
       </c>
       <c r="D30" s="54"/>
       <c r="E30" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F30" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="54"/>
-      <c r="H30" s="34"/>
+        <v>99</v>
+      </c>
+      <c r="G30" s="54" t="s">
+        <v>326</v>
+      </c>
+      <c r="H30" s="66">
+        <v>44949</v>
+      </c>
       <c r="I30" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="J30" s="54">
-        <v>18064001003</v>
-      </c>
-      <c r="K30" s="54"/>
-      <c r="L30" s="54"/>
+        <v>327</v>
+      </c>
+      <c r="J30" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="K30" s="54" t="s">
+        <v>334</v>
+      </c>
+      <c r="L30" s="75">
+        <v>46644</v>
+      </c>
       <c r="M30" s="34" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="N30" s="33"/>
       <c r="O30" s="54"/>
@@ -3814,262 +3782,262 @@
       <c r="T30" s="54"/>
       <c r="U30" s="54"/>
     </row>
-    <row r="31" spans="1:21" s="56" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B31" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="D31" s="54"/>
-      <c r="E31" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="54" t="s">
-        <v>332</v>
-      </c>
-      <c r="H31" s="66">
-        <v>44949</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="J31" s="54" t="s">
-        <v>334</v>
-      </c>
-      <c r="K31" s="54" t="s">
-        <v>340</v>
-      </c>
-      <c r="L31" s="75">
-        <v>46644</v>
-      </c>
-      <c r="M31" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="N31" s="33"/>
-      <c r="O31" s="54"/>
-      <c r="P31" s="54"/>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="54"/>
-      <c r="U31" s="54"/>
-    </row>
-    <row r="32" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B32" s="61" t="s">
+    <row r="31" spans="1:21" s="56" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B31" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="62" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="G31" s="62" t="s">
+        <v>203</v>
+      </c>
+      <c r="H31" s="64">
+        <v>41592</v>
+      </c>
+      <c r="I31" s="61" t="s">
         <v>204</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="J31" s="62" t="s">
+        <v>205</v>
+      </c>
+      <c r="K31" s="62" t="s">
         <v>207</v>
       </c>
-      <c r="D32" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="E32" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="G32" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="H32" s="64">
-        <v>41592</v>
-      </c>
-      <c r="I32" s="61" t="s">
+      <c r="L31" s="62"/>
+      <c r="M31" s="63" t="s">
+        <v>206</v>
+      </c>
+      <c r="N31" s="61"/>
+      <c r="O31" s="62"/>
+      <c r="P31" s="62"/>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="63"/>
+      <c r="S31" s="62"/>
+      <c r="T31" s="62"/>
+      <c r="U31" s="62"/>
+    </row>
+    <row r="32" spans="1:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B32" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G32" s="54"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="J32" s="41" t="s">
+        <v>113</v>
+      </c>
+      <c r="K32" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="J32" s="62" t="s">
-        <v>211</v>
-      </c>
-      <c r="K32" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="L32" s="62"/>
-      <c r="M32" s="63" t="s">
+      <c r="L32" s="54"/>
+      <c r="M32" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" s="40"/>
+      <c r="O32" s="41"/>
+      <c r="P32" s="41"/>
+      <c r="Q32" s="41"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="41"/>
+      <c r="T32" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="U32" s="41"/>
+    </row>
+    <row r="33" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B33" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G33" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="H33" s="45">
+        <v>42426</v>
+      </c>
+      <c r="I33" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="J33" s="44">
+        <v>13068821001</v>
+      </c>
+      <c r="K33" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="L33" s="54"/>
+      <c r="M33" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="43" t="s">
+        <v>145</v>
+      </c>
+      <c r="O33" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q33" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="R33" s="45">
+        <v>46854</v>
+      </c>
+      <c r="S33" s="44"/>
+      <c r="T33" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="U33" s="44"/>
+    </row>
+    <row r="34" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B34" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="N32" s="61"/>
-      <c r="O32" s="62"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="62"/>
-      <c r="R32" s="63"/>
-      <c r="S32" s="62"/>
-      <c r="T32" s="62"/>
-      <c r="U32" s="62"/>
-    </row>
-    <row r="33" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B33" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="41" t="s">
+      <c r="C34" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G34" s="41"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="J34" s="41">
+        <v>12838081003</v>
+      </c>
+      <c r="K34" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="L34" s="41"/>
+      <c r="M34" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="N34" s="40"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="U34" s="41"/>
+    </row>
+    <row r="35" spans="2:21" s="52" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B35" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="H35" s="66">
+        <v>45394</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="54">
+        <v>13068821001</v>
+      </c>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="33"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="34"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="54"/>
+    </row>
+    <row r="36" spans="2:21" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B36" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="C36" s="54" t="s">
         <v>98</v>
-      </c>
-      <c r="D33" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" s="54"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="J33" s="41" t="s">
-        <v>114</v>
-      </c>
-      <c r="K33" s="41" t="s">
-        <v>216</v>
-      </c>
-      <c r="L33" s="54"/>
-      <c r="M33" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="N33" s="40"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="U33" s="41"/>
-    </row>
-    <row r="34" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B34" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E34" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F34" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G34" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="H34" s="45">
-        <v>42426</v>
-      </c>
-      <c r="I34" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="J34" s="44">
-        <v>13068821001</v>
-      </c>
-      <c r="K34" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="L34" s="54"/>
-      <c r="M34" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N34" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="O34" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="P34" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q34" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="R34" s="45">
-        <v>46854</v>
-      </c>
-      <c r="S34" s="44"/>
-      <c r="T34" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="U34" s="44"/>
-    </row>
-    <row r="35" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B35" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>226</v>
-      </c>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G35" s="41"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="40" t="s">
-        <v>227</v>
-      </c>
-      <c r="J35" s="41">
-        <v>12838081003</v>
-      </c>
-      <c r="K35" s="68" t="s">
-        <v>170</v>
-      </c>
-      <c r="L35" s="41"/>
-      <c r="M35" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="N35" s="40"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
-      <c r="S35" s="41"/>
-      <c r="T35" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="U35" s="41"/>
-    </row>
-    <row r="36" spans="2:21" s="52" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B36" s="33" t="s">
-        <v>264</v>
-      </c>
-      <c r="C36" s="54" t="s">
-        <v>207</v>
       </c>
       <c r="D36" s="54"/>
       <c r="E36" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F36" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G36" s="54" t="s">
-        <v>278</v>
+        <v>307</v>
       </c>
       <c r="H36" s="66">
-        <v>45394</v>
+        <v>40148</v>
       </c>
       <c r="I36" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="J36" s="54">
-        <v>13068821001</v>
-      </c>
-      <c r="K36" s="54"/>
-      <c r="L36" s="54"/>
+        <v>310</v>
+      </c>
+      <c r="J36" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="K36" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="L36" s="75">
+        <v>47654</v>
+      </c>
       <c r="M36" s="34" t="s">
-        <v>22</v>
+        <v>188</v>
       </c>
       <c r="N36" s="33"/>
       <c r="O36" s="54"/>
@@ -4080,183 +4048,184 @@
       <c r="T36" s="54"/>
       <c r="U36" s="54"/>
     </row>
-    <row r="37" spans="2:21" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B37" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="C37" s="54" t="s">
+    <row r="37" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B37" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G37" s="54" t="s">
-        <v>313</v>
-      </c>
-      <c r="H37" s="66">
-        <v>40148</v>
-      </c>
-      <c r="I37" s="33" t="s">
-        <v>316</v>
-      </c>
-      <c r="J37" s="54" t="s">
-        <v>315</v>
-      </c>
-      <c r="K37" s="54" t="s">
-        <v>336</v>
-      </c>
-      <c r="L37" s="75">
-        <v>47654</v>
-      </c>
-      <c r="M37" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="N37" s="33"/>
-      <c r="O37" s="54"/>
-      <c r="P37" s="54"/>
-      <c r="Q37" s="54"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="54"/>
-      <c r="T37" s="54"/>
-      <c r="U37" s="54"/>
-    </row>
-    <row r="38" spans="2:21" s="65" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B38" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>207</v>
-      </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F38" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="H38" s="69">
+      <c r="G37" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="H37" s="69">
         <v>45701</v>
       </c>
-      <c r="I38" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="J38" s="41">
+      <c r="I37" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="J37" s="41">
         <v>12578741006</v>
       </c>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="42" t="s">
+      <c r="K37" s="41"/>
+      <c r="L37" s="41"/>
+      <c r="M37" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="N38" s="40" t="s">
+      <c r="N37" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="O37" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="P37" s="41" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q37" s="41" t="s">
+        <v>156</v>
+      </c>
+      <c r="R37" s="69">
+        <v>44044</v>
+      </c>
+      <c r="S37" s="41"/>
+      <c r="T37" s="41"/>
+      <c r="U37" s="41"/>
+    </row>
+    <row r="38" spans="2:21" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B38" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="C38" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="G38" s="54" t="s">
+        <v>265</v>
+      </c>
+      <c r="H38" s="66">
+        <v>45084</v>
+      </c>
+      <c r="I38" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="J38" s="54">
+        <v>13068821001</v>
+      </c>
+      <c r="K38" s="54"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="O38" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q38" s="54" t="s">
+        <v>142</v>
+      </c>
+      <c r="R38" s="66">
+        <v>46568</v>
+      </c>
+      <c r="S38" s="54"/>
+      <c r="T38" s="54"/>
+      <c r="U38" s="54"/>
+    </row>
+    <row r="39" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B39" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G39" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="H39" s="45">
+        <v>43879</v>
+      </c>
+      <c r="I39" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="O38" s="41" t="s">
+      <c r="J39" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="K39" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="L39" s="47">
+        <v>46594</v>
+      </c>
+      <c r="M39" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="P38" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q38" s="41" t="s">
-        <v>161</v>
-      </c>
-      <c r="R38" s="69">
-        <v>44044</v>
-      </c>
-      <c r="S38" s="41"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="41"/>
-    </row>
-    <row r="39" spans="2:21" s="65" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="B39" s="33" t="s">
-        <v>261</v>
-      </c>
-      <c r="C39" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G39" s="54" t="s">
-        <v>271</v>
-      </c>
-      <c r="H39" s="66">
-        <v>45084</v>
-      </c>
-      <c r="I39" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="J39" s="54">
-        <v>13068821001</v>
-      </c>
-      <c r="K39" s="54"/>
-      <c r="L39" s="54"/>
-      <c r="M39" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="N39" s="33" t="s">
-        <v>145</v>
-      </c>
-      <c r="O39" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="P39" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q39" s="54" t="s">
-        <v>147</v>
-      </c>
-      <c r="R39" s="66">
-        <v>46568</v>
-      </c>
-      <c r="S39" s="54"/>
-      <c r="T39" s="54"/>
-      <c r="U39" s="54"/>
+      <c r="N39" s="43"/>
+      <c r="O39" s="44"/>
+      <c r="P39" s="44"/>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="46"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="U39" s="44"/>
     </row>
     <row r="40" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B40" s="43" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="D40" s="44" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E40" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F40" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G40" s="44" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="H40" s="45">
-        <v>43879</v>
+        <v>45648</v>
       </c>
       <c r="I40" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="J40" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="J40" s="44">
+        <v>13068821001</v>
+      </c>
+      <c r="K40" s="58" t="s">
         <v>165</v>
-      </c>
-      <c r="K40" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="L40" s="47">
-        <v>46594</v>
       </c>
       <c r="M40" s="46" t="s">
         <v>22</v>
@@ -4268,191 +4237,194 @@
       <c r="R40" s="46"/>
       <c r="S40" s="44"/>
       <c r="T40" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U40" s="44"/>
     </row>
-    <row r="41" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B41" s="43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D41" s="44" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E41" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F41" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G41" s="44" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H41" s="45">
-        <v>45648</v>
+        <v>45412</v>
       </c>
       <c r="I41" s="43" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J41" s="44">
         <v>13068821001</v>
       </c>
       <c r="K41" s="58" t="s">
-        <v>170</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="L41" s="54"/>
       <c r="M41" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N41" s="43"/>
-      <c r="O41" s="44"/>
-      <c r="P41" s="44"/>
-      <c r="Q41" s="44"/>
-      <c r="R41" s="46"/>
+      <c r="N41" s="43" t="s">
+        <v>140</v>
+      </c>
+      <c r="O41" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q41" s="44" t="s">
+        <v>142</v>
+      </c>
+      <c r="R41" s="45">
+        <v>46568</v>
+      </c>
       <c r="S41" s="44"/>
       <c r="T41" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="U41" s="44"/>
     </row>
-    <row r="42" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B42" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G42" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="H42" s="45">
-        <v>45412</v>
-      </c>
+    <row r="42" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B42" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G42" s="54"/>
+      <c r="H42" s="34"/>
       <c r="I42" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="J42" s="44">
-        <v>13068821001</v>
-      </c>
-      <c r="K42" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="L42" s="54"/>
+        <v>149</v>
+      </c>
+      <c r="J42" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="K42" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="L42" s="47">
+        <v>46766</v>
+      </c>
       <c r="M42" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N42" s="43" t="s">
-        <v>145</v>
-      </c>
-      <c r="O42" s="44" t="s">
+      <c r="N42" s="33"/>
+      <c r="O42" s="54"/>
+      <c r="P42" s="54"/>
+      <c r="Q42" s="54"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="54"/>
+      <c r="T42" s="54"/>
+      <c r="U42" s="54"/>
+    </row>
+    <row r="43" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B43" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="G43" s="54" t="s">
+        <v>266</v>
+      </c>
+      <c r="H43" s="66">
+        <v>42865</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="J43" s="54">
+        <v>17830511006</v>
+      </c>
+      <c r="M43" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="N43" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="O43" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="P42" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q42" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="R42" s="45">
-        <v>46568</v>
-      </c>
-      <c r="S42" s="44"/>
-      <c r="T42" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="U42" s="44"/>
-    </row>
-    <row r="43" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B43" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F43" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G43" s="54"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="43" t="s">
-        <v>154</v>
-      </c>
-      <c r="J43" s="44" t="s">
-        <v>155</v>
-      </c>
-      <c r="K43" s="44" t="s">
-        <v>156</v>
-      </c>
-      <c r="L43" s="47">
-        <v>46766</v>
-      </c>
-      <c r="M43" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N43" s="33"/>
-      <c r="O43" s="54"/>
-      <c r="P43" s="54"/>
-      <c r="Q43" s="54"/>
-      <c r="R43" s="34"/>
+      <c r="P43" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q43" s="54" t="s">
+        <v>289</v>
+      </c>
+      <c r="R43" s="66">
+        <v>46294</v>
+      </c>
       <c r="S43" s="54"/>
       <c r="T43" s="54"/>
       <c r="U43" s="54"/>
     </row>
     <row r="44" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B44" s="33" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C44" s="54" t="s">
-        <v>133</v>
+        <v>282</v>
       </c>
       <c r="D44" s="54"/>
       <c r="E44" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F44" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G44" s="54" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="H44" s="66">
         <v>42865</v>
       </c>
       <c r="I44" s="33" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J44" s="54">
         <v>17830511006</v>
       </c>
       <c r="M44" s="34" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N44" s="33" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="O44" s="54" t="s">
         <v>22</v>
       </c>
       <c r="P44" s="54" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="Q44" s="54" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="R44" s="66">
         <v>46294</v>
@@ -4461,209 +4433,205 @@
       <c r="T44" s="54"/>
       <c r="U44" s="54"/>
     </row>
-    <row r="45" spans="2:21" ht="30" x14ac:dyDescent="0.25">
-      <c r="B45" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="C45" s="54" t="s">
-        <v>288</v>
-      </c>
-      <c r="D45" s="54"/>
-      <c r="E45" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="54" t="s">
-        <v>289</v>
-      </c>
-      <c r="H45" s="66">
-        <v>42865</v>
-      </c>
-      <c r="I45" s="33" t="s">
-        <v>273</v>
-      </c>
-      <c r="J45" s="54">
-        <v>17830511006</v>
-      </c>
-      <c r="M45" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="N45" s="33" t="s">
-        <v>274</v>
-      </c>
-      <c r="O45" s="54" t="s">
+    <row r="45" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B45" s="61" t="s">
+        <v>214</v>
+      </c>
+      <c r="C45" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="62"/>
+      <c r="E45" s="62" t="s">
+        <v>93</v>
+      </c>
+      <c r="F45" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="G45" s="62" t="s">
+        <v>224</v>
+      </c>
+      <c r="H45" s="63"/>
+      <c r="I45" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="J45" s="62">
+        <v>11432111000</v>
+      </c>
+      <c r="K45" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="L45" s="62"/>
+      <c r="M45" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="P45" s="54" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q45" s="54" t="s">
-        <v>295</v>
-      </c>
-      <c r="R45" s="66">
-        <v>46294</v>
-      </c>
-      <c r="S45" s="54"/>
-      <c r="T45" s="54"/>
-      <c r="U45" s="54"/>
-    </row>
-    <row r="46" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B46" s="61" t="s">
-        <v>220</v>
-      </c>
-      <c r="C46" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="D46" s="62"/>
-      <c r="E46" s="62" t="s">
-        <v>94</v>
-      </c>
-      <c r="F46" s="62" t="s">
-        <v>100</v>
-      </c>
-      <c r="G46" s="62" t="s">
-        <v>230</v>
-      </c>
-      <c r="H46" s="63"/>
-      <c r="I46" s="61" t="s">
-        <v>229</v>
-      </c>
-      <c r="J46" s="62">
-        <v>11432111000</v>
+      <c r="N45" s="61"/>
+      <c r="O45" s="62"/>
+      <c r="P45" s="62"/>
+      <c r="Q45" s="62"/>
+      <c r="R45" s="63"/>
+      <c r="S45" s="62"/>
+      <c r="T45" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="U45" s="62"/>
+    </row>
+    <row r="46" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B46" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="C46" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F46" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="G46" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="H46" s="66">
+        <v>42140</v>
+      </c>
+      <c r="I46" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="J46" s="54">
+        <v>7500861005</v>
       </c>
       <c r="K46" s="68" t="s">
-        <v>170</v>
-      </c>
-      <c r="L46" s="62"/>
-      <c r="M46" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="M46" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="N46" s="33"/>
+      <c r="O46" s="54"/>
+      <c r="P46" s="54"/>
+      <c r="Q46" s="54"/>
+      <c r="R46" s="34"/>
+      <c r="S46" s="54"/>
+      <c r="T46" s="54"/>
+      <c r="U46" s="54"/>
+    </row>
+    <row r="47" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B47" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E47" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F47" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G47" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="H47" s="45">
+        <v>44985</v>
+      </c>
+      <c r="I47" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="44">
+        <v>11767131003</v>
+      </c>
+      <c r="K47" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="M47" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N46" s="61"/>
-      <c r="O46" s="62"/>
-      <c r="P46" s="62"/>
-      <c r="Q46" s="62"/>
-      <c r="R46" s="63"/>
-      <c r="S46" s="62"/>
-      <c r="T46" s="62" t="s">
-        <v>76</v>
-      </c>
-      <c r="U46" s="62"/>
-    </row>
-    <row r="47" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B47" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="C47" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G47" s="54" t="s">
-        <v>241</v>
-      </c>
-      <c r="H47" s="66">
-        <v>42140</v>
-      </c>
-      <c r="I47" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="J47" s="54">
-        <v>7500861005</v>
-      </c>
-      <c r="K47" s="68" t="s">
-        <v>169</v>
-      </c>
-      <c r="M47" s="34" t="s">
-        <v>194</v>
-      </c>
-      <c r="N47" s="33"/>
-      <c r="O47" s="54"/>
-      <c r="P47" s="54"/>
-      <c r="Q47" s="54"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="54"/>
-      <c r="T47" s="54"/>
-      <c r="U47" s="54"/>
-    </row>
-    <row r="48" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B48" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="C48" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E48" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G48" s="44" t="s">
+      <c r="N47" s="43"/>
+      <c r="O47" s="44"/>
+      <c r="P47" s="44"/>
+      <c r="Q47" s="44"/>
+      <c r="R47" s="46"/>
+      <c r="S47" s="44"/>
+      <c r="T47" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="U47" s="44"/>
+    </row>
+    <row r="48" spans="2:21" ht="45" x14ac:dyDescent="0.15">
+      <c r="B48" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="C48" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="54"/>
+      <c r="E48" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F48" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="G48" s="54"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="J48" s="54">
+        <v>17044251001</v>
+      </c>
+      <c r="K48" s="67" t="s">
+        <v>165</v>
+      </c>
+      <c r="M48" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="N48" s="33"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="54"/>
+      <c r="Q48" s="54"/>
+      <c r="R48" s="34"/>
+      <c r="S48" s="54"/>
+      <c r="T48" s="54"/>
+      <c r="U48" s="54"/>
+    </row>
+    <row r="49" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="B49" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="C49" s="54" t="s">
         <v>129</v>
-      </c>
-      <c r="H48" s="45">
-        <v>44985</v>
-      </c>
-      <c r="I48" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="J48" s="44">
-        <v>11767131003</v>
-      </c>
-      <c r="K48" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="M48" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N48" s="43"/>
-      <c r="O48" s="44"/>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
-      <c r="R48" s="46"/>
-      <c r="S48" s="44"/>
-      <c r="T48" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="U48" s="44"/>
-    </row>
-    <row r="49" spans="2:21" ht="45" x14ac:dyDescent="0.15">
-      <c r="B49" s="33" t="s">
-        <v>255</v>
-      </c>
-      <c r="C49" s="54" t="s">
-        <v>98</v>
       </c>
       <c r="D49" s="54"/>
       <c r="E49" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F49" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49" s="54"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="J49" s="54">
-        <v>17044251001</v>
-      </c>
-      <c r="K49" s="67" t="s">
-        <v>170</v>
-      </c>
-      <c r="M49" s="34" t="s">
-        <v>143</v>
+        <v>99</v>
+      </c>
+      <c r="G49" s="54" t="s">
+        <v>311</v>
+      </c>
+      <c r="H49" s="66">
+        <v>35494</v>
+      </c>
+      <c r="I49" s="40" t="s">
+        <v>313</v>
+      </c>
+      <c r="J49" s="41" t="s">
+        <v>314</v>
+      </c>
+      <c r="K49" s="41" t="s">
+        <v>331</v>
+      </c>
+      <c r="L49" s="76">
+        <v>44865</v>
+      </c>
+      <c r="M49" s="42" t="s">
+        <v>315</v>
       </c>
       <c r="N49" s="33"/>
       <c r="O49" s="54"/>
@@ -4674,40 +4642,34 @@
       <c r="T49" s="54"/>
       <c r="U49" s="54"/>
     </row>
-    <row r="50" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B50" s="33" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="C50" s="54" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="D50" s="54"/>
       <c r="E50" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F50" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G50" s="54" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="H50" s="66">
-        <v>35494</v>
-      </c>
-      <c r="I50" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="J50" s="41" t="s">
-        <v>320</v>
-      </c>
-      <c r="K50" s="41" t="s">
-        <v>337</v>
-      </c>
-      <c r="L50" s="76">
-        <v>44865</v>
-      </c>
-      <c r="M50" s="42" t="s">
-        <v>321</v>
+        <v>45978</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="J50" s="54">
+        <v>16319061004</v>
+      </c>
+      <c r="M50" s="34" t="s">
+        <v>188</v>
       </c>
       <c r="N50" s="33"/>
       <c r="O50" s="54"/>
@@ -4718,34 +4680,40 @@
       <c r="T50" s="54"/>
       <c r="U50" s="54"/>
     </row>
-    <row r="51" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" s="52" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B51" s="33" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C51" s="54" t="s">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="D51" s="54"/>
       <c r="E51" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F51" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G51" s="54" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="H51" s="66">
-        <v>45978</v>
+        <v>36213</v>
       </c>
       <c r="I51" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="J51" s="54">
-        <v>16319061004</v>
+        <v>319</v>
+      </c>
+      <c r="J51" s="54" t="s">
+        <v>320</v>
+      </c>
+      <c r="K51" s="54" t="s">
+        <v>332</v>
+      </c>
+      <c r="L51" s="75">
+        <v>47491</v>
       </c>
       <c r="M51" s="34" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="N51" s="33"/>
       <c r="O51" s="54"/>
@@ -4756,40 +4724,33 @@
       <c r="T51" s="54"/>
       <c r="U51" s="54"/>
     </row>
-    <row r="52" spans="2:21" s="52" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" ht="45" x14ac:dyDescent="0.15">
       <c r="B52" s="33" t="s">
-        <v>311</v>
+        <v>248</v>
       </c>
       <c r="C52" s="54" t="s">
-        <v>323</v>
+        <v>97</v>
       </c>
       <c r="D52" s="54"/>
       <c r="E52" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F52" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G52" s="54" t="s">
-        <v>324</v>
-      </c>
-      <c r="H52" s="66">
-        <v>36213</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G52" s="54"/>
+      <c r="H52" s="34"/>
       <c r="I52" s="33" t="s">
-        <v>325</v>
-      </c>
-      <c r="J52" s="54" t="s">
-        <v>326</v>
-      </c>
-      <c r="K52" s="54" t="s">
-        <v>338</v>
-      </c>
-      <c r="L52" s="75">
-        <v>47491</v>
+        <v>250</v>
+      </c>
+      <c r="J52" s="54">
+        <v>17044251001</v>
+      </c>
+      <c r="K52" s="67" t="s">
+        <v>165</v>
       </c>
       <c r="M52" s="34" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="N52" s="33"/>
       <c r="O52" s="54"/>
@@ -4800,33 +4761,40 @@
       <c r="T52" s="54"/>
       <c r="U52" s="54"/>
     </row>
-    <row r="53" spans="2:21" ht="45" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B53" s="33" t="s">
-        <v>254</v>
+        <v>312</v>
       </c>
       <c r="C53" s="54" t="s">
-        <v>98</v>
+        <v>236</v>
       </c>
       <c r="D53" s="54"/>
       <c r="E53" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F53" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" s="54"/>
-      <c r="H53" s="34"/>
+        <v>99</v>
+      </c>
+      <c r="G53" s="54" t="s">
+        <v>323</v>
+      </c>
+      <c r="H53" s="66">
+        <v>45314</v>
+      </c>
       <c r="I53" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="J53" s="54">
-        <v>17044251001</v>
-      </c>
-      <c r="K53" s="67" t="s">
-        <v>170</v>
+        <v>324</v>
+      </c>
+      <c r="J53" s="54" t="s">
+        <v>325</v>
+      </c>
+      <c r="K53" s="54" t="s">
+        <v>333</v>
+      </c>
+      <c r="L53" s="75">
+        <v>46344</v>
       </c>
       <c r="M53" s="34" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="N53" s="33"/>
       <c r="O53" s="54"/>
@@ -4838,97 +4806,104 @@
       <c r="U53" s="54"/>
     </row>
     <row r="54" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B54" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="C54" s="54" t="s">
-        <v>242</v>
-      </c>
-      <c r="D54" s="54"/>
-      <c r="E54" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G54" s="54" t="s">
-        <v>329</v>
-      </c>
-      <c r="H54" s="66">
-        <v>45314</v>
-      </c>
-      <c r="I54" s="33" t="s">
-        <v>330</v>
-      </c>
-      <c r="J54" s="54" t="s">
-        <v>331</v>
-      </c>
-      <c r="K54" s="54" t="s">
-        <v>339</v>
-      </c>
-      <c r="L54" s="75">
-        <v>46344</v>
-      </c>
-      <c r="M54" s="34" t="s">
+      <c r="B54" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="C54" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E54" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G54" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="H54" s="45">
+        <v>45979</v>
+      </c>
+      <c r="I54" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="N54" s="33"/>
-      <c r="O54" s="54"/>
-      <c r="P54" s="54"/>
-      <c r="Q54" s="54"/>
-      <c r="R54" s="34"/>
-      <c r="S54" s="54"/>
-      <c r="T54" s="54"/>
-      <c r="U54" s="54"/>
+      <c r="J54" s="44">
+        <v>9075711219</v>
+      </c>
+      <c r="K54" s="58" t="s">
+        <v>164</v>
+      </c>
+      <c r="L54" s="44"/>
+      <c r="M54" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="N54" s="43" t="s">
+        <v>196</v>
+      </c>
+      <c r="O54" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="P54" s="44">
+        <v>2828850582</v>
+      </c>
+      <c r="Q54" s="44"/>
+      <c r="R54" s="46"/>
+      <c r="S54" s="44"/>
+      <c r="T54" s="44"/>
+      <c r="U54" s="44"/>
     </row>
     <row r="55" spans="2:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B55" s="43" t="s">
-        <v>197</v>
+        <v>69</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>198</v>
+        <v>97</v>
       </c>
       <c r="D55" s="44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E55" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F55" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="H55" s="45">
-        <v>45979</v>
+        <v>43584</v>
       </c>
       <c r="I55" s="43" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="J55" s="44">
-        <v>9075711219</v>
+        <v>15242251005</v>
       </c>
       <c r="K55" s="58" t="s">
-        <v>169</v>
-      </c>
-      <c r="L55" s="44"/>
+        <v>164</v>
+      </c>
       <c r="M55" s="46" t="s">
-        <v>201</v>
+        <v>22</v>
       </c>
       <c r="N55" s="43" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="O55" s="44" t="s">
-        <v>194</v>
+        <v>22</v>
       </c>
       <c r="P55" s="44">
-        <v>2828850582</v>
+        <v>14119701002</v>
       </c>
       <c r="Q55" s="44"/>
       <c r="R55" s="46"/>
       <c r="S55" s="44"/>
-      <c r="T55" s="44"/>
+      <c r="T55" s="44" t="s">
+        <v>88</v>
+      </c>
       <c r="U55" s="44"/>
     </row>
     <row r="56" spans="2:21" ht="45" x14ac:dyDescent="0.25">
@@ -4936,19 +4911,19 @@
         <v>69</v>
       </c>
       <c r="C56" s="44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D56" s="44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E56" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F56" s="44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H56" s="45">
         <v>43584</v>
@@ -4959,59 +4934,45 @@
       <c r="J56" s="44">
         <v>15242251005</v>
       </c>
-      <c r="K56" s="58" t="s">
-        <v>169</v>
+      <c r="K56" s="44" t="s">
+        <v>164</v>
       </c>
       <c r="M56" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="N56" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="O56" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="P56" s="44">
-        <v>14119701002</v>
-      </c>
+      <c r="N56" s="43"/>
+      <c r="O56" s="44"/>
+      <c r="P56" s="44"/>
       <c r="Q56" s="44"/>
       <c r="R56" s="46"/>
       <c r="S56" s="44"/>
-      <c r="T56" s="44" t="s">
-        <v>89</v>
-      </c>
+      <c r="T56" s="44"/>
       <c r="U56" s="44"/>
     </row>
     <row r="57" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B57" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="D57" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E57" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G57" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="H57" s="45">
-        <v>43584</v>
-      </c>
+      <c r="B57" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="C57" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="38"/>
+      <c r="E57" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" s="54"/>
+      <c r="H57" s="34"/>
       <c r="I57" s="43" t="s">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="J57" s="44">
-        <v>15242251005</v>
+        <v>14119701002</v>
       </c>
       <c r="K57" s="44" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="M57" s="46" t="s">
         <v>22</v>
@@ -5025,31 +4986,32 @@
       <c r="T57" s="44"/>
       <c r="U57" s="44"/>
     </row>
-    <row r="58" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B58" s="37" t="s">
         <v>67</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D58" s="38"/>
       <c r="E58" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F58" s="38" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G58" s="54"/>
       <c r="H58" s="34"/>
       <c r="I58" s="43" t="s">
-        <v>167</v>
+        <v>78</v>
       </c>
       <c r="J58" s="44">
-        <v>14119701002</v>
+        <v>15242251005</v>
       </c>
       <c r="K58" s="44" t="s">
-        <v>168</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="L58" s="54"/>
       <c r="M58" s="46" t="s">
         <v>22</v>
       </c>
@@ -5062,241 +5024,241 @@
       <c r="T58" s="44"/>
       <c r="U58" s="44"/>
     </row>
-    <row r="59" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B59" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F59" s="38" t="s">
-        <v>97</v>
+    <row r="59" spans="2:21" ht="30" x14ac:dyDescent="0.15">
+      <c r="B59" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="C59" s="54" t="s">
+        <v>245</v>
+      </c>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="54" t="s">
+        <v>96</v>
       </c>
       <c r="G59" s="54"/>
       <c r="H59" s="34"/>
-      <c r="I59" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="J59" s="44">
-        <v>15242251005</v>
-      </c>
-      <c r="K59" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="L59" s="54"/>
-      <c r="M59" s="46" t="s">
+      <c r="I59" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="J59" s="54">
+        <v>14699681004</v>
+      </c>
+      <c r="K59" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="M59" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="43"/>
-      <c r="O59" s="44"/>
-      <c r="P59" s="44"/>
-      <c r="Q59" s="44"/>
-      <c r="R59" s="46"/>
-      <c r="S59" s="44"/>
-      <c r="T59" s="44"/>
-      <c r="U59" s="44"/>
-    </row>
-    <row r="60" spans="2:21" ht="30" x14ac:dyDescent="0.15">
-      <c r="B60" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="C60" s="54" t="s">
+      <c r="N59" s="33"/>
+      <c r="O59" s="54"/>
+      <c r="P59" s="54"/>
+      <c r="Q59" s="54"/>
+      <c r="R59" s="34"/>
+      <c r="S59" s="54"/>
+      <c r="T59" s="54"/>
+      <c r="U59" s="54"/>
+    </row>
+    <row r="60" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B60" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C60" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F60" s="44" t="s">
+        <v>99</v>
+      </c>
+      <c r="G60" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H60" s="45">
+        <v>45909</v>
+      </c>
+      <c r="I60" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="J60" s="44">
+        <v>13068821001</v>
+      </c>
+      <c r="K60" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="M60" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N60" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="O60" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P60" s="44" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q60" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="R60" s="45">
+        <v>47469</v>
+      </c>
+      <c r="S60" s="44"/>
+      <c r="T60" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="U60" s="44"/>
+    </row>
+    <row r="61" spans="2:21" ht="33.75" x14ac:dyDescent="0.15">
+      <c r="B61" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="C61" s="54" t="s">
+        <v>241</v>
+      </c>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F61" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="G61" s="54" t="s">
+        <v>242</v>
+      </c>
+      <c r="H61" s="66">
+        <v>43883</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="J61" s="54">
+        <v>1158230639</v>
+      </c>
+      <c r="K61" s="67" t="s">
         <v>251</v>
       </c>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="G60" s="54"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="J60" s="54">
-        <v>14699681004</v>
-      </c>
-      <c r="K60" s="67" t="s">
-        <v>258</v>
-      </c>
-      <c r="M60" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="N60" s="33"/>
-      <c r="O60" s="54"/>
-      <c r="P60" s="54"/>
-      <c r="Q60" s="54"/>
-      <c r="R60" s="34"/>
-      <c r="S60" s="54"/>
-      <c r="T60" s="54"/>
-      <c r="U60" s="54"/>
-    </row>
-    <row r="61" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B61" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C61" s="44" t="s">
-        <v>133</v>
-      </c>
-      <c r="D61" s="44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E61" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="F61" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G61" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="H61" s="45">
-        <v>45909</v>
-      </c>
-      <c r="I61" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="J61" s="44">
-        <v>13068821001</v>
-      </c>
-      <c r="K61" s="58" t="s">
-        <v>170</v>
-      </c>
-      <c r="M61" s="46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N61" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="O61" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="P61" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q61" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="R61" s="45">
-        <v>47469</v>
-      </c>
-      <c r="S61" s="44"/>
-      <c r="T61" s="44" t="s">
-        <v>89</v>
-      </c>
-      <c r="U61" s="44"/>
-    </row>
-    <row r="62" spans="2:21" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="B62" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="C62" s="54" t="s">
-        <v>247</v>
-      </c>
-      <c r="D62" s="54"/>
-      <c r="E62" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F62" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G62" s="54" t="s">
-        <v>248</v>
-      </c>
-      <c r="H62" s="66">
-        <v>43883</v>
-      </c>
-      <c r="I62" s="33" t="s">
-        <v>249</v>
-      </c>
-      <c r="J62" s="54">
-        <v>1158230639</v>
-      </c>
-      <c r="K62" s="67" t="s">
-        <v>257</v>
-      </c>
-      <c r="M62" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="N62" s="33"/>
-      <c r="O62" s="54"/>
-      <c r="P62" s="54"/>
-      <c r="Q62" s="54"/>
-      <c r="R62" s="34"/>
-      <c r="S62" s="54"/>
-      <c r="T62" s="54"/>
-      <c r="U62" s="54"/>
-    </row>
-    <row r="63" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="B63" s="40" t="s">
-        <v>269</v>
-      </c>
-      <c r="C63" s="41" t="s">
-        <v>290</v>
-      </c>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="G63" s="41"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="40" t="s">
+      <c r="M61" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="N61" s="33"/>
+      <c r="O61" s="54"/>
+      <c r="P61" s="54"/>
+      <c r="Q61" s="54"/>
+      <c r="R61" s="34"/>
+      <c r="S61" s="54"/>
+      <c r="T61" s="54"/>
+      <c r="U61" s="54"/>
+    </row>
+    <row r="62" spans="2:21" s="52" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="B62" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="C62" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="F62" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G62" s="41"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="J62" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="K62" s="41"/>
+      <c r="L62" s="41"/>
+      <c r="M62" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="N62" s="40"/>
+      <c r="O62" s="41"/>
+      <c r="P62" s="41"/>
+      <c r="Q62" s="41"/>
+      <c r="R62" s="42"/>
+      <c r="S62" s="41"/>
+      <c r="T62" s="41"/>
+      <c r="U62" s="41"/>
+    </row>
+    <row r="63" spans="2:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B63" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="J63" s="41" t="s">
+      <c r="C63" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="F63" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="G63" s="54" t="s">
+        <v>298</v>
+      </c>
+      <c r="H63" s="66">
+        <v>41058</v>
+      </c>
+      <c r="I63" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="J63" s="54">
+        <v>9750851009</v>
+      </c>
+      <c r="M63" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="N63" s="33"/>
+      <c r="O63" s="54"/>
+      <c r="P63" s="54"/>
+      <c r="Q63" s="54"/>
+      <c r="R63" s="34"/>
+      <c r="S63" s="54"/>
+      <c r="T63" s="54"/>
+      <c r="U63" s="54"/>
+    </row>
+    <row r="64" spans="2:21" ht="60" x14ac:dyDescent="0.25">
+      <c r="B64" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="K63" s="41"/>
-      <c r="L63" s="41"/>
-      <c r="M63" s="42" t="s">
-        <v>293</v>
-      </c>
-      <c r="N63" s="40"/>
-      <c r="O63" s="41"/>
-      <c r="P63" s="41"/>
-      <c r="Q63" s="41"/>
-      <c r="R63" s="42"/>
-      <c r="S63" s="41"/>
-      <c r="T63" s="41"/>
-      <c r="U63" s="41"/>
-    </row>
-    <row r="64" spans="2:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="B64" s="33" t="s">
-        <v>297</v>
-      </c>
       <c r="C64" s="54" t="s">
-        <v>133</v>
+        <v>300</v>
       </c>
       <c r="D64" s="54"/>
       <c r="E64" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F64" s="54" t="s">
-        <v>100</v>
+        <v>303</v>
       </c>
       <c r="G64" s="54" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H64" s="66">
-        <v>41058</v>
+        <v>42936</v>
       </c>
       <c r="I64" s="33" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J64" s="54">
-        <v>9750851009</v>
+        <v>7978810583</v>
       </c>
       <c r="M64" s="34" t="s">
-        <v>294</v>
+        <v>188</v>
       </c>
       <c r="N64" s="33"/>
       <c r="O64" s="54"/>
@@ -5307,34 +5269,34 @@
       <c r="T64" s="54"/>
       <c r="U64" s="54"/>
     </row>
-    <row r="65" spans="2:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B65" s="33" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="C65" s="54" t="s">
-        <v>306</v>
+        <v>175</v>
       </c>
       <c r="D65" s="54"/>
       <c r="E65" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>309</v>
+        <v>99</v>
       </c>
       <c r="G65" s="54" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="H65" s="66">
-        <v>42936</v>
+        <v>44901</v>
       </c>
       <c r="I65" s="33" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="J65" s="54">
-        <v>7978810583</v>
+        <v>3185110214</v>
       </c>
       <c r="M65" s="34" t="s">
-        <v>194</v>
+        <v>288</v>
       </c>
       <c r="N65" s="33"/>
       <c r="O65" s="54"/>
@@ -5345,170 +5307,152 @@
       <c r="T65" s="54"/>
       <c r="U65" s="54"/>
     </row>
-    <row r="66" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:21" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B66" s="33" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C66" s="54" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="D66" s="54"/>
       <c r="E66" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F66" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G66" s="54" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="H66" s="66">
-        <v>44901</v>
+        <v>45825</v>
       </c>
       <c r="I66" s="33" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="J66" s="54">
-        <v>3185110214</v>
-      </c>
+        <v>6575701005</v>
+      </c>
+      <c r="K66" s="54"/>
+      <c r="L66" s="54"/>
       <c r="M66" s="34" t="s">
-        <v>294</v>
-      </c>
-      <c r="N66" s="33"/>
-      <c r="O66" s="54"/>
-      <c r="P66" s="54"/>
+        <v>275</v>
+      </c>
+      <c r="N66" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="O66" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="P66" s="54">
+        <v>8822460963</v>
+      </c>
       <c r="Q66" s="54"/>
       <c r="R66" s="34"/>
       <c r="S66" s="54"/>
       <c r="T66" s="54"/>
       <c r="U66" s="54"/>
     </row>
-    <row r="67" spans="2:21" s="70" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B67" s="33" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C67" s="54" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D67" s="54"/>
       <c r="E67" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F67" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G67" s="54" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="H67" s="66">
-        <v>45825</v>
+        <v>46084</v>
       </c>
       <c r="I67" s="33" t="s">
-        <v>280</v>
+        <v>118</v>
       </c>
       <c r="J67" s="54">
-        <v>6575701005</v>
-      </c>
-      <c r="K67" s="54"/>
-      <c r="L67" s="54"/>
+        <v>13068821001</v>
+      </c>
       <c r="M67" s="34" t="s">
-        <v>281</v>
+        <v>22</v>
       </c>
       <c r="N67" s="33" t="s">
-        <v>282</v>
+        <v>119</v>
       </c>
       <c r="O67" s="54" t="s">
-        <v>283</v>
-      </c>
-      <c r="P67" s="54">
-        <v>8822460963</v>
-      </c>
-      <c r="Q67" s="54"/>
-      <c r="R67" s="34"/>
+        <v>22</v>
+      </c>
+      <c r="P67" s="54" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q67" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="R67" s="66">
+        <v>46790</v>
+      </c>
       <c r="S67" s="54"/>
       <c r="T67" s="54"/>
       <c r="U67" s="54"/>
     </row>
-    <row r="68" spans="2:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:21" ht="33.75" x14ac:dyDescent="0.15">
       <c r="B68" s="33" t="s">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="C68" s="54" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="D68" s="54"/>
       <c r="E68" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F68" s="54" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G68" s="54" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="H68" s="66">
-        <v>46084</v>
+        <v>46019</v>
       </c>
       <c r="I68" s="33" t="s">
-        <v>122</v>
+        <v>238</v>
       </c>
       <c r="J68" s="54">
-        <v>13068821001</v>
+        <v>17702651005</v>
+      </c>
+      <c r="K68" s="67" t="s">
+        <v>164</v>
       </c>
       <c r="M68" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="N68" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="O68" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="P68" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q68" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="R68" s="66">
-        <v>46790</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N68" s="33"/>
+      <c r="O68" s="54"/>
+      <c r="P68" s="54"/>
+      <c r="Q68" s="54"/>
+      <c r="R68" s="34"/>
       <c r="S68" s="54"/>
       <c r="T68" s="54"/>
       <c r="U68" s="54"/>
     </row>
-    <row r="69" spans="2:21" ht="33.75" x14ac:dyDescent="0.15">
-      <c r="B69" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="C69" s="54" t="s">
-        <v>242</v>
-      </c>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B69" s="33"/>
+      <c r="C69" s="54"/>
       <c r="D69" s="54"/>
-      <c r="E69" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="F69" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="G69" s="54" t="s">
-        <v>243</v>
-      </c>
-      <c r="H69" s="66">
-        <v>46019</v>
-      </c>
-      <c r="I69" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="J69" s="54">
-        <v>17702651005</v>
-      </c>
-      <c r="K69" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="M69" s="34" t="s">
-        <v>245</v>
-      </c>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="54"/>
+      <c r="M69" s="34"/>
       <c r="N69" s="33"/>
       <c r="O69" s="54"/>
       <c r="P69" s="54"/>
@@ -5538,26 +5482,6 @@
       <c r="T70" s="54"/>
       <c r="U70" s="54"/>
     </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B71" s="33"/>
-      <c r="C71" s="54"/>
-      <c r="D71" s="54"/>
-      <c r="E71" s="54"/>
-      <c r="F71" s="54"/>
-      <c r="G71" s="54"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="33"/>
-      <c r="J71" s="54"/>
-      <c r="M71" s="34"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="54"/>
-      <c r="P71" s="54"/>
-      <c r="Q71" s="54"/>
-      <c r="R71" s="34"/>
-      <c r="S71" s="54"/>
-      <c r="T71" s="54"/>
-      <c r="U71" s="54"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
